--- a/research/traditional_assets/database/data/argentina/argentina_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_oil_gas_production_and_exploration.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.6820000000000001</v>
+        <v>0.651</v>
       </c>
       <c r="E2">
-        <v>0.28</v>
+        <v>0.493</v>
       </c>
       <c r="G2">
-        <v>0.2497055359246172</v>
+        <v>0.1825497002208899</v>
       </c>
       <c r="H2">
-        <v>0.2497055359246172</v>
+        <v>0.1825497002208899</v>
       </c>
       <c r="I2">
-        <v>0.09481743227326267</v>
+        <v>0.03923950773114548</v>
       </c>
       <c r="J2">
-        <v>0.09481743227326267</v>
+        <v>0.03923950773114548</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>39.9</v>
       </c>
       <c r="L2">
-        <v>0.03828032979976442</v>
+        <v>0.06295361312716946</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -635,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.3</v>
+        <v>16.36</v>
       </c>
       <c r="V2">
-        <v>0.007446948728087518</v>
+        <v>0.007209589282566544</v>
       </c>
       <c r="W2">
-        <v>0.02890173410404624</v>
+        <v>0.04493590784984723</v>
       </c>
       <c r="X2">
-        <v>0.277924760643432</v>
+        <v>0.2615456150448038</v>
       </c>
       <c r="Y2">
-        <v>-0.2490230265393857</v>
+        <v>-0.2166097071949566</v>
       </c>
       <c r="Z2">
-        <v>0.4237637105529143</v>
+        <v>0.5003236552518985</v>
       </c>
       <c r="AA2">
-        <v>0.04018018692521744</v>
+        <v>0.01221497796807725</v>
       </c>
       <c r="AB2">
-        <v>0.2504196420332779</v>
+        <v>0.2459944231280793</v>
       </c>
       <c r="AC2">
-        <v>-0.2102394551080605</v>
+        <v>-0.233779445160002</v>
       </c>
       <c r="AD2">
-        <v>434.4</v>
+        <v>455.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>434.4</v>
+        <v>455.4</v>
       </c>
       <c r="AG2">
-        <v>423.1</v>
+        <v>439.04</v>
       </c>
       <c r="AH2">
-        <v>0.2225637872732862</v>
+        <v>0.1671438009249064</v>
       </c>
       <c r="AI2">
-        <v>0.4799469671859463</v>
+        <v>0.3247290359383913</v>
       </c>
       <c r="AJ2">
-        <v>0.2180365885081164</v>
+        <v>0.1621126635748678</v>
       </c>
       <c r="AK2">
-        <v>0.4733721190422913</v>
+        <v>0.3167585351072119</v>
       </c>
       <c r="AL2">
         <v>38.2</v>
       </c>
       <c r="AM2">
-        <v>33.58000000000001</v>
+        <v>-55.82000000000001</v>
       </c>
       <c r="AN2">
-        <v>3.706484641638225</v>
+        <v>3.702138037557922</v>
       </c>
       <c r="AO2">
-        <v>0.8429319371727749</v>
+        <v>0.6510471204188483</v>
       </c>
       <c r="AP2">
-        <v>3.610068259385665</v>
+        <v>3.569140720266645</v>
       </c>
       <c r="AQ2">
-        <v>0.958904109589041</v>
+        <v>-0.4455392332497313</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +775,10 @@
         <v>0.02890173410404624</v>
       </c>
       <c r="X3">
-        <v>0.277924760643432</v>
+        <v>0.27798172175035</v>
       </c>
       <c r="Y3">
-        <v>-0.2490230265393857</v>
+        <v>-0.2490799876463038</v>
       </c>
       <c r="Z3">
         <v>0.4237637105529143</v>
@@ -787,10 +787,10 @@
         <v>0.04018018692521744</v>
       </c>
       <c r="AB3">
-        <v>0.2504196420332779</v>
+        <v>0.2504639256605131</v>
       </c>
       <c r="AC3">
-        <v>-0.2102394551080605</v>
+        <v>-0.2102837387352956</v>
       </c>
       <c r="AD3">
         <v>434.4</v>
@@ -833,6 +833,134 @@
       </c>
       <c r="AQ3">
         <v>0.958904109589041</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial del Plata S.A. (BASE:COME)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Oil/Gas (Production and Exploration)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.62</v>
+      </c>
+      <c r="E4">
+        <v>0.706</v>
+      </c>
+      <c r="G4">
+        <v>0.1050305914343984</v>
+      </c>
+      <c r="H4">
+        <v>0.1050305914343984</v>
+      </c>
+      <c r="I4">
+        <v>-0.02491502379333787</v>
+      </c>
+      <c r="J4">
+        <v>-0.02491502379333787</v>
+      </c>
+      <c r="K4">
+        <v>26.9</v>
+      </c>
+      <c r="L4">
+        <v>0.09143439836845683</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>5.06</v>
+      </c>
+      <c r="V4">
+        <v>0.006730513434424048</v>
+      </c>
+      <c r="W4">
+        <v>0.06097008159564823</v>
+      </c>
+      <c r="X4">
+        <v>0.2451095083392577</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1841394267436094</v>
+      </c>
+      <c r="Z4">
+        <v>0.6321579750316938</v>
+      </c>
+      <c r="AA4">
+        <v>-0.01575023098906294</v>
+      </c>
+      <c r="AB4">
+        <v>0.2415249205956455</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2572751515847084</v>
+      </c>
+      <c r="AD4">
+        <v>21</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>21</v>
+      </c>
+      <c r="AG4">
+        <v>15.94</v>
+      </c>
+      <c r="AH4">
+        <v>0.02717391304347826</v>
+      </c>
+      <c r="AI4">
+        <v>0.04222803136939473</v>
+      </c>
+      <c r="AJ4">
+        <v>0.02076223721572407</v>
+      </c>
+      <c r="AK4">
+        <v>0.03238257760442061</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-89.40000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>3.614457831325301</v>
+      </c>
+      <c r="AP4">
+        <v>2.743545611015491</v>
+      </c>
+      <c r="AQ4">
+        <v>0.08199105145413869</v>
       </c>
     </row>
   </sheetData>
@@ -1127,7 +1255,7 @@
         <v>0.842931937172775</v>
       </c>
       <c r="F2">
-        <v>10.9776544771515</v>
+        <v>11.0419834293491</v>
       </c>
       <c r="G2">
         <v>3.70648464163822</v>
@@ -1145,13 +1273,13 @@
         <v>1517.4</v>
       </c>
       <c r="L2">
-        <v>1982.46315048064</v>
+        <v>1982.61167312806</v>
       </c>
       <c r="M2">
         <v>1940.5</v>
       </c>
       <c r="N2">
-        <v>2029.71715048064</v>
+        <v>2029.86567312806</v>
       </c>
       <c r="O2">
         <v>434.4</v>
@@ -1160,16 +1288,16 @@
         <v>58.554</v>
       </c>
       <c r="Q2">
-        <v>0.250419642033278</v>
+        <v>0.250463925660513</v>
       </c>
       <c r="R2">
-        <v>0.24142549159697</v>
+        <v>0.241453511954912</v>
       </c>
       <c r="S2">
         <v>0.154341679374328</v>
       </c>
       <c r="T2">
-        <v>0.111571679374328</v>
+        <v>0.110921679374328</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,10 +1310,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.277924760643432</v>
+        <v>0.27798172175035</v>
       </c>
       <c r="X2">
-        <v>0.245441588882206</v>
+        <v>0.24549057894194</v>
       </c>
       <c r="Y2">
         <v>1.14079521355345</v>
@@ -1224,7 +1352,7 @@
         <v>1517.4</v>
       </c>
       <c r="AK2">
-        <v>0.2034762750453591</v>
+        <v>0.2035262060989271</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.2415072675247498</v>
+        <v>0.2415552921411639</v>
       </c>
       <c r="C2">
-        <v>2040.169036840248</v>
+        <v>2040.110273276448</v>
       </c>
       <c r="D2">
-        <v>2028.869036840248</v>
+        <v>2028.810273276448</v>
       </c>
       <c r="E2">
         <v>-434.4</v>
@@ -1463,19 +1591,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.2415072675247498</v>
+        <v>0.2415552921411639</v>
       </c>
       <c r="T2">
         <v>0.9618186075065634</v>
       </c>
       <c r="U2">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V2">
         <v>0.35</v>
       </c>
       <c r="W2">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1622,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.2414728588821565</v>
+        <v>0.2415116154124131</v>
       </c>
       <c r="C3">
-        <v>2021.007809005566</v>
+        <v>2021.04504045537</v>
       </c>
       <c r="D3">
-        <v>2029.225809005566</v>
+        <v>2029.26304045537</v>
       </c>
       <c r="E3">
         <v>-414.8819999999999</v>
@@ -1527,37 +1655,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M3">
-        <v>3.328770258504835</v>
+        <v>3.301445058504835</v>
       </c>
       <c r="N3">
-        <v>107.0045630748285</v>
+        <v>107.0318882748285</v>
       </c>
       <c r="O3">
-        <v>37.45159707618998</v>
+        <v>37.46116089618997</v>
       </c>
       <c r="P3">
-        <v>69.55296599863854</v>
+        <v>69.57072737863854</v>
       </c>
       <c r="Q3">
-        <v>154.5529659986385</v>
+        <v>154.5707273786385</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.2427922142307204</v>
+        <v>0.2428405541602726</v>
       </c>
       <c r="T3">
         <v>0.9681335781619097</v>
       </c>
       <c r="U3">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V3">
         <v>0.35</v>
       </c>
       <c r="W3">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>33.14537344577548</v>
+        <v>33.41970906015965</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1704,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.2414384502395631</v>
+        <v>0.2414679386836623</v>
       </c>
       <c r="C4">
-        <v>2001.846706668156</v>
+        <v>2001.98000976643</v>
       </c>
       <c r="D4">
-        <v>2029.582706668156</v>
+        <v>2029.71600976643</v>
       </c>
       <c r="E4">
         <v>-395.364</v>
@@ -1609,37 +1737,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M4">
-        <v>6.65754051700967</v>
+        <v>6.602890117009671</v>
       </c>
       <c r="N4">
-        <v>103.6757928163237</v>
+        <v>103.7304432163237</v>
       </c>
       <c r="O4">
-        <v>36.28652748571329</v>
+        <v>36.30565512571329</v>
       </c>
       <c r="P4">
-        <v>67.38926533061039</v>
+        <v>67.42478809061039</v>
       </c>
       <c r="Q4">
-        <v>152.3892653306104</v>
+        <v>152.4247880906104</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.2441033843388536</v>
+        <v>0.2441520460165059</v>
       </c>
       <c r="T4">
         <v>0.9745774257694056</v>
       </c>
       <c r="U4">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V4">
         <v>0.35</v>
       </c>
       <c r="W4">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>16.57268672288774</v>
+        <v>16.70985453007982</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1786,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.2414254915969698</v>
+        <v>0.2414535119549115</v>
       </c>
       <c r="C5">
-        <v>1982.46315048064</v>
+        <v>1982.611673128061</v>
       </c>
       <c r="D5">
-        <v>2029.71715048064</v>
+        <v>2029.865673128061</v>
       </c>
       <c r="E5">
         <v>-375.846</v>
@@ -1691,37 +1819,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M5">
-        <v>10.05072017551451</v>
+        <v>9.992166175514505</v>
       </c>
       <c r="N5">
-        <v>100.2826131578188</v>
+        <v>100.3411671578188</v>
       </c>
       <c r="O5">
-        <v>35.09891460523659</v>
+        <v>35.11940850523658</v>
       </c>
       <c r="P5">
-        <v>65.18369855258226</v>
+        <v>65.22175865258225</v>
       </c>
       <c r="Q5">
-        <v>150.1836985525823</v>
+        <v>150.2217586525823</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.2454415888822061</v>
+        <v>0.2454905789419399</v>
       </c>
       <c r="T5">
         <v>0.9811541362141696</v>
       </c>
       <c r="U5">
-        <v>0.1716487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V5">
         <v>0.35</v>
       </c>
       <c r="W5">
-        <v>0.1115716793743285</v>
+        <v>0.1109216793743285</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>10.97765447715146</v>
+        <v>11.04198342934906</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1868,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.2414554329543764</v>
+        <v>0.2414637852261608</v>
       </c>
       <c r="C6">
-        <v>1962.634540722867</v>
+        <v>1962.987095609715</v>
       </c>
       <c r="D6">
-        <v>2029.406540722867</v>
+        <v>2029.759095609715</v>
       </c>
       <c r="E6">
         <v>-356.328</v>
@@ -1773,37 +1901,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M6">
-        <v>13.57271863401934</v>
+        <v>13.45561063401934</v>
       </c>
       <c r="N6">
-        <v>96.760614699314</v>
+        <v>96.87772269931401</v>
       </c>
       <c r="O6">
-        <v>33.8662151447599</v>
+        <v>33.9072029447599</v>
       </c>
       <c r="P6">
-        <v>62.89439955455411</v>
+        <v>62.9705197545541</v>
       </c>
       <c r="Q6">
-        <v>147.8943995545541</v>
+        <v>147.9705197545541</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.2468076726868784</v>
+        <v>0.2468569979699871</v>
       </c>
       <c r="T6">
         <v>0.9878678614598663</v>
       </c>
       <c r="U6">
-        <v>0.1738487374989668</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.1130016793743285</v>
+        <v>0.1120266793743285</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>8.12905183614345</v>
+        <v>8.199801282476287</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1950,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.2414912243117831</v>
+        <v>0.2414669084974099</v>
       </c>
       <c r="C7">
-        <v>1942.745368152008</v>
+        <v>1943.436696221006</v>
       </c>
       <c r="D7">
-        <v>2029.035368152008</v>
+        <v>2029.726696221006</v>
       </c>
       <c r="E7">
         <v>-336.8099999999999</v>
@@ -1855,37 +1983,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M7">
-        <v>17.11228329252418</v>
+        <v>16.89758529252418</v>
       </c>
       <c r="N7">
-        <v>93.22105004080916</v>
+        <v>93.43574804080916</v>
       </c>
       <c r="O7">
-        <v>32.62736751428321</v>
+        <v>32.70251181428321</v>
       </c>
       <c r="P7">
-        <v>60.59368252652595</v>
+        <v>60.73323622652595</v>
       </c>
       <c r="Q7">
-        <v>145.593682526526</v>
+        <v>145.7332362265259</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.2482025161505965</v>
+        <v>0.2482521837144142</v>
       </c>
       <c r="T7">
         <v>0.9947229282896827</v>
       </c>
       <c r="U7">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V7">
         <v>0.35</v>
       </c>
       <c r="W7">
-        <v>0.1139766793743285</v>
+        <v>0.1125466793743285</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>6.447610260258753</v>
+        <v>6.52953255884123</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2032,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.2415426156691898</v>
+        <v>0.2414882317686592</v>
       </c>
       <c r="C8">
-        <v>1922.694653896407</v>
+        <v>1923.697525982436</v>
       </c>
       <c r="D8">
-        <v>2028.502653896407</v>
+        <v>2029.505525982436</v>
       </c>
       <c r="E8">
         <v>-317.292</v>
@@ -1937,37 +2065,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M8">
-        <v>20.69869115102901</v>
+        <v>20.39421035102901</v>
       </c>
       <c r="N8">
-        <v>89.63464218230433</v>
+        <v>89.93912298230433</v>
       </c>
       <c r="O8">
-        <v>31.37212476380651</v>
+        <v>31.47869304380651</v>
       </c>
       <c r="P8">
-        <v>58.26251741849782</v>
+        <v>58.46042993849781</v>
       </c>
       <c r="Q8">
-        <v>143.2625174184978</v>
+        <v>143.4604299384978</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.2496270371348192</v>
+        <v>0.2496770542619144</v>
       </c>
       <c r="T8">
         <v>1.00172384760524</v>
       </c>
       <c r="U8">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.1148866793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.330449762657977</v>
+        <v>5.410032133348391</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2114,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.2415485070265964</v>
+        <v>0.2414770550399084</v>
       </c>
       <c r="C9">
-        <v>1903.115602937113</v>
+        <v>1904.295447763647</v>
       </c>
       <c r="D9">
-        <v>2028.441602937113</v>
+        <v>2029.621447763647</v>
       </c>
       <c r="E9">
         <v>-297.7739999999999</v>
@@ -2019,37 +2147,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M9">
-        <v>24.14847300953385</v>
+        <v>23.79324540953385</v>
       </c>
       <c r="N9">
-        <v>86.18486032379948</v>
+        <v>86.54008792379949</v>
       </c>
       <c r="O9">
-        <v>30.16470111332982</v>
+        <v>30.28903077332982</v>
       </c>
       <c r="P9">
-        <v>56.02015921046967</v>
+        <v>56.25105715046967</v>
       </c>
       <c r="Q9">
-        <v>141.0201592104697</v>
+        <v>141.2510571504697</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.2510821929789177</v>
+        <v>0.25113256718678</v>
       </c>
       <c r="T9">
         <v>1.008875324325433</v>
       </c>
       <c r="U9">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.1148866793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>4.56895693942112</v>
+        <v>4.637170400012906</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2196,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.241829998384003</v>
+        <v>0.2415958783111576</v>
       </c>
       <c r="C10">
-        <v>1880.684840681653</v>
+        <v>1883.545724900525</v>
       </c>
       <c r="D10">
-        <v>2025.528840681653</v>
+        <v>2028.389724900525</v>
       </c>
       <c r="E10">
         <v>-278.256</v>
@@ -2101,45 +2229,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M10">
-        <v>28.42581806803868</v>
+        <v>27.58264046803868</v>
       </c>
       <c r="N10">
-        <v>81.90751526529466</v>
+        <v>82.75069286529467</v>
       </c>
       <c r="O10">
-        <v>28.66763034285313</v>
+        <v>28.96274250285313</v>
       </c>
       <c r="P10">
-        <v>53.23988492244153</v>
+        <v>53.78795036244153</v>
       </c>
       <c r="Q10">
-        <v>138.2398849224415</v>
+        <v>138.7879503624415</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.2525689826457139</v>
+        <v>0.2526197216969688</v>
       </c>
       <c r="T10">
         <v>1.016182267930847</v>
       </c>
       <c r="U10">
-        <v>0.1820487374989669</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.1183316793743285</v>
+        <v>0.1148216793743285</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.881447952324353</v>
+        <v>4.000100478457885</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2278,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.2421452897414097</v>
+        <v>0.2419695015824068</v>
       </c>
       <c r="C11">
-        <v>1857.914245529072</v>
+        <v>1860.164465840006</v>
       </c>
       <c r="D11">
-        <v>2022.276245529072</v>
+        <v>2024.526465840006</v>
       </c>
       <c r="E11">
         <v>-258.7379999999999</v>
@@ -2183,37 +2311,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M11">
-        <v>32.80465672654352</v>
+        <v>32.13714112654352</v>
       </c>
       <c r="N11">
-        <v>77.52867660678982</v>
+        <v>78.19619220678982</v>
       </c>
       <c r="O11">
-        <v>27.13503681237643</v>
+        <v>27.36866727237643</v>
       </c>
       <c r="P11">
-        <v>50.39363979441338</v>
+        <v>50.82752493441338</v>
       </c>
       <c r="Q11">
-        <v>135.3936397944134</v>
+        <v>135.8275249344134</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.2540884490084837</v>
+        <v>0.2541395609216673</v>
       </c>
       <c r="T11">
         <v>1.023649803703414</v>
       </c>
       <c r="U11">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.1213866793743285</v>
+        <v>0.1189166793743285</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>3.363343632980569</v>
+        <v>3.433203124661392</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2360,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.2422161810988164</v>
+        <v>0.242015524853656</v>
       </c>
       <c r="C12">
-        <v>1837.666357047915</v>
+        <v>1840.171603666088</v>
       </c>
       <c r="D12">
-        <v>2021.546357047916</v>
+        <v>2024.051603666088</v>
       </c>
       <c r="E12">
         <v>-239.2199999999999</v>
@@ -2265,37 +2393,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M12">
-        <v>36.44961858504836</v>
+        <v>35.70793458504836</v>
       </c>
       <c r="N12">
-        <v>73.88371474828497</v>
+        <v>74.62539874828499</v>
       </c>
       <c r="O12">
-        <v>25.85930016189974</v>
+        <v>26.11888956189975</v>
       </c>
       <c r="P12">
-        <v>48.02441458638523</v>
+        <v>48.50650918638524</v>
       </c>
       <c r="Q12">
-        <v>133.0244145863852</v>
+        <v>133.5065091863852</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.2556416812904261</v>
+        <v>0.2556931743513591</v>
       </c>
       <c r="T12">
         <v>1.031283284715371</v>
       </c>
       <c r="U12">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.1213866793743285</v>
+        <v>0.1189166793743285</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>3.027009269682511</v>
+        <v>3.089882812195253</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2442,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.2429520224562231</v>
+        <v>0.2426192481249053</v>
       </c>
       <c r="C13">
-        <v>1810.603228182899</v>
+        <v>1814.445028707164</v>
       </c>
       <c r="D13">
-        <v>2014.001228182899</v>
+        <v>2017.843028707164</v>
       </c>
       <c r="E13">
         <v>-219.702</v>
@@ -2347,37 +2475,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M13">
-        <v>42.09127184355319</v>
+        <v>40.95337244355319</v>
       </c>
       <c r="N13">
-        <v>68.24206148978016</v>
+        <v>69.37996088978015</v>
       </c>
       <c r="O13">
-        <v>23.88472152142305</v>
+        <v>24.28298631142305</v>
       </c>
       <c r="P13">
-        <v>44.3573399683571</v>
+        <v>45.0969745783571</v>
       </c>
       <c r="Q13">
-        <v>129.3573399683571</v>
+        <v>130.0969745783571</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.2572298176685921</v>
+        <v>0.2572817004423923</v>
       </c>
       <c r="T13">
         <v>1.039088304626473</v>
       </c>
       <c r="U13">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.1274316793743284</v>
+        <v>0.1239866793743285</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.621287704097549</v>
+        <v>2.694120819607906</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2524,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.2434499638136297</v>
+        <v>0.2430201713961544</v>
       </c>
       <c r="C14">
-        <v>1786.011336510824</v>
+        <v>1790.825013065409</v>
       </c>
       <c r="D14">
-        <v>2008.927336510824</v>
+        <v>2013.741013065409</v>
       </c>
       <c r="E14">
         <v>-200.184</v>
@@ -2429,37 +2557,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M14">
-        <v>47.01856630205802</v>
+        <v>45.58984870205802</v>
       </c>
       <c r="N14">
-        <v>63.31476703127532</v>
+        <v>64.74348463127532</v>
       </c>
       <c r="O14">
-        <v>22.16016846094636</v>
+        <v>22.66021962094636</v>
       </c>
       <c r="P14">
-        <v>41.15459857032896</v>
+        <v>42.08326501032896</v>
       </c>
       <c r="Q14">
-        <v>126.154598570329</v>
+        <v>127.083265010329</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.2588540480553526</v>
+        <v>0.2589063293991307</v>
       </c>
       <c r="T14">
         <v>1.047070711353736</v>
       </c>
       <c r="U14">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.1304866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.346590762136956</v>
+        <v>2.420129403244821</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2606,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.2436118551710364</v>
+        <v>0.2431422446674037</v>
       </c>
       <c r="C15">
-        <v>1764.849208694734</v>
+        <v>1770.061339827385</v>
       </c>
       <c r="D15">
-        <v>2007.283208694734</v>
+        <v>2012.495339827386</v>
       </c>
       <c r="E15">
         <v>-180.6659999999999</v>
@@ -2511,37 +2639,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M15">
-        <v>50.93678016056286</v>
+        <v>49.38900276056286</v>
       </c>
       <c r="N15">
-        <v>59.39655317277048</v>
+        <v>60.94433057277048</v>
       </c>
       <c r="O15">
-        <v>20.78879361046967</v>
+        <v>21.33051570046967</v>
       </c>
       <c r="P15">
-        <v>38.60775956230081</v>
+        <v>39.61381487230081</v>
       </c>
       <c r="Q15">
-        <v>123.6077595623008</v>
+        <v>124.6138148723008</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.2605156170716939</v>
+        <v>0.2605683061479781</v>
       </c>
       <c r="T15">
         <v>1.055236621683925</v>
       </c>
       <c r="U15">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.1304866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>2.166083780434113</v>
+        <v>2.233965602995219</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2688,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.2437737465284431</v>
+        <v>0.2432643179386529</v>
       </c>
       <c r="C16">
-        <v>1743.689769821885</v>
+        <v>1749.299206750225</v>
       </c>
       <c r="D16">
-        <v>2005.641769821886</v>
+        <v>2011.251206750225</v>
       </c>
       <c r="E16">
         <v>-161.1479999999999</v>
@@ -2593,37 +2721,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M16">
-        <v>54.8549940190677</v>
+        <v>53.18815681906771</v>
       </c>
       <c r="N16">
-        <v>55.47833931426564</v>
+        <v>57.14517651426564</v>
       </c>
       <c r="O16">
-        <v>19.41741875999297</v>
+        <v>20.00081177999297</v>
       </c>
       <c r="P16">
-        <v>36.06092055427267</v>
+        <v>37.14436473427266</v>
       </c>
       <c r="Q16">
-        <v>121.0609205542727</v>
+        <v>122.1443647342727</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.2622158272279501</v>
+        <v>0.2622689335188917</v>
       </c>
       <c r="T16">
         <v>1.063592436905514</v>
       </c>
       <c r="U16">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.1304866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.011363510403105</v>
+        <v>2.074396631352703</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2770,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.2455248878858497</v>
+        <v>0.2447708912099021</v>
       </c>
       <c r="C17">
-        <v>1706.586769332189</v>
+        <v>1714.552359498086</v>
       </c>
       <c r="D17">
-        <v>1988.056769332189</v>
+        <v>1996.022359498086</v>
       </c>
       <c r="E17">
         <v>-141.6299999999999</v>
@@ -2675,37 +2803,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M17">
-        <v>63.54535887757254</v>
+        <v>61.14464487757254</v>
       </c>
       <c r="N17">
-        <v>46.7879744557608</v>
+        <v>49.1886884557608</v>
       </c>
       <c r="O17">
-        <v>16.37579105951628</v>
+        <v>17.21604095951628</v>
       </c>
       <c r="P17">
-        <v>30.41218339624452</v>
+        <v>31.97264749624452</v>
       </c>
       <c r="Q17">
-        <v>115.4121833962445</v>
+        <v>116.9726474962445</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.2639560423290593</v>
+        <v>0.2640095756514739</v>
       </c>
       <c r="T17">
         <v>1.072144859544081</v>
       </c>
       <c r="U17">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.1410816793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>1.736292552000583</v>
+        <v>1.804464373850716</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2852,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.2457927292432563</v>
+        <v>0.2449852644811513</v>
       </c>
       <c r="C18">
-        <v>1684.406253421164</v>
+        <v>1692.886139127433</v>
       </c>
       <c r="D18">
-        <v>1985.394253421164</v>
+        <v>1993.874139127433</v>
       </c>
       <c r="E18">
         <v>-122.112</v>
@@ -2757,37 +2885,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M18">
-        <v>67.78171613607736</v>
+        <v>65.22095453607737</v>
       </c>
       <c r="N18">
-        <v>42.55161719725598</v>
+        <v>45.11237879725597</v>
       </c>
       <c r="O18">
-        <v>14.89306601903959</v>
+        <v>15.78933257903959</v>
       </c>
       <c r="P18">
-        <v>27.65855117821638</v>
+        <v>29.32304621821638</v>
       </c>
       <c r="Q18">
-        <v>112.6585511782164</v>
+        <v>114.3230462182164</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.2657376911230521</v>
+        <v>0.2657916616443556</v>
       </c>
       <c r="T18">
         <v>1.08090091129309</v>
       </c>
       <c r="U18">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.1410816793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>1.627774267500547</v>
+        <v>1.691685350485047</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2934,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.246060570600663</v>
+        <v>0.2451996377524005</v>
       </c>
       <c r="C19">
-        <v>1662.232859549925</v>
+        <v>1671.224537832657</v>
       </c>
       <c r="D19">
-        <v>1982.738859549925</v>
+        <v>1991.730537832658</v>
       </c>
       <c r="E19">
         <v>-102.5939999999999</v>
@@ -2839,37 +2967,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M19">
-        <v>72.0180733945822</v>
+        <v>69.29726419458221</v>
       </c>
       <c r="N19">
-        <v>38.31525993875114</v>
+        <v>41.03606913875113</v>
       </c>
       <c r="O19">
-        <v>13.4103409785629</v>
+        <v>14.36262419856289</v>
       </c>
       <c r="P19">
-        <v>24.90491896018824</v>
+        <v>26.67344494018824</v>
       </c>
       <c r="Q19">
-        <v>109.9049189601882</v>
+        <v>111.6734449401882</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.2675622712132857</v>
+        <v>0.2676166894683911</v>
       </c>
       <c r="T19">
         <v>1.089867952240871</v>
       </c>
       <c r="U19">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.1410816793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.532022840000515</v>
+        <v>1.592174447515338</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +3016,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.2501543119580697</v>
+        <v>0.2454140110236497</v>
       </c>
       <c r="C20">
-        <v>1602.995511362438</v>
+        <v>1649.56754073194</v>
       </c>
       <c r="D20">
-        <v>1943.019511362438</v>
+        <v>1989.59154073194</v>
       </c>
       <c r="E20">
         <v>-83.07599999999996</v>
@@ -2921,45 +3049,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M20">
-        <v>87.74272545308703</v>
+        <v>73.37357385308704</v>
       </c>
       <c r="N20">
-        <v>22.59060788024631</v>
+        <v>36.9597594802463</v>
       </c>
       <c r="O20">
-        <v>7.906712758086208</v>
+        <v>12.93591581808621</v>
       </c>
       <c r="P20">
-        <v>14.6838951221601</v>
+        <v>24.0238436621601</v>
       </c>
       <c r="Q20">
-        <v>99.6838951221601</v>
+        <v>109.0238436621601</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.2694313532569397</v>
+        <v>0.2694862301661836</v>
       </c>
       <c r="T20">
         <v>1.099053701504451</v>
       </c>
       <c r="U20">
-        <v>0.2497487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.1623366793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.257464168836706</v>
+        <v>1.503720311542264</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3098,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.2546731533154764</v>
+        <v>0.249160484294899</v>
       </c>
       <c r="C21">
-        <v>1541.441487168696</v>
+        <v>1593.395657093235</v>
       </c>
       <c r="D21">
-        <v>1900.983487168696</v>
+        <v>1952.937657093235</v>
       </c>
       <c r="E21">
         <v>-63.55799999999994</v>
@@ -3003,45 +3131,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M21">
-        <v>104.7438547115919</v>
+        <v>88.05596471159188</v>
       </c>
       <c r="N21">
-        <v>5.589478621741463</v>
+        <v>22.27736862174146</v>
       </c>
       <c r="O21">
-        <v>1.956317517609512</v>
+        <v>7.79707901760951</v>
       </c>
       <c r="P21">
-        <v>3.633161104131951</v>
+        <v>14.48028960413195</v>
       </c>
       <c r="Q21">
-        <v>88.63316110413196</v>
+        <v>99.48028960413195</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.271346585474511</v>
+        <v>0.2714019323626871</v>
       </c>
       <c r="T21">
         <v>1.108466259391824</v>
       </c>
       <c r="U21">
-        <v>0.2824487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V21">
         <v>0.35</v>
       </c>
       <c r="W21">
-        <v>0.1835916793743285</v>
+        <v>0.1543416793743285</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.053363308397728</v>
+        <v>1.25299102331916</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3180,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.255366094672883</v>
+        <v>0.2532267575661482</v>
       </c>
       <c r="C22">
-        <v>1515.637784893896</v>
+        <v>1535.593405395757</v>
       </c>
       <c r="D22">
-        <v>1894.697784893896</v>
+        <v>1914.653405395757</v>
       </c>
       <c r="E22">
         <v>-44.03999999999991</v>
@@ -3085,37 +3213,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M22">
-        <v>110.2566891700967</v>
+        <v>103.6986411700967</v>
       </c>
       <c r="N22">
-        <v>0.07664416323660816</v>
+        <v>6.634692163236636</v>
       </c>
       <c r="O22">
-        <v>0.02682545713281285</v>
+        <v>2.322142257132823</v>
       </c>
       <c r="P22">
-        <v>0.04981870610379531</v>
+        <v>4.312549906103813</v>
       </c>
       <c r="Q22">
-        <v>85.04981870610379</v>
+        <v>89.31254990610381</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.2733096984975216</v>
+        <v>0.2733655271141031</v>
       </c>
       <c r="T22">
         <v>1.11811413122638</v>
       </c>
       <c r="U22">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.1835916793743285</v>
+        <v>0.1726716793743285</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>1.000695142977841</v>
+        <v>1.063980512072032</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3262,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.2577093149726283</v>
+        <v>0.2538103308373973</v>
       </c>
       <c r="C23">
-        <v>1475.16886863984</v>
+        <v>1510.703842615211</v>
       </c>
       <c r="D23">
-        <v>1873.74686863984</v>
+        <v>1909.281842615211</v>
       </c>
       <c r="E23">
         <v>-24.52199999999993</v>
@@ -3167,37 +3295,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M23">
-        <v>115.7695236286016</v>
+        <v>108.8835732286015</v>
       </c>
       <c r="N23">
-        <v>-5.436190295268219</v>
+        <v>1.449760104731808</v>
       </c>
       <c r="O23">
-        <v>-1.902666603343876</v>
+        <v>0.507416036656133</v>
       </c>
       <c r="P23">
-        <v>-3.533523691924342</v>
+        <v>0.9423440680756755</v>
       </c>
       <c r="Q23">
-        <v>81.46647630807566</v>
+        <v>85.94234406807567</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.2761775135199064</v>
+        <v>0.2753788331250486</v>
       </c>
       <c r="T23">
-        <v>1.132208231493084</v>
+        <v>1.128006252980799</v>
       </c>
       <c r="U23">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V23">
-        <v>0.3335650476592804</v>
+        <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.1882337109138204</v>
+        <v>0.1726716793743285</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.9530429933122297</v>
+        <v>1.013314773401935</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3344,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.260075802347618</v>
+        <v>0.2555572716899343</v>
       </c>
       <c r="C24">
-        <v>1434.956985989623</v>
+        <v>1475.284594362888</v>
       </c>
       <c r="D24">
-        <v>1853.052985989623</v>
+        <v>1893.380594362888</v>
       </c>
       <c r="E24">
         <v>-5.003999999999962</v>
@@ -3249,37 +3377,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M24">
-        <v>121.2823580871064</v>
+        <v>114.0685052871064</v>
       </c>
       <c r="N24">
-        <v>-10.94902475377305</v>
+        <v>-3.735171953773019</v>
       </c>
       <c r="O24">
-        <v>-3.832158663820566</v>
+        <v>-1.307310183820557</v>
       </c>
       <c r="P24">
-        <v>-7.116866089952479</v>
+        <v>-2.427861769952463</v>
       </c>
       <c r="Q24">
-        <v>77.88313391004752</v>
+        <v>82.57213823004754</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.2791310713855462</v>
+        <v>0.2780765449013363</v>
       </c>
       <c r="T24">
-        <v>1.146723721640431</v>
+        <v>1.141261114986021</v>
       </c>
       <c r="U24">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V24">
-        <v>0.318403000038404</v>
+        <v>0.338539253841101</v>
       </c>
       <c r="W24">
-        <v>0.1925162121222362</v>
+        <v>0.1757162121222361</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.9097228572525831</v>
+        <v>0.9672550109745742</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3426,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.2624422897226076</v>
+        <v>0.2577557590649239</v>
       </c>
       <c r="C25">
-        <v>1395.197201700202</v>
+        <v>1436.127716178493</v>
       </c>
       <c r="D25">
-        <v>1832.811201700202</v>
+        <v>1873.741716178493</v>
       </c>
       <c r="E25">
         <v>14.51400000000007</v>
@@ -3331,37 +3459,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M25">
-        <v>126.7951925456112</v>
+        <v>119.2534373456112</v>
       </c>
       <c r="N25">
-        <v>-16.46185921227789</v>
+        <v>-8.920104012277861</v>
       </c>
       <c r="O25">
-        <v>-5.76165072429726</v>
+        <v>-3.122036404297251</v>
       </c>
       <c r="P25">
-        <v>-10.70020848798063</v>
+        <v>-5.798067607980609</v>
       </c>
       <c r="Q25">
-        <v>74.29979151201937</v>
+        <v>79.20193239201939</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.2821613450399039</v>
+        <v>0.2810931234065485</v>
       </c>
       <c r="T25">
-        <v>1.161616237505891</v>
+        <v>1.156082687907918</v>
       </c>
       <c r="U25">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V25">
-        <v>0.3045593913410821</v>
+        <v>0.3238201558480096</v>
       </c>
       <c r="W25">
-        <v>0.1964263219212244</v>
+        <v>0.1796263219212244</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.870169689545949</v>
+        <v>0.9252004452800274</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3508,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.2648087770975973</v>
+        <v>0.2599542464399135</v>
       </c>
       <c r="C26">
-        <v>1355.874860399167</v>
+        <v>1397.374059750986</v>
       </c>
       <c r="D26">
-        <v>1813.006860399167</v>
+        <v>1854.506059750986</v>
       </c>
       <c r="E26">
         <v>34.03200000000004</v>
@@ -3413,37 +3541,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M26">
-        <v>132.308027004116</v>
+        <v>124.438369404116</v>
       </c>
       <c r="N26">
-        <v>-21.9746936707827</v>
+        <v>-14.10503607078269</v>
       </c>
       <c r="O26">
-        <v>-7.691142784773944</v>
+        <v>-4.936762624773941</v>
       </c>
       <c r="P26">
-        <v>-14.28355088600875</v>
+        <v>-9.168273446008747</v>
       </c>
       <c r="Q26">
-        <v>70.71644911399125</v>
+        <v>75.83172655399125</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.2852713627377974</v>
+        <v>0.2841890855566346</v>
       </c>
       <c r="T26">
-        <v>1.1769006616836</v>
+        <v>1.171294302222495</v>
       </c>
       <c r="U26">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V26">
-        <v>0.2918694167018704</v>
+        <v>0.3103276493543425</v>
       </c>
       <c r="W26">
-        <v>0.2000105892369637</v>
+        <v>0.1832105892369637</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8339126191482013</v>
+        <v>0.886650426726693</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3590,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.267175264472587</v>
+        <v>0.2621527338149032</v>
       </c>
       <c r="C27">
-        <v>1316.975933374072</v>
+        <v>1359.011332960094</v>
       </c>
       <c r="D27">
-        <v>1793.625933374072</v>
+        <v>1835.661332960094</v>
       </c>
       <c r="E27">
         <v>53.55000000000007</v>
@@ -3495,37 +3623,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M27">
-        <v>137.8208614626209</v>
+        <v>129.6233014626209</v>
       </c>
       <c r="N27">
-        <v>-27.48752812928757</v>
+        <v>-19.28996812928753</v>
       </c>
       <c r="O27">
-        <v>-9.620634845250649</v>
+        <v>-6.751488845250635</v>
       </c>
       <c r="P27">
-        <v>-17.86689328403692</v>
+        <v>-12.5384792840369</v>
       </c>
       <c r="Q27">
-        <v>67.13310671596308</v>
+        <v>72.4615207159631</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.288464314240968</v>
+        <v>0.2873676066973898</v>
       </c>
       <c r="T27">
-        <v>1.192592670506049</v>
+        <v>1.186911559585462</v>
       </c>
       <c r="U27">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V27">
-        <v>0.2801946400337955</v>
+        <v>0.2979145433801688</v>
       </c>
       <c r="W27">
-        <v>0.2033081151674438</v>
+        <v>0.1865081151674438</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.800556114382273</v>
+        <v>0.8511844096576253</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3672,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.2852521476700328</v>
+        <v>0.2643512211898929</v>
       </c>
       <c r="C28">
-        <v>1162.052313449575</v>
+        <v>1321.027738289438</v>
       </c>
       <c r="D28">
-        <v>1658.220313449576</v>
+        <v>1817.195738289438</v>
       </c>
       <c r="E28">
         <v>73.0680000000001</v>
@@ -3577,45 +3705,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M28">
-        <v>169.8235255211258</v>
+        <v>134.8082335211257</v>
       </c>
       <c r="N28">
-        <v>-59.49019218779242</v>
+        <v>-24.47490018779237</v>
       </c>
       <c r="O28">
-        <v>-20.82156726572735</v>
+        <v>-8.566215065727329</v>
       </c>
       <c r="P28">
-        <v>-38.66862492206507</v>
+        <v>-15.90868512206504</v>
       </c>
       <c r="Q28">
-        <v>46.33137507793493</v>
+        <v>69.09131487793496</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.2946332858151111</v>
+        <v>0.290632033814922</v>
       </c>
       <c r="T28">
-        <v>1.222910561733259</v>
+        <v>1.202950904985266</v>
       </c>
       <c r="U28">
-        <v>0.3346487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V28">
-        <v>0.2273929159588836</v>
+        <v>0.2864562917117008</v>
       </c>
       <c r="W28">
-        <v>0.2585519852571178</v>
+        <v>0.1895519852571177</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.6496940455968102</v>
+        <v>0.8184465477477165</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3754,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.2881406350450226</v>
+        <v>0.2835927175244632</v>
       </c>
       <c r="C29">
-        <v>1122.769784733783</v>
+        <v>1154.467534888503</v>
       </c>
       <c r="D29">
-        <v>1638.455784733783</v>
+        <v>1670.153534888504</v>
       </c>
       <c r="E29">
         <v>92.58600000000013</v>
@@ -3659,37 +3787,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M29">
-        <v>176.3551995796306</v>
+        <v>168.4504095796306</v>
       </c>
       <c r="N29">
-        <v>-66.02186624629726</v>
+        <v>-58.11707624629724</v>
       </c>
       <c r="O29">
-        <v>-23.10765318620404</v>
+        <v>-20.34097668620403</v>
       </c>
       <c r="P29">
-        <v>-42.91421306009322</v>
+        <v>-37.77609956009321</v>
       </c>
       <c r="Q29">
-        <v>42.08578693990678</v>
+        <v>47.22390043990679</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.2980419609632634</v>
+        <v>0.2973598821679765</v>
       </c>
       <c r="T29">
-        <v>1.239662761209057</v>
+        <v>1.236007327949217</v>
       </c>
       <c r="U29">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V29">
-        <v>0.2189709561085545</v>
+        <v>0.229246499091542</v>
       </c>
       <c r="W29">
-        <v>0.2613703834882974</v>
+        <v>0.2463703834882974</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.6256313031672986</v>
+        <v>0.6549899974044059</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3836,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.2910291224200122</v>
+        <v>0.2863312048994528</v>
       </c>
       <c r="C30">
-        <v>1083.952858072958</v>
+        <v>1115.934561877005</v>
       </c>
       <c r="D30">
-        <v>1619.156858072958</v>
+        <v>1651.138561877005</v>
       </c>
       <c r="E30">
         <v>112.1040000000002</v>
@@ -3741,37 +3869,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M30">
-        <v>182.8868736381355</v>
+        <v>174.6893136381354</v>
       </c>
       <c r="N30">
-        <v>-72.55354030480211</v>
+        <v>-64.3559803048021</v>
       </c>
       <c r="O30">
-        <v>-25.39373910668074</v>
+        <v>-22.52459310668073</v>
       </c>
       <c r="P30">
-        <v>-47.15980119812137</v>
+        <v>-41.83138719812137</v>
       </c>
       <c r="Q30">
-        <v>37.84019880187863</v>
+        <v>43.16861280187863</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.3015453215321976</v>
+        <v>0.3008537694203095</v>
       </c>
       <c r="T30">
-        <v>1.256880299559183</v>
+        <v>1.253174096392956</v>
       </c>
       <c r="U30">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V30">
-        <v>0.2111505648189633</v>
+        <v>0.2210591241239869</v>
       </c>
       <c r="W30">
-        <v>0.263987467560107</v>
+        <v>0.248987467560107</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.6032873280541808</v>
+        <v>0.6315974974971056</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3918,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.2939176097950019</v>
+        <v>0.2890696922744425</v>
       </c>
       <c r="C31">
-        <v>1045.585272400519</v>
+        <v>1077.829692038086</v>
       </c>
       <c r="D31">
-        <v>1600.30727240052</v>
+        <v>1632.551692038086</v>
       </c>
       <c r="E31">
         <v>131.6220000000001</v>
@@ -3823,37 +3951,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M31">
-        <v>189.4185476966402</v>
+        <v>180.9282176966402</v>
       </c>
       <c r="N31">
-        <v>-79.0852143633069</v>
+        <v>-70.5948843633069</v>
       </c>
       <c r="O31">
-        <v>-27.67982502715741</v>
+        <v>-24.70820952715741</v>
       </c>
       <c r="P31">
-        <v>-51.40538933614949</v>
+        <v>-45.88667483614949</v>
       </c>
       <c r="Q31">
-        <v>33.59461066385051</v>
+        <v>39.11332516385051</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.3051473683143412</v>
+        <v>0.3044460760318632</v>
       </c>
       <c r="T31">
-        <v>1.274582838989594</v>
+        <v>1.270824435778772</v>
       </c>
       <c r="U31">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V31">
-        <v>0.2038695108596887</v>
+        <v>0.2134363957059185</v>
       </c>
       <c r="W31">
-        <v>0.2664240630752401</v>
+        <v>0.2514240630752401</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5824843167419679</v>
+        <v>0.6098182734454813</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +4000,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.2968060971699916</v>
+        <v>0.2918081796494322</v>
       </c>
       <c r="C32">
-        <v>1007.651515155776</v>
+        <v>1040.138628833296</v>
       </c>
       <c r="D32">
-        <v>1581.891515155776</v>
+        <v>1614.378628833297</v>
       </c>
       <c r="E32">
         <v>151.1400000000001</v>
@@ -3905,37 +4033,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M32">
-        <v>195.9502217551451</v>
+        <v>187.1671217551451</v>
       </c>
       <c r="N32">
-        <v>-85.61688842181175</v>
+        <v>-76.83378842181176</v>
       </c>
       <c r="O32">
-        <v>-29.96591094763411</v>
+        <v>-26.89182594763411</v>
       </c>
       <c r="P32">
-        <v>-55.65097747417764</v>
+        <v>-49.94196247417764</v>
       </c>
       <c r="Q32">
-        <v>29.34902252582236</v>
+        <v>35.05803752582236</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.3088523307188318</v>
+        <v>0.3081410199751755</v>
       </c>
       <c r="T32">
-        <v>1.292791165260874</v>
+        <v>1.288979070575612</v>
       </c>
       <c r="U32">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V32">
-        <v>0.1970738604976991</v>
+        <v>0.2063218491823878</v>
       </c>
       <c r="W32">
-        <v>0.2686982188893643</v>
+        <v>0.2536982188893643</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5630681728505689</v>
+        <v>0.5894909976639653</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4082,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.2996945845449812</v>
+        <v>0.2945466670244218</v>
       </c>
       <c r="C33">
-        <v>970.1367797062209</v>
+        <v>1002.847705294671</v>
       </c>
       <c r="D33">
-        <v>1563.894779706221</v>
+        <v>1596.605705294671</v>
       </c>
       <c r="E33">
         <v>170.6580000000001</v>
@@ -3987,37 +4115,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M33">
-        <v>202.4818958136499</v>
+        <v>193.4060258136499</v>
       </c>
       <c r="N33">
-        <v>-92.1485624803166</v>
+        <v>-83.07269248031659</v>
       </c>
       <c r="O33">
-        <v>-32.25199686811081</v>
+        <v>-29.0754423681108</v>
       </c>
       <c r="P33">
-        <v>-59.89656561220579</v>
+        <v>-53.99725011220579</v>
       </c>
       <c r="Q33">
-        <v>25.10343438779421</v>
+        <v>31.00274988779421</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.3126646833379453</v>
+        <v>0.3119430637429317</v>
       </c>
       <c r="T33">
-        <v>1.311527269105234</v>
+        <v>1.307659926670911</v>
       </c>
       <c r="U33">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V33">
-        <v>0.1907166391913217</v>
+        <v>0.1996663056603753</v>
       </c>
       <c r="W33">
-        <v>0.2708256549735451</v>
+        <v>0.2558256549735451</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5449046834037763</v>
+        <v>0.5704751590296437</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4164,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.3025830719199709</v>
+        <v>0.2972851543994115</v>
       </c>
       <c r="C34">
-        <v>933.0269256434983</v>
+        <v>965.9438497469439</v>
       </c>
       <c r="D34">
-        <v>1546.302925643498</v>
+        <v>1579.219849746944</v>
       </c>
       <c r="E34">
         <v>190.176</v>
@@ -4069,37 +4197,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M34">
-        <v>209.0135698721548</v>
+        <v>199.6449298721547</v>
       </c>
       <c r="N34">
-        <v>-98.68023653882142</v>
+        <v>-89.31159653882139</v>
       </c>
       <c r="O34">
-        <v>-34.5380827885875</v>
+        <v>-31.25905878858748</v>
       </c>
       <c r="P34">
-        <v>-64.14215375023392</v>
+        <v>-58.05253775023391</v>
       </c>
       <c r="Q34">
-        <v>20.85784624976608</v>
+        <v>26.94746224976609</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.316589163975268</v>
+        <v>0.3158569323273865</v>
       </c>
       <c r="T34">
-        <v>1.33081443482737</v>
+        <v>1.326890219710189</v>
       </c>
       <c r="U34">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V34">
-        <v>0.1847567442165929</v>
+        <v>0.1934267336084886</v>
       </c>
       <c r="W34">
-        <v>0.2728201263024645</v>
+        <v>0.2578201263024645</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5278764120474084</v>
+        <v>0.5526478103099676</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4246,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.3054715592949606</v>
+        <v>0.3000236417744012</v>
       </c>
       <c r="C35">
-        <v>896.3084417292882</v>
+        <v>929.4145537452023</v>
       </c>
       <c r="D35">
-        <v>1529.102441729288</v>
+        <v>1562.208553745202</v>
       </c>
       <c r="E35">
         <v>209.6940000000001</v>
@@ -4151,37 +4279,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M35">
-        <v>215.5452439306596</v>
+        <v>205.8838339306596</v>
       </c>
       <c r="N35">
-        <v>-105.2119105973263</v>
+        <v>-95.55050059732625</v>
       </c>
       <c r="O35">
-        <v>-36.82416870906419</v>
+        <v>-33.44267520906418</v>
       </c>
       <c r="P35">
-        <v>-68.38774188826207</v>
+        <v>-62.10782538826206</v>
       </c>
       <c r="Q35">
-        <v>16.61225811173793</v>
+        <v>22.89217461173794</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.3206307932883317</v>
+        <v>0.3198876328098849</v>
       </c>
       <c r="T35">
-        <v>1.350677336839719</v>
+        <v>1.346694551347654</v>
       </c>
       <c r="U35">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V35">
-        <v>0.1791580549979083</v>
+        <v>0.1875653174385344</v>
       </c>
       <c r="W35">
-        <v>0.2746937205811464</v>
+        <v>0.2596937205811464</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5118801571368807</v>
+        <v>0.5359009069672411</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4328,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.3195119739494133</v>
+        <v>0.3027621291493908</v>
       </c>
       <c r="C36">
-        <v>798.3531266888319</v>
+        <v>893.2478420626921</v>
       </c>
       <c r="D36">
-        <v>1450.665126688832</v>
+        <v>1545.559842062692</v>
       </c>
       <c r="E36">
         <v>229.2120000000001</v>
@@ -4233,45 +4361,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M36">
-        <v>241.9852779891644</v>
+        <v>212.1227379891644</v>
       </c>
       <c r="N36">
-        <v>-131.6519446558311</v>
+        <v>-101.7894046558311</v>
       </c>
       <c r="O36">
-        <v>-46.07818062954088</v>
+        <v>-35.62629162954089</v>
       </c>
       <c r="P36">
-        <v>-85.57376402629022</v>
+        <v>-66.16311302629022</v>
       </c>
       <c r="Q36">
-        <v>-0.5737640262902204</v>
+        <v>18.83688697370978</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.3262372102767354</v>
+        <v>0.3240404757312468</v>
       </c>
       <c r="T36">
-        <v>1.378230509744785</v>
+        <v>1.367099014246861</v>
       </c>
       <c r="U36">
-        <v>0.3646487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V36">
-        <v>0.1595827109300254</v>
+        <v>0.1820486904550481</v>
       </c>
       <c r="W36">
-        <v>0.3064571034316705</v>
+        <v>0.2614571034316706</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.4559506026572154</v>
+        <v>0.5201391155858517</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4410,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.322700461324403</v>
+        <v>0.3055006165243805</v>
       </c>
       <c r="C37">
-        <v>762.1308300630262</v>
+        <v>857.4322445774646</v>
       </c>
       <c r="D37">
-        <v>1433.960830063026</v>
+        <v>1529.262244577465</v>
       </c>
       <c r="E37">
         <v>248.7300000000001</v>
@@ -4315,45 +4443,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M37">
-        <v>249.1024920476693</v>
+        <v>218.3616420476693</v>
       </c>
       <c r="N37">
-        <v>-138.7691587143359</v>
+        <v>-108.0283087143359</v>
       </c>
       <c r="O37">
-        <v>-48.56920555001757</v>
+        <v>-37.80990805001758</v>
       </c>
       <c r="P37">
-        <v>-90.19995316431836</v>
+        <v>-70.21840066431835</v>
       </c>
       <c r="Q37">
-        <v>-5.199953164318359</v>
+        <v>14.78159933568165</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.3305516288963775</v>
+        <v>0.3283210984348044</v>
       </c>
       <c r="T37">
-        <v>1.399434056048551</v>
+        <v>1.388131306773736</v>
       </c>
       <c r="U37">
-        <v>0.3646487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V37">
-        <v>0.1550232049034533</v>
+        <v>0.1768472992991896</v>
       </c>
       <c r="W37">
-        <v>0.308119721547879</v>
+        <v>0.263119721547879</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.442923442581295</v>
+        <v>0.5052779979976845</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4492,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.3258889486993927</v>
+        <v>0.322034879298261</v>
       </c>
       <c r="C38">
-        <v>726.2888514693806</v>
+        <v>746.3790124364267</v>
       </c>
       <c r="D38">
-        <v>1417.636851469381</v>
+        <v>1437.727012436427</v>
       </c>
       <c r="E38">
         <v>268.248</v>
@@ -4397,37 +4525,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M38">
-        <v>256.2197061061741</v>
+        <v>249.1932261061741</v>
       </c>
       <c r="N38">
-        <v>-145.8863727728408</v>
+        <v>-138.8598927728407</v>
       </c>
       <c r="O38">
-        <v>-51.06023047049426</v>
+        <v>-48.60096247049425</v>
       </c>
       <c r="P38">
-        <v>-94.8261423023465</v>
+        <v>-90.25893030234649</v>
       </c>
       <c r="Q38">
-        <v>-9.826142302346497</v>
+        <v>-5.258930302346485</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.3350008730978833</v>
+        <v>0.3346038896586151</v>
       </c>
       <c r="T38">
-        <v>1.42130021317431</v>
+        <v>1.419000998418048</v>
       </c>
       <c r="U38">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V38">
-        <v>0.1507170047672462</v>
+        <v>0.1549667592096312</v>
       </c>
       <c r="W38">
-        <v>0.3096899719909648</v>
+        <v>0.2996899719909648</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4306200136207036</v>
+        <v>0.4427621691703749</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4574,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.3290774360743823</v>
+        <v>0.3251233666732506</v>
       </c>
       <c r="C39">
-        <v>690.8143486646769</v>
+        <v>710.9640190001923</v>
       </c>
       <c r="D39">
-        <v>1401.680348664677</v>
+        <v>1421.830019000192</v>
       </c>
       <c r="E39">
         <v>287.7660000000001</v>
@@ -4479,37 +4607,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M39">
-        <v>263.3369201646789</v>
+        <v>256.1152601646789</v>
       </c>
       <c r="N39">
-        <v>-153.0035868313456</v>
+        <v>-145.7819268313456</v>
       </c>
       <c r="O39">
-        <v>-53.55125539097095</v>
+        <v>-51.02367439097096</v>
       </c>
       <c r="P39">
-        <v>-99.45233144037464</v>
+        <v>-94.75825244037463</v>
       </c>
       <c r="Q39">
-        <v>-14.45233144037464</v>
+        <v>-9.758252440374633</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.3395913631470561</v>
+        <v>0.339188078383355</v>
       </c>
       <c r="T39">
-        <v>1.443860534018346</v>
+        <v>1.441524823789764</v>
       </c>
       <c r="U39">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V39">
-        <v>0.1466435722059693</v>
+        <v>0.1507784684201817</v>
       </c>
       <c r="W39">
-        <v>0.3111753440317215</v>
+        <v>0.3011753440317216</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.418981634874198</v>
+        <v>0.430795624057662</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4656,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.3322659234493719</v>
+        <v>0.3282118540482403</v>
       </c>
       <c r="C40">
-        <v>655.6950511641793</v>
+        <v>675.8967281325598</v>
       </c>
       <c r="D40">
-        <v>1386.079051164179</v>
+        <v>1406.28072813256</v>
       </c>
       <c r="E40">
         <v>307.2840000000001</v>
@@ -4561,37 +4689,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M40">
-        <v>270.4541342231838</v>
+        <v>263.0372942231838</v>
       </c>
       <c r="N40">
-        <v>-160.1208008898504</v>
+        <v>-152.7039608898504</v>
       </c>
       <c r="O40">
-        <v>-56.04228031144764</v>
+        <v>-53.44638631144765</v>
       </c>
       <c r="P40">
-        <v>-104.0785205784028</v>
+        <v>-99.2575745784028</v>
       </c>
       <c r="Q40">
-        <v>-19.07852057840277</v>
+        <v>-14.2575745784028</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.3443299335203956</v>
+        <v>0.3439201441637317</v>
       </c>
       <c r="T40">
-        <v>1.467148607147674</v>
+        <v>1.46477522417347</v>
       </c>
       <c r="U40">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V40">
-        <v>0.142784530832128</v>
+        <v>0.1468106139880717</v>
       </c>
       <c r="W40">
-        <v>0.3125825385966491</v>
+        <v>0.3025825385966491</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4079558023775086</v>
+        <v>0.4194588971087763</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4738,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.3354544108243617</v>
+        <v>0.33130034142323</v>
       </c>
       <c r="C41">
-        <v>620.9192287723268</v>
+        <v>641.1658556964804</v>
       </c>
       <c r="D41">
-        <v>1370.821228772327</v>
+        <v>1391.067855696481</v>
       </c>
       <c r="E41">
         <v>326.8020000000001</v>
@@ -4643,37 +4771,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M41">
-        <v>277.5713482816886</v>
+        <v>269.9593282816886</v>
       </c>
       <c r="N41">
-        <v>-167.2380149483553</v>
+        <v>-159.6259949483553</v>
       </c>
       <c r="O41">
-        <v>-58.53330523192435</v>
+        <v>-55.86909823192434</v>
       </c>
       <c r="P41">
-        <v>-108.704709716431</v>
+        <v>-103.7568967164309</v>
       </c>
       <c r="Q41">
-        <v>-23.70470971643095</v>
+        <v>-18.75689671643093</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.3492238668567956</v>
+        <v>0.3488073596418257</v>
       </c>
       <c r="T41">
-        <v>1.491200223658292</v>
+        <v>1.488787932766477</v>
       </c>
       <c r="U41">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V41">
-        <v>0.1391233890159196</v>
+        <v>0.1430462392704288</v>
       </c>
       <c r="W41">
-        <v>0.3139175693377342</v>
+        <v>0.3039175693377342</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3974953971883417</v>
+        <v>0.4087035407726538</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4820,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.3386428981993513</v>
+        <v>0.3343888287982196</v>
       </c>
       <c r="C42">
-        <v>586.4756621692642</v>
+        <v>606.7606006077657</v>
       </c>
       <c r="D42">
-        <v>1355.895662169264</v>
+        <v>1376.180600607766</v>
       </c>
       <c r="E42">
         <v>346.3200000000002</v>
@@ -4725,37 +4853,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M42">
-        <v>284.6885623401935</v>
+        <v>276.8813623401934</v>
       </c>
       <c r="N42">
-        <v>-174.3552290068601</v>
+        <v>-166.5480290068601</v>
       </c>
       <c r="O42">
-        <v>-61.02433015240104</v>
+        <v>-58.29181015240103</v>
       </c>
       <c r="P42">
-        <v>-113.3308988544591</v>
+        <v>-108.2562188544591</v>
       </c>
       <c r="Q42">
-        <v>-28.33089885445909</v>
+        <v>-23.25621885445906</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.3542809313044089</v>
+        <v>0.3538574823025227</v>
       </c>
       <c r="T42">
-        <v>1.516053560719263</v>
+        <v>1.513601064979252</v>
       </c>
       <c r="U42">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V42">
-        <v>0.1356453042905216</v>
+        <v>0.1394700832886681</v>
       </c>
       <c r="W42">
-        <v>0.315185848541765</v>
+        <v>0.305185848541765</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3875580122586332</v>
+        <v>0.3984859522533374</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4902,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.341831385574341</v>
+        <v>0.3374773161732093</v>
       </c>
       <c r="C43">
-        <v>552.3536153982021</v>
+        <v>572.6706192605474</v>
       </c>
       <c r="D43">
-        <v>1341.291615398202</v>
+        <v>1361.608619260548</v>
       </c>
       <c r="E43">
         <v>365.8380000000002</v>
@@ -4807,37 +4935,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M43">
-        <v>291.8057763986983</v>
+        <v>283.8033963986983</v>
       </c>
       <c r="N43">
-        <v>-181.472443065365</v>
+        <v>-173.4700630653649</v>
       </c>
       <c r="O43">
-        <v>-63.51535507287773</v>
+        <v>-60.71452207287773</v>
       </c>
       <c r="P43">
-        <v>-117.9570879924872</v>
+        <v>-112.7555409924872</v>
       </c>
       <c r="Q43">
-        <v>-32.95708799248723</v>
+        <v>-27.75554099248721</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.3595094216655006</v>
+        <v>0.3590787955618875</v>
       </c>
       <c r="T43">
-        <v>1.541749383782302</v>
+        <v>1.539255320317883</v>
       </c>
       <c r="U43">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V43">
-        <v>0.1323368822346552</v>
+        <v>0.136068373940164</v>
       </c>
       <c r="W43">
-        <v>0.3163922604675504</v>
+        <v>0.3063922604675504</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3781053778133007</v>
+        <v>0.3887667826861828</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4984,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.3450198729493307</v>
+        <v>0.3405658035481989</v>
       </c>
       <c r="C44">
-        <v>518.5428101118337</v>
+        <v>538.8860015605208</v>
       </c>
       <c r="D44">
-        <v>1326.998810111834</v>
+        <v>1347.342001560521</v>
       </c>
       <c r="E44">
         <v>385.3560000000001</v>
@@ -4889,37 +5017,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M44">
-        <v>298.9229904572031</v>
+        <v>290.7254304572031</v>
       </c>
       <c r="N44">
-        <v>-188.5896571238698</v>
+        <v>-180.3920971238698</v>
       </c>
       <c r="O44">
-        <v>-66.00637999335441</v>
+        <v>-63.13723399335441</v>
       </c>
       <c r="P44">
-        <v>-122.5832771305154</v>
+        <v>-117.2548631305154</v>
       </c>
       <c r="Q44">
-        <v>-37.58327713051537</v>
+        <v>-32.25486313051536</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.3649182047976643</v>
+        <v>0.3644801541060579</v>
       </c>
       <c r="T44">
-        <v>1.568331269709583</v>
+        <v>1.56579420515095</v>
       </c>
       <c r="U44">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V44">
-        <v>0.129186004086211</v>
+        <v>0.1328286507511125</v>
       </c>
       <c r="W44">
-        <v>0.3175412242063936</v>
+        <v>0.3075412242063936</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3691028688177459</v>
+        <v>0.3795104307174643</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5066,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.3482083603243203</v>
+        <v>0.3436542909231887</v>
       </c>
       <c r="C45">
-        <v>485.0334014479652</v>
+        <v>505.3972484492749</v>
       </c>
       <c r="D45">
-        <v>1313.007401447965</v>
+        <v>1333.371248449275</v>
       </c>
       <c r="E45">
         <v>404.8740000000001</v>
@@ -4971,37 +5099,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M45">
-        <v>306.040204515708</v>
+        <v>297.647464515708</v>
       </c>
       <c r="N45">
-        <v>-195.7068711823746</v>
+        <v>-187.3141311823746</v>
       </c>
       <c r="O45">
-        <v>-68.4974049138311</v>
+        <v>-65.55994591383111</v>
       </c>
       <c r="P45">
-        <v>-127.2094662685435</v>
+        <v>-121.7541852685435</v>
       </c>
       <c r="Q45">
-        <v>-42.20946626854351</v>
+        <v>-36.75418526854349</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.3705167697941146</v>
+        <v>0.3700710340026555</v>
       </c>
       <c r="T45">
-        <v>1.595845853388698</v>
+        <v>1.593264278925528</v>
       </c>
       <c r="U45">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V45">
-        <v>0.1261816784097875</v>
+        <v>0.1297396123615517</v>
       </c>
       <c r="W45">
-        <v>0.3186367477713372</v>
+        <v>0.3086367477713372</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3605190811708215</v>
+        <v>0.3706846067472906</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5148,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.35139684769931</v>
+        <v>0.3467427782981783</v>
       </c>
       <c r="C46">
-        <v>451.8159554153805</v>
+        <v>472.1952508125897</v>
       </c>
       <c r="D46">
-        <v>1299.307955415381</v>
+        <v>1319.68725081259</v>
       </c>
       <c r="E46">
         <v>424.3920000000001</v>
@@ -5053,37 +5181,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M46">
-        <v>313.1574185742128</v>
+        <v>304.5694985742127</v>
       </c>
       <c r="N46">
-        <v>-202.8240852408794</v>
+        <v>-194.2361652408794</v>
       </c>
       <c r="O46">
-        <v>-70.98842983430779</v>
+        <v>-67.98265783430779</v>
       </c>
       <c r="P46">
-        <v>-131.8356554065716</v>
+        <v>-126.2535074065716</v>
       </c>
       <c r="Q46">
-        <v>-46.83565540657165</v>
+        <v>-41.2535074065716</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.376315283540438</v>
+        <v>0.3758615881812744</v>
       </c>
       <c r="T46">
-        <v>1.624343100770639</v>
+        <v>1.621715426763484</v>
       </c>
       <c r="U46">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V46">
-        <v>0.1233139129913833</v>
+        <v>0.1267909848078801</v>
       </c>
       <c r="W46">
-        <v>0.3196824748106015</v>
+        <v>0.3096824748106015</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3523254656896665</v>
+        <v>0.3622599565939432</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5230,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.3545853350742996</v>
+        <v>0.349831265673168</v>
       </c>
       <c r="C47">
-        <v>418.8814276807692</v>
+        <v>439.2712696742848</v>
       </c>
       <c r="D47">
-        <v>1285.891427680769</v>
+        <v>1306.281269674285</v>
       </c>
       <c r="E47">
         <v>443.9100000000001</v>
@@ -5135,37 +5263,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M47">
-        <v>320.2746326327176</v>
+        <v>311.4915326327176</v>
       </c>
       <c r="N47">
-        <v>-209.9412992993843</v>
+        <v>-201.1581992993843</v>
       </c>
       <c r="O47">
-        <v>-73.47945475478448</v>
+        <v>-70.40536975478449</v>
       </c>
       <c r="P47">
-        <v>-136.4618445445998</v>
+        <v>-130.7528295445998</v>
       </c>
       <c r="Q47">
-        <v>-51.46184454459978</v>
+        <v>-45.75282954459979</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.3823246523320823</v>
+        <v>0.3818627079663884</v>
       </c>
       <c r="T47">
-        <v>1.653876611693742</v>
+        <v>1.651201161795547</v>
       </c>
       <c r="U47">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V47">
-        <v>0.120573603813797</v>
+        <v>0.123973407367705</v>
       </c>
       <c r="W47">
-        <v>0.3206817250925652</v>
+        <v>0.3106817250925651</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3444960108965628</v>
+        <v>0.3542097353363</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5312,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.3577738224492893</v>
+        <v>0.3529197530481577</v>
       </c>
       <c r="C48">
-        <v>386.2211436564932</v>
+        <v>406.6169175851306</v>
       </c>
       <c r="D48">
-        <v>1272.749143656493</v>
+        <v>1293.144917585131</v>
       </c>
       <c r="E48">
         <v>463.4280000000001</v>
@@ -5217,37 +5345,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M48">
-        <v>327.3918466912224</v>
+        <v>318.4135666912225</v>
       </c>
       <c r="N48">
-        <v>-217.0585133578891</v>
+        <v>-208.0802333578891</v>
       </c>
       <c r="O48">
-        <v>-75.97047967526117</v>
+        <v>-72.82808167526119</v>
       </c>
       <c r="P48">
-        <v>-141.0880336826279</v>
+        <v>-135.2521516826279</v>
       </c>
       <c r="Q48">
-        <v>-56.08803368262792</v>
+        <v>-50.25215168262793</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.3885565903382321</v>
+        <v>0.3880860914472475</v>
       </c>
       <c r="T48">
-        <v>1.684503956354737</v>
+        <v>1.681778961088058</v>
       </c>
       <c r="U48">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V48">
-        <v>0.117952438513497</v>
+        <v>0.121278333294494</v>
       </c>
       <c r="W48">
-        <v>0.3216375297100957</v>
+        <v>0.3116375297100956</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3370069671814202</v>
+        <v>0.3465095236985543</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5394,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.360962309824279</v>
+        <v>0.3560082404231473</v>
       </c>
       <c r="C49">
-        <v>353.8267797970572</v>
+        <v>374.2241411235328</v>
       </c>
       <c r="D49">
-        <v>1259.872779797057</v>
+        <v>1280.270141123533</v>
       </c>
       <c r="E49">
         <v>482.9460000000001</v>
@@ -5299,37 +5427,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M49">
-        <v>334.5090607497273</v>
+        <v>325.3356007497273</v>
       </c>
       <c r="N49">
-        <v>-224.175727416394</v>
+        <v>-215.0022674163939</v>
       </c>
       <c r="O49">
-        <v>-78.46150459573789</v>
+        <v>-75.25079359573787</v>
       </c>
       <c r="P49">
-        <v>-145.7142228206561</v>
+        <v>-139.7514738206561</v>
       </c>
       <c r="Q49">
-        <v>-60.71422282065609</v>
+        <v>-54.75147382065609</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.3950236958163119</v>
+        <v>0.3945443195877616</v>
       </c>
       <c r="T49">
-        <v>1.716287049870864</v>
+        <v>1.713510639599153</v>
       </c>
       <c r="U49">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V49">
-        <v>0.115442812162146</v>
+        <v>0.1186979432243984</v>
       </c>
       <c r="W49">
-        <v>0.32255266179071</v>
+        <v>0.3125526617907099</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3298366061775602</v>
+        <v>0.3391369806411383</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5476,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.3641507971992686</v>
+        <v>0.3590967277981369</v>
       </c>
       <c r="C50">
-        <v>321.690346019549</v>
+        <v>342.0852044312608</v>
       </c>
       <c r="D50">
-        <v>1247.254346019549</v>
+        <v>1267.649204431261</v>
       </c>
       <c r="E50">
         <v>502.4640000000001</v>
@@ -5381,37 +5509,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M50">
-        <v>341.6262748082321</v>
+        <v>332.2576348082321</v>
       </c>
       <c r="N50">
-        <v>-231.2929414748988</v>
+        <v>-221.9243014748988</v>
       </c>
       <c r="O50">
-        <v>-80.95252951621455</v>
+        <v>-77.67350551621458</v>
       </c>
       <c r="P50">
-        <v>-150.3404119586842</v>
+        <v>-144.2507959586842</v>
       </c>
       <c r="Q50">
-        <v>-65.3404119586842</v>
+        <v>-59.25079595868419</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.4017395361204717</v>
+        <v>0.4012509411182955</v>
       </c>
       <c r="T50">
-        <v>1.749292570060688</v>
+        <v>1.746462767283752</v>
       </c>
       <c r="U50">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V50">
-        <v>0.1130377535754347</v>
+        <v>0.1162250694072234</v>
       </c>
       <c r="W50">
-        <v>0.3234296633679653</v>
+        <v>0.3134296633679653</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3229650102155277</v>
+        <v>0.3320716268777812</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5558,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.3673392845742584</v>
+        <v>0.3621852151731266</v>
       </c>
       <c r="C51">
-        <v>289.8041691700234</v>
+        <v>310.1926737135113</v>
       </c>
       <c r="D51">
-        <v>1234.886169170024</v>
+        <v>1255.274673713511</v>
       </c>
       <c r="E51">
         <v>521.9820000000001</v>
@@ -5463,37 +5591,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M51">
-        <v>348.743488866737</v>
+        <v>339.179668866737</v>
       </c>
       <c r="N51">
-        <v>-238.4101555334036</v>
+        <v>-228.8463355334036</v>
       </c>
       <c r="O51">
-        <v>-83.44355443669127</v>
+        <v>-80.09621743669126</v>
       </c>
       <c r="P51">
-        <v>-154.9666010967124</v>
+        <v>-148.7501180967124</v>
       </c>
       <c r="Q51">
-        <v>-69.96660109671237</v>
+        <v>-63.75011809671236</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.4087187427110692</v>
+        <v>0.4082205674147326</v>
       </c>
       <c r="T51">
-        <v>1.783592424375604</v>
+        <v>1.780707135269708</v>
       </c>
       <c r="U51">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V51">
-        <v>0.1107308606453238</v>
+        <v>0.1138531292152393</v>
       </c>
       <c r="W51">
-        <v>0.3242708689624755</v>
+        <v>0.3142708689624755</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3163738875580678</v>
+        <v>0.3252946549006837</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5640,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.370527771949248</v>
+        <v>0.3652737025481163</v>
       </c>
       <c r="C52">
-        <v>258.1608774639496</v>
+        <v>278.5394026380318</v>
       </c>
       <c r="D52">
-        <v>1222.76087746395</v>
+        <v>1243.139402638032</v>
       </c>
       <c r="E52">
         <v>541.5000000000001</v>
@@ -5545,37 +5673,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M52">
-        <v>355.8607029252418</v>
+        <v>346.1017029252418</v>
       </c>
       <c r="N52">
-        <v>-245.5273695919085</v>
+        <v>-235.7683695919085</v>
       </c>
       <c r="O52">
-        <v>-85.93457935716796</v>
+        <v>-82.51892935716795</v>
       </c>
       <c r="P52">
-        <v>-159.5927902347405</v>
+        <v>-153.2494402347405</v>
       </c>
       <c r="Q52">
-        <v>-74.59279023474051</v>
+        <v>-68.24944023474052</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.4159771175652906</v>
+        <v>0.4154689787630272</v>
       </c>
       <c r="T52">
-        <v>1.819264272863116</v>
+        <v>1.816321277975102</v>
       </c>
       <c r="U52">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V52">
-        <v>0.1085162434324173</v>
+        <v>0.1115760666309345</v>
       </c>
       <c r="W52">
-        <v>0.3250784263332053</v>
+        <v>0.3150784263332054</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3100464098069066</v>
+        <v>0.3187887618026699</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5722,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.3737162593242377</v>
+        <v>0.368362189923106</v>
       </c>
       <c r="C53">
-        <v>226.7533858344111</v>
+        <v>247.1185185730551</v>
       </c>
       <c r="D53">
-        <v>1210.871385834411</v>
+        <v>1231.236518573055</v>
       </c>
       <c r="E53">
         <v>561.0180000000001</v>
@@ -5627,37 +5755,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M53">
-        <v>362.9779169837466</v>
+        <v>353.0237369837466</v>
       </c>
       <c r="N53">
-        <v>-252.6445836504133</v>
+        <v>-242.6904036504133</v>
       </c>
       <c r="O53">
-        <v>-88.42560427764465</v>
+        <v>-84.94164127764465</v>
       </c>
       <c r="P53">
-        <v>-164.2189793727686</v>
+        <v>-157.7487623727686</v>
       </c>
       <c r="Q53">
-        <v>-79.21897937276864</v>
+        <v>-72.74876237276862</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.4235317526176435</v>
+        <v>0.4230132436357421</v>
       </c>
       <c r="T53">
-        <v>1.856392115166445</v>
+        <v>1.853389059158267</v>
       </c>
       <c r="U53">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V53">
-        <v>0.1063884739533503</v>
+        <v>0.1093883006185632</v>
       </c>
       <c r="W53">
-        <v>0.325854314787436</v>
+        <v>0.315854314787436</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3039670684381437</v>
+        <v>0.3125380017673235</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5804,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.3769047466992274</v>
+        <v>0.3714506772980957</v>
       </c>
       <c r="C54">
-        <v>195.5748821268746</v>
+        <v>215.9234096083521</v>
       </c>
       <c r="D54">
-        <v>1199.210882126875</v>
+        <v>1219.559409608352</v>
       </c>
       <c r="E54">
         <v>580.5360000000002</v>
@@ -5709,37 +5837,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M54">
-        <v>370.0951310422515</v>
+        <v>359.9457710422515</v>
       </c>
       <c r="N54">
-        <v>-259.7617977089182</v>
+        <v>-249.6124377089181</v>
       </c>
       <c r="O54">
-        <v>-90.91662919812134</v>
+        <v>-87.36435319812134</v>
       </c>
       <c r="P54">
-        <v>-168.8451685107968</v>
+        <v>-162.2480845107968</v>
       </c>
       <c r="Q54">
-        <v>-83.84516851079681</v>
+        <v>-77.24808451079679</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.4314011641305111</v>
+        <v>0.4308718528781534</v>
       </c>
       <c r="T54">
-        <v>1.895066950899079</v>
+        <v>1.892001331224065</v>
       </c>
       <c r="U54">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V54">
-        <v>0.1043425417619397</v>
+        <v>0.1072846794528216</v>
       </c>
       <c r="W54">
-        <v>0.3266003613780423</v>
+        <v>0.3166003613780423</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2981215478912562</v>
+        <v>0.3065276555794904</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5886,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.380093234074217</v>
+        <v>0.3745391646730853</v>
       </c>
       <c r="C55">
-        <v>164.6188140840052</v>
+        <v>184.9477123079075</v>
       </c>
       <c r="D55">
-        <v>1187.772814084005</v>
+        <v>1208.101712307908</v>
       </c>
       <c r="E55">
         <v>600.0540000000002</v>
@@ -5791,37 +5919,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M55">
-        <v>377.2123451007564</v>
+        <v>366.8678051007563</v>
       </c>
       <c r="N55">
-        <v>-266.879011767423</v>
+        <v>-256.5344717674229</v>
       </c>
       <c r="O55">
-        <v>-93.40765411859803</v>
+        <v>-89.78706511859802</v>
       </c>
       <c r="P55">
-        <v>-173.4713576488249</v>
+        <v>-166.7474066488249</v>
       </c>
       <c r="Q55">
-        <v>-88.47135764882495</v>
+        <v>-81.74740664882489</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.4396054442183943</v>
+        <v>0.4390648710244971</v>
       </c>
       <c r="T55">
-        <v>1.935387524322464</v>
+        <v>1.932256678696917</v>
       </c>
       <c r="U55">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V55">
-        <v>0.1023738145588842</v>
+        <v>0.1052604402178627</v>
       </c>
       <c r="W55">
-        <v>0.3273182552671164</v>
+        <v>0.3173182552671164</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2924966130253835</v>
+        <v>0.3007441149081793</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5968,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.3832817214492067</v>
+        <v>0.377627652048075</v>
       </c>
       <c r="C56">
-        <v>133.8788770682761</v>
+        <v>154.1853001465431</v>
       </c>
       <c r="D56">
-        <v>1176.550877068276</v>
+        <v>1196.857300146543</v>
       </c>
       <c r="E56">
         <v>619.5720000000002</v>
@@ -5873,37 +6001,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M56">
-        <v>384.3295591592612</v>
+        <v>373.7898391592612</v>
       </c>
       <c r="N56">
-        <v>-273.9962258259278</v>
+        <v>-263.4565058259278</v>
       </c>
       <c r="O56">
-        <v>-95.89867903907472</v>
+        <v>-92.20977703907474</v>
       </c>
       <c r="P56">
-        <v>-178.0975467868531</v>
+        <v>-171.2467287868531</v>
       </c>
       <c r="Q56">
-        <v>-93.09754678685309</v>
+        <v>-86.24672878685308</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.4481664321361855</v>
+        <v>0.4476141073511167</v>
       </c>
       <c r="T56">
-        <v>1.977461166155561</v>
+        <v>1.974262258668589</v>
       </c>
       <c r="U56">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V56">
-        <v>0.1004780031781641</v>
+        <v>0.1033111728064208</v>
       </c>
       <c r="W56">
-        <v>0.3280095604936321</v>
+        <v>0.3180095604936322</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.287080009080469</v>
+        <v>0.2951747794469166</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6050,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.3864702088241964</v>
+        <v>0.3807161394230647</v>
       </c>
       <c r="C57">
-        <v>103.3490024740372</v>
+        <v>123.630272586347</v>
       </c>
       <c r="D57">
-        <v>1165.539002474037</v>
+        <v>1185.820272586347</v>
       </c>
       <c r="E57">
         <v>639.0900000000003</v>
@@ -5955,37 +6083,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M57">
-        <v>391.446773217766</v>
+        <v>380.711873217766</v>
       </c>
       <c r="N57">
-        <v>-281.1134398844326</v>
+        <v>-270.3785398844327</v>
       </c>
       <c r="O57">
-        <v>-98.38970395955141</v>
+        <v>-94.63248895955144</v>
       </c>
       <c r="P57">
-        <v>-182.7237359248812</v>
+        <v>-175.7460509248813</v>
       </c>
       <c r="Q57">
-        <v>-97.72373592488123</v>
+        <v>-90.74605092488127</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.4571079084058786</v>
+        <v>0.456543309736697</v>
       </c>
       <c r="T57">
-        <v>2.021404747625685</v>
+        <v>2.018134753305669</v>
       </c>
       <c r="U57">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V57">
-        <v>0.09865113039310661</v>
+        <v>0.1014327878463041</v>
       </c>
       <c r="W57">
-        <v>0.3286757273482746</v>
+        <v>0.3186757273482746</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2818603725517332</v>
+        <v>0.2898079652751544</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6132,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3896586961991861</v>
+        <v>0.3838046267980543</v>
       </c>
       <c r="C58">
-        <v>73.02334678428883</v>
+        <v>93.27694475197995</v>
       </c>
       <c r="D58">
-        <v>1154.731346784289</v>
+        <v>1174.98494475198</v>
       </c>
       <c r="E58">
         <v>658.6080000000003</v>
@@ -6037,37 +6165,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M58">
-        <v>398.5639872762709</v>
+        <v>387.6339072762709</v>
       </c>
       <c r="N58">
-        <v>-288.2306539429376</v>
+        <v>-277.3005739429375</v>
       </c>
       <c r="O58">
-        <v>-100.8807288800281</v>
+        <v>-97.05520088002811</v>
       </c>
       <c r="P58">
-        <v>-187.3499250629094</v>
+        <v>-180.2453730629094</v>
       </c>
       <c r="Q58">
-        <v>-102.3499250629094</v>
+        <v>-95.24537306290938</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.4664558154151031</v>
+        <v>0.4658783849579856</v>
       </c>
       <c r="T58">
-        <v>2.067345764617178</v>
+        <v>2.064001452244435</v>
       </c>
       <c r="U58">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V58">
-        <v>0.09688950306465827</v>
+        <v>0.09962148806333433</v>
       </c>
       <c r="W58">
-        <v>0.329318102529537</v>
+        <v>0.3193181025295369</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2768271516133093</v>
+        <v>0.2846328230380982</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6214,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3928471835741757</v>
+        <v>0.386893114173044</v>
       </c>
       <c r="C59">
-        <v>42.89628123070088</v>
+        <v>63.11983766690309</v>
       </c>
       <c r="D59">
-        <v>1144.122281230701</v>
+        <v>1164.345837666903</v>
       </c>
       <c r="E59">
         <v>678.1260000000003</v>
@@ -6119,37 +6247,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M59">
-        <v>405.6812013347757</v>
+        <v>394.5559413347757</v>
       </c>
       <c r="N59">
-        <v>-295.3478680014424</v>
+        <v>-284.2226080014424</v>
       </c>
       <c r="O59">
-        <v>-103.3717538005048</v>
+        <v>-99.47791280050482</v>
       </c>
       <c r="P59">
-        <v>-191.9761142009376</v>
+        <v>-184.7446952009375</v>
       </c>
       <c r="Q59">
-        <v>-106.9761142009376</v>
+        <v>-99.74469520093754</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.4762385087968496</v>
+        <v>0.4756476497244504</v>
       </c>
       <c r="T59">
-        <v>2.115423573096647</v>
+        <v>2.112001486017561</v>
       </c>
       <c r="U59">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V59">
-        <v>0.09518968722141864</v>
+        <v>0.09787374265871443</v>
       </c>
       <c r="W59">
-        <v>0.329937938230755</v>
+        <v>0.319937938230755</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.271970534918339</v>
+        <v>0.2796392647391841</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6296,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.3960356709491654</v>
+        <v>0.3899816015480336</v>
       </c>
       <c r="C60">
-        <v>12.96238201843062</v>
+        <v>33.15366901529069</v>
       </c>
       <c r="D60">
-        <v>1133.706382018431</v>
+        <v>1153.897669015291</v>
       </c>
       <c r="E60">
         <v>697.6440000000001</v>
@@ -6201,37 +6329,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M60">
-        <v>412.7984153932805</v>
+        <v>401.4779753932805</v>
       </c>
       <c r="N60">
-        <v>-302.4650820599471</v>
+        <v>-291.1446420599472</v>
       </c>
       <c r="O60">
-        <v>-105.8627787209815</v>
+        <v>-101.9006247209815</v>
       </c>
       <c r="P60">
-        <v>-196.6023033389656</v>
+        <v>-189.2440173389656</v>
       </c>
       <c r="Q60">
-        <v>-111.6023033389656</v>
+        <v>-104.2440173389656</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.486487044720584</v>
+        <v>0.4858821175750324</v>
       </c>
       <c r="T60">
-        <v>2.165790801027519</v>
+        <v>2.162287235684645</v>
       </c>
       <c r="U60">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V60">
-        <v>0.0935484857176011</v>
+        <v>0.09618626433701248</v>
       </c>
       <c r="W60">
-        <v>0.3305364002871035</v>
+        <v>0.3205364002871035</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2672813877645747</v>
+        <v>0.2748178981057499</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6378,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.399224158324155</v>
+        <v>0.3930700889230233</v>
       </c>
       <c r="C61">
-        <v>-16.78357891992596</v>
+        <v>3.37334439690494</v>
       </c>
       <c r="D61">
-        <v>1123.478421080074</v>
+        <v>1143.635344396905</v>
       </c>
       <c r="E61">
         <v>717.1620000000001</v>
@@ -6283,37 +6411,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M61">
-        <v>419.9156294517853</v>
+        <v>408.4000094517853</v>
       </c>
       <c r="N61">
-        <v>-309.5822961184519</v>
+        <v>-298.0666761184519</v>
       </c>
       <c r="O61">
-        <v>-108.3538036414582</v>
+        <v>-104.3233366414582</v>
       </c>
       <c r="P61">
-        <v>-201.2284924769938</v>
+        <v>-193.7433394769938</v>
       </c>
       <c r="Q61">
-        <v>-116.2284924769938</v>
+        <v>-108.7433394769938</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.4972355092259642</v>
+        <v>0.4966158277597893</v>
       </c>
       <c r="T61">
-        <v>2.218614966906239</v>
+        <v>2.215025948750124</v>
       </c>
       <c r="U61">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V61">
-        <v>0.0919629181630655</v>
+        <v>0.09455598867028346</v>
       </c>
       <c r="W61">
-        <v>0.3311145754940842</v>
+        <v>0.3211145754940842</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2627511947516158</v>
+        <v>0.2701599676293814</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6460,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.4024126456991446</v>
+        <v>0.396158576298013</v>
       </c>
       <c r="C62">
-        <v>-46.3466426743646</v>
+        <v>-26.22605095548784</v>
       </c>
       <c r="D62">
-        <v>1113.433357325636</v>
+        <v>1133.553949044512</v>
       </c>
       <c r="E62">
         <v>736.6800000000002</v>
@@ -6365,37 +6493,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M62">
-        <v>427.0328435102901</v>
+        <v>415.3220435102901</v>
       </c>
       <c r="N62">
-        <v>-316.6995101769568</v>
+        <v>-304.9887101769568</v>
       </c>
       <c r="O62">
-        <v>-110.8448285619349</v>
+        <v>-106.7460485619349</v>
       </c>
       <c r="P62">
-        <v>-205.8546816150219</v>
+        <v>-198.2426616150219</v>
       </c>
       <c r="Q62">
-        <v>-120.8546816150219</v>
+        <v>-113.2426616150219</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.5085213969566131</v>
+        <v>0.5078862234537841</v>
       </c>
       <c r="T62">
-        <v>2.274080341078895</v>
+        <v>2.270401597468878</v>
       </c>
       <c r="U62">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V62">
-        <v>0.09043020286034774</v>
+        <v>0.09298005552577872</v>
       </c>
       <c r="W62">
-        <v>0.3316734781941656</v>
+        <v>0.3216734781941656</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2583720081724222</v>
+        <v>0.2656573015022249</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6542,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.4056011330741343</v>
+        <v>0.3992470636730027</v>
       </c>
       <c r="C63">
-        <v>-75.73167164226334</v>
+        <v>-55.64926002445554</v>
       </c>
       <c r="D63">
-        <v>1103.566328357737</v>
+        <v>1123.648739975545</v>
       </c>
       <c r="E63">
         <v>756.1980000000002</v>
@@ -6447,37 +6575,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M63">
-        <v>434.150057568795</v>
+        <v>422.244077568795</v>
       </c>
       <c r="N63">
-        <v>-323.8167242354617</v>
+        <v>-311.9107442354617</v>
       </c>
       <c r="O63">
-        <v>-113.3358534824116</v>
+        <v>-109.1687604824116</v>
       </c>
       <c r="P63">
-        <v>-210.4808707530501</v>
+        <v>-202.7419837530501</v>
       </c>
       <c r="Q63">
-        <v>-125.4808707530501</v>
+        <v>-117.7419837530501</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.5203860481606289</v>
+        <v>0.5197345881577273</v>
       </c>
       <c r="T63">
-        <v>2.332390093414251</v>
+        <v>2.328617023045003</v>
       </c>
       <c r="U63">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V63">
-        <v>0.08894774051837481</v>
+        <v>0.09145579232043807</v>
       </c>
       <c r="W63">
-        <v>0.3322140562155558</v>
+        <v>0.3222140562155558</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2541364014810709</v>
+        <v>0.2613022637726802</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6624,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.408789620449124</v>
+        <v>0.4023355510479923</v>
       </c>
       <c r="C64">
-        <v>-104.9433573765239</v>
+        <v>-84.90086144831548</v>
       </c>
       <c r="D64">
-        <v>1093.872642623476</v>
+        <v>1113.915138551685</v>
       </c>
       <c r="E64">
         <v>775.7160000000002</v>
@@ -6529,37 +6657,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M64">
-        <v>441.2672716272999</v>
+        <v>429.1661116272999</v>
       </c>
       <c r="N64">
-        <v>-330.9339382939665</v>
+        <v>-318.8327782939665</v>
       </c>
       <c r="O64">
-        <v>-115.8268784028883</v>
+        <v>-111.5914724028883</v>
       </c>
       <c r="P64">
-        <v>-215.1070598910783</v>
+        <v>-207.2413058910782</v>
       </c>
       <c r="Q64">
-        <v>-130.1070598910783</v>
+        <v>-122.2413058910782</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.5328751546911717</v>
+        <v>0.5322065510039833</v>
       </c>
       <c r="T64">
-        <v>2.393768780083047</v>
+        <v>2.389896418388292</v>
       </c>
       <c r="U64">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V64">
-        <v>0.08751309954227199</v>
+        <v>0.08998069889591488</v>
       </c>
       <c r="W64">
-        <v>0.332737196236256</v>
+        <v>0.322737196236256</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2500374272636342</v>
+        <v>0.2570877111311854</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6706,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.4119781078241137</v>
+        <v>0.405424038422982</v>
       </c>
       <c r="C65">
-        <v>-133.9862280236978</v>
+        <v>-113.9852765781636</v>
       </c>
       <c r="D65">
-        <v>1084.347771976302</v>
+        <v>1104.348723421836</v>
       </c>
       <c r="E65">
         <v>795.234</v>
@@ -6611,37 +6739,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M65">
-        <v>448.3844856858046</v>
+        <v>436.0881456858046</v>
       </c>
       <c r="N65">
-        <v>-338.0511523524713</v>
+        <v>-325.7548123524713</v>
       </c>
       <c r="O65">
-        <v>-118.3179033233649</v>
+        <v>-114.0141843233649</v>
       </c>
       <c r="P65">
-        <v>-219.7332490291063</v>
+        <v>-211.7406280291063</v>
       </c>
       <c r="Q65">
-        <v>-134.7332490291063</v>
+        <v>-126.7406280291063</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.5460393480612036</v>
+        <v>0.5453526740040909</v>
       </c>
       <c r="T65">
-        <v>2.458465233598806</v>
+        <v>2.454488213479868</v>
       </c>
       <c r="U65">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V65">
-        <v>0.0861240027241407</v>
+        <v>0.08855243383407499</v>
       </c>
       <c r="W65">
-        <v>0.3332437286372514</v>
+        <v>0.3232437286372514</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2460685792118307</v>
+        <v>0.2530069538116428</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6788,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.4151665951991034</v>
+        <v>0.4085125257979716</v>
       </c>
       <c r="C66">
-        <v>-162.864655376856</v>
+        <v>-142.9067761743534</v>
       </c>
       <c r="D66">
-        <v>1074.987344623144</v>
+        <v>1094.945223825647</v>
       </c>
       <c r="E66">
         <v>814.7520000000001</v>
@@ -6693,37 +6821,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M66">
-        <v>455.5016997443095</v>
+        <v>443.0101797443095</v>
       </c>
       <c r="N66">
-        <v>-345.1683664109761</v>
+        <v>-332.6768464109762</v>
       </c>
       <c r="O66">
-        <v>-120.8089282438416</v>
+        <v>-116.4368962438416</v>
       </c>
       <c r="P66">
-        <v>-224.3594381671345</v>
+        <v>-216.2399501671345</v>
       </c>
       <c r="Q66">
-        <v>-139.3594381671345</v>
+        <v>-131.2399501671345</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.559934885507348</v>
+        <v>0.5592291371708711</v>
       </c>
       <c r="T66">
-        <v>2.526755934532106</v>
+        <v>2.522668441632086</v>
       </c>
       <c r="U66">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V66">
-        <v>0.08477831518157601</v>
+        <v>0.08716880205541756</v>
       </c>
       <c r="W66">
-        <v>0.3337344319007157</v>
+        <v>0.3237344319007157</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2422237576616458</v>
+        <v>0.2490537201583358</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6870,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.418355082574093</v>
+        <v>0.4116010131729613</v>
       </c>
       <c r="C67">
-        <v>-191.5828615662936</v>
+        <v>-171.6694867637466</v>
       </c>
       <c r="D67">
-        <v>1065.787138433707</v>
+        <v>1085.700513236254</v>
       </c>
       <c r="E67">
         <v>834.2700000000001</v>
@@ -6775,37 +6903,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M67">
-        <v>462.6189138028143</v>
+        <v>449.9322138028143</v>
       </c>
       <c r="N67">
-        <v>-352.285580469481</v>
+        <v>-339.5988804694809</v>
       </c>
       <c r="O67">
-        <v>-123.2999531643184</v>
+        <v>-118.8596081643183</v>
       </c>
       <c r="P67">
-        <v>-228.9856273051627</v>
+        <v>-220.7392723051626</v>
       </c>
       <c r="Q67">
-        <v>-143.9856273051627</v>
+        <v>-135.7392723051626</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.5746244536647009</v>
+        <v>0.5738985410900389</v>
       </c>
       <c r="T67">
-        <v>2.598948961233023</v>
+        <v>2.594744682821574</v>
       </c>
       <c r="U67">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V67">
-        <v>0.08347403340955174</v>
+        <v>0.08582774356225729</v>
       </c>
       <c r="W67">
-        <v>0.3342100366022273</v>
+        <v>0.3242100366022272</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.238497238313005</v>
+        <v>0.2452221244635924</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6952,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.4215435699490827</v>
+        <v>0.414689500547951</v>
       </c>
       <c r="C68">
-        <v>-220.1449254095755</v>
+        <v>-200.2773966776074</v>
       </c>
       <c r="D68">
-        <v>1056.743074590425</v>
+        <v>1076.610603322393</v>
       </c>
       <c r="E68">
         <v>853.7880000000001</v>
@@ -6857,37 +6985,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M68">
-        <v>469.7361278613192</v>
+        <v>456.8542478613192</v>
       </c>
       <c r="N68">
-        <v>-359.4027945279859</v>
+        <v>-346.5209145279858</v>
       </c>
       <c r="O68">
-        <v>-125.790978084795</v>
+        <v>-121.282320084795</v>
       </c>
       <c r="P68">
-        <v>-233.6118164431908</v>
+        <v>-225.2385944431908</v>
       </c>
       <c r="Q68">
-        <v>-148.6118164431908</v>
+        <v>-140.2385944431908</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.5901781140666038</v>
+        <v>0.5894308511220989</v>
       </c>
       <c r="T68">
-        <v>2.675388636563406</v>
+        <v>2.671060702904562</v>
       </c>
       <c r="U68">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V68">
-        <v>0.08220927532758886</v>
+        <v>0.0845273232052534</v>
       </c>
       <c r="W68">
-        <v>0.3346712290400566</v>
+        <v>0.3246712290400566</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.234883643793111</v>
+        <v>0.2415066377292954</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7034,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.4247320573240724</v>
+        <v>0.4177779879229407</v>
       </c>
       <c r="C69">
-        <v>-248.5547884409943</v>
+        <v>-228.73436178871</v>
       </c>
       <c r="D69">
-        <v>1047.851211559006</v>
+        <v>1067.67163821129</v>
       </c>
       <c r="E69">
         <v>873.3060000000002</v>
@@ -6939,37 +7067,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M69">
-        <v>476.853341919824</v>
+        <v>463.776281919824</v>
       </c>
       <c r="N69">
-        <v>-366.5200085864907</v>
+        <v>-353.4429485864906</v>
       </c>
       <c r="O69">
-        <v>-128.2820030052717</v>
+        <v>-123.7050320052717</v>
       </c>
       <c r="P69">
-        <v>-238.2380055812189</v>
+        <v>-229.7379165812189</v>
       </c>
       <c r="Q69">
-        <v>-153.2380055812189</v>
+        <v>-144.7379165812189</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.6066744205534707</v>
+        <v>0.6059045132773141</v>
       </c>
       <c r="T69">
-        <v>2.75646101948957</v>
+        <v>2.752001936325912</v>
       </c>
       <c r="U69">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V69">
-        <v>0.08098227121822185</v>
+        <v>0.08326572136636901</v>
       </c>
       <c r="W69">
-        <v>0.3351186545394433</v>
+        <v>0.3251186545394433</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2313779177663481</v>
+        <v>0.2379020610467687</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7116,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.427920544699062</v>
+        <v>0.4208664752979304</v>
       </c>
       <c r="C70">
-        <v>-276.8162606391584</v>
+        <v>-257.044110964988</v>
       </c>
       <c r="D70">
-        <v>1039.107739360842</v>
+        <v>1058.879889035012</v>
       </c>
       <c r="E70">
         <v>892.8240000000002</v>
@@ -7021,37 +7149,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M70">
-        <v>483.9705559783289</v>
+        <v>470.6983159783288</v>
       </c>
       <c r="N70">
-        <v>-373.6372226449955</v>
+        <v>-360.3649826449955</v>
       </c>
       <c r="O70">
-        <v>-130.7730279257484</v>
+        <v>-126.1277439257484</v>
       </c>
       <c r="P70">
-        <v>-242.8641947192471</v>
+        <v>-234.2372387192471</v>
       </c>
       <c r="Q70">
-        <v>-157.8641947192471</v>
+        <v>-149.2372387192471</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.6242017461957666</v>
+        <v>0.6234077793172302</v>
       </c>
       <c r="T70">
-        <v>2.84260042634862</v>
+        <v>2.838001996836097</v>
       </c>
       <c r="U70">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V70">
-        <v>0.07979135546501269</v>
+        <v>0.08204122546392241</v>
       </c>
       <c r="W70">
-        <v>0.3355529204653187</v>
+        <v>0.3255529204653187</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2279753013286078</v>
+        <v>0.2344035013254926</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7198,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.4311090320740517</v>
+        <v>0.42395496267292</v>
       </c>
       <c r="C71">
-        <v>-304.9330258702037</v>
+        <v>-285.2102512559397</v>
       </c>
       <c r="D71">
-        <v>1030.508974129797</v>
+        <v>1050.23174874406</v>
       </c>
       <c r="E71">
         <v>912.3420000000002</v>
@@ -7103,37 +7231,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M71">
-        <v>491.0877700368337</v>
+        <v>477.6203500368337</v>
       </c>
       <c r="N71">
-        <v>-380.7544367035003</v>
+        <v>-367.2870167035004</v>
       </c>
       <c r="O71">
-        <v>-133.2640528462251</v>
+        <v>-128.5504558462251</v>
       </c>
       <c r="P71">
-        <v>-247.4903838572752</v>
+        <v>-238.7365608572753</v>
       </c>
       <c r="Q71">
-        <v>-162.4903838572752</v>
+        <v>-153.7365608572753</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.6428598670407915</v>
+        <v>0.6420402883274634</v>
       </c>
       <c r="T71">
-        <v>2.934297214295349</v>
+        <v>2.929550448346939</v>
       </c>
       <c r="U71">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V71">
-        <v>0.07863495900899801</v>
+        <v>0.08085222219632932</v>
       </c>
       <c r="W71">
-        <v>0.3359745989730528</v>
+        <v>0.3259745989730528</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2246713114542801</v>
+        <v>0.2310063491323695</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7280,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.4342975194490414</v>
+        <v>0.4270434500479097</v>
       </c>
       <c r="C72">
-        <v>-332.9086470629625</v>
+        <v>-313.2362728269381</v>
       </c>
       <c r="D72">
-        <v>1022.051352937038</v>
+        <v>1041.723727173062</v>
       </c>
       <c r="E72">
         <v>931.8600000000002</v>
@@ -7185,37 +7313,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M72">
-        <v>498.2049840953385</v>
+        <v>484.5423840953385</v>
       </c>
       <c r="N72">
-        <v>-387.8716507620052</v>
+        <v>-374.2090507620052</v>
       </c>
       <c r="O72">
-        <v>-135.7550777667018</v>
+        <v>-130.9731677667018</v>
       </c>
       <c r="P72">
-        <v>-252.1165729953034</v>
+        <v>-243.2358829953034</v>
       </c>
       <c r="Q72">
-        <v>-167.1165729953034</v>
+        <v>-158.2358829953034</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.6627618626088178</v>
+        <v>0.6619149646050455</v>
       </c>
       <c r="T72">
-        <v>3.032107121438528</v>
+        <v>3.027202129958504</v>
       </c>
       <c r="U72">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V72">
-        <v>0.07751160245172663</v>
+        <v>0.07969719045066748</v>
       </c>
       <c r="W72">
-        <v>0.336384229523423</v>
+        <v>0.3263842295234229</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2214617212906476</v>
+        <v>0.2277062584304785</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7362,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.437486006824031</v>
+        <v>0.4301319374228993</v>
       </c>
       <c r="C73">
-        <v>-360.7465711313625</v>
+        <v>-341.1255536556266</v>
       </c>
       <c r="D73">
-        <v>1013.731428868637</v>
+        <v>1033.352446344373</v>
       </c>
       <c r="E73">
         <v>951.378</v>
@@ -7267,37 +7395,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M73">
-        <v>505.3221981538433</v>
+        <v>491.4644181538433</v>
       </c>
       <c r="N73">
-        <v>-394.98886482051</v>
+        <v>-381.13108482051</v>
       </c>
       <c r="O73">
-        <v>-138.2461026871785</v>
+        <v>-133.3958796871785</v>
       </c>
       <c r="P73">
-        <v>-256.7427621333316</v>
+        <v>-247.7352051333315</v>
       </c>
       <c r="Q73">
-        <v>-171.7427621333316</v>
+        <v>-162.7352051333315</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.6840364095953286</v>
+        <v>0.6831603082121158</v>
       </c>
       <c r="T73">
-        <v>3.136662539419166</v>
+        <v>3.131588410301899</v>
       </c>
       <c r="U73">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V73">
-        <v>0.07641988974113893</v>
+        <v>0.07857469481051724</v>
       </c>
       <c r="W73">
-        <v>0.3367823211850503</v>
+        <v>0.3267823211850503</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2183425421175398</v>
+        <v>0.2244991280300493</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7444,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.4406744941990207</v>
+        <v>0.433220424797889</v>
       </c>
       <c r="C74">
-        <v>-388.4501336583481</v>
+        <v>-368.8813640036853</v>
       </c>
       <c r="D74">
-        <v>1005.545866341652</v>
+        <v>1025.114635996315</v>
       </c>
       <c r="E74">
         <v>970.8960000000001</v>
@@ -7349,37 +7477,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M74">
-        <v>512.4394122123482</v>
+        <v>498.3864522123482</v>
       </c>
       <c r="N74">
-        <v>-402.1060788790148</v>
+        <v>-388.0531188790148</v>
       </c>
       <c r="O74">
-        <v>-140.7371276076552</v>
+        <v>-135.8185916076552</v>
       </c>
       <c r="P74">
-        <v>-261.3689512713597</v>
+        <v>-252.2345272713597</v>
       </c>
       <c r="Q74">
-        <v>-176.3689512713597</v>
+        <v>-167.2345272713597</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.706830567080876</v>
+        <v>0.7059231763625485</v>
       </c>
       <c r="T74">
-        <v>3.248686201541279</v>
+        <v>3.243430853526967</v>
       </c>
       <c r="U74">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V74">
-        <v>0.07535850238362311</v>
+        <v>0.07748337960481561</v>
       </c>
       <c r="W74">
-        <v>0.3371693547449658</v>
+        <v>0.3271693547449658</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2153100068103518</v>
+        <v>0.2213810845851875</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7526,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.4438629815740103</v>
+        <v>0.4363089121728787</v>
       </c>
       <c r="C75">
-        <v>-416.0225633546881</v>
+        <v>-396.5068706763886</v>
       </c>
       <c r="D75">
-        <v>997.491436645312</v>
+        <v>1017.007129323611</v>
       </c>
       <c r="E75">
         <v>990.4140000000001</v>
@@ -7431,37 +7559,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M75">
-        <v>519.556626270853</v>
+        <v>505.308486270853</v>
       </c>
       <c r="N75">
-        <v>-409.2232929375197</v>
+        <v>-394.9751529375196</v>
       </c>
       <c r="O75">
-        <v>-143.2281525281319</v>
+        <v>-138.2413035281319</v>
       </c>
       <c r="P75">
-        <v>-265.9951404093878</v>
+        <v>-256.7338494093877</v>
       </c>
       <c r="Q75">
-        <v>-180.9951404093878</v>
+        <v>-171.7338494093877</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.731313180676464</v>
+        <v>0.7303721828944949</v>
       </c>
       <c r="T75">
-        <v>3.369007912709474</v>
+        <v>3.363557922176115</v>
       </c>
       <c r="U75">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V75">
-        <v>0.07432619413179266</v>
+        <v>0.07642196344584554</v>
       </c>
       <c r="W75">
-        <v>0.3375457846457056</v>
+        <v>0.3275457846457056</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2123605546622648</v>
+        <v>0.2183484669881302</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7608,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.447051468949</v>
+        <v>0.4393973995478684</v>
       </c>
       <c r="C76">
-        <v>-443.4669863052001</v>
+        <v>-424.0051410816266</v>
       </c>
       <c r="D76">
-        <v>989.5650136948001</v>
+        <v>1009.026858918374</v>
       </c>
       <c r="E76">
         <v>1009.932</v>
@@ -7513,37 +7641,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M76">
-        <v>526.6738403293579</v>
+        <v>512.2305203293579</v>
       </c>
       <c r="N76">
-        <v>-416.3405069960245</v>
+        <v>-401.8971869960245</v>
       </c>
       <c r="O76">
-        <v>-145.7191774486085</v>
+        <v>-140.6640154486086</v>
       </c>
       <c r="P76">
-        <v>-270.6213295474159</v>
+        <v>-261.233171547416</v>
       </c>
       <c r="Q76">
-        <v>-185.6213295474159</v>
+        <v>-176.233171547416</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.7576790722409433</v>
+        <v>0.7567018822365909</v>
       </c>
       <c r="T76">
-        <v>3.498585140121377</v>
+        <v>3.492925534567504</v>
       </c>
       <c r="U76">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V76">
-        <v>0.07332178610298465</v>
+        <v>0.07538923421009086</v>
       </c>
       <c r="W76">
-        <v>0.3379120407653442</v>
+        <v>0.3279120407653442</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2094908174370991</v>
+        <v>0.2153978120288311</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7690,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.4502399563239897</v>
+        <v>0.442485886922858</v>
       </c>
       <c r="C77">
-        <v>-470.7864300141143</v>
+        <v>-451.379147099307</v>
       </c>
       <c r="D77">
-        <v>981.7635699858859</v>
+        <v>1001.170852900693</v>
       </c>
       <c r="E77">
         <v>1029.45</v>
@@ -7595,37 +7723,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M77">
-        <v>533.7910543878627</v>
+        <v>519.1525543878627</v>
       </c>
       <c r="N77">
-        <v>-423.4577210545293</v>
+        <v>-408.8192210545293</v>
       </c>
       <c r="O77">
-        <v>-148.2102023690852</v>
+        <v>-143.0867273690853</v>
       </c>
       <c r="P77">
-        <v>-275.2475186854441</v>
+        <v>-265.7324936854441</v>
       </c>
       <c r="Q77">
-        <v>-190.2475186854441</v>
+        <v>-180.7324936854441</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.7861542351305811</v>
+        <v>0.7851379575260544</v>
       </c>
       <c r="T77">
-        <v>3.638528545726232</v>
+        <v>3.632642555950204</v>
       </c>
       <c r="U77">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V77">
-        <v>0.0723441622882782</v>
+        <v>0.07438404442062299</v>
       </c>
       <c r="W77">
-        <v>0.3382685300551259</v>
+        <v>0.3282685300551259</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2066976065379378</v>
+        <v>0.2125258412017801</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7772,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.4534284436989794</v>
+        <v>0.4455743742978477</v>
       </c>
       <c r="C78">
-        <v>-497.9838272605843</v>
+        <v>-478.6317687713997</v>
       </c>
       <c r="D78">
-        <v>974.0841727394159</v>
+        <v>993.4362312286005</v>
       </c>
       <c r="E78">
         <v>1048.968</v>
@@ -7677,37 +7805,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M78">
-        <v>540.9082684463675</v>
+        <v>526.0745884463676</v>
       </c>
       <c r="N78">
-        <v>-430.5749351130341</v>
+        <v>-415.7412551130342</v>
       </c>
       <c r="O78">
-        <v>-150.7012272895619</v>
+        <v>-145.509439289562</v>
       </c>
       <c r="P78">
-        <v>-279.8737078234722</v>
+        <v>-270.2318158234722</v>
       </c>
       <c r="Q78">
-        <v>-194.8737078234722</v>
+        <v>-185.2318158234722</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.817002328261022</v>
+        <v>0.8159437057563068</v>
       </c>
       <c r="T78">
-        <v>3.790133901798158</v>
+        <v>3.784002662448129</v>
       </c>
       <c r="U78">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V78">
-        <v>0.071392265416064</v>
+        <v>0.07340530699403583</v>
       </c>
       <c r="W78">
-        <v>0.338615638047808</v>
+        <v>0.328615638047808</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2039779011887544</v>
+        <v>0.2097294485543881</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7854,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.4566169310739691</v>
+        <v>0.4486628616728374</v>
       </c>
       <c r="C79">
-        <v>-525.0620197746503</v>
+        <v>-505.7657978222448</v>
       </c>
       <c r="D79">
-        <v>966.52398022535</v>
+        <v>985.8202021777554</v>
       </c>
       <c r="E79">
         <v>1068.486</v>
@@ -7759,37 +7887,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M79">
-        <v>548.0254825048723</v>
+        <v>532.9966225048723</v>
       </c>
       <c r="N79">
-        <v>-437.692149171539</v>
+        <v>-422.663289171539</v>
       </c>
       <c r="O79">
-        <v>-153.1922522100386</v>
+        <v>-147.9321512100386</v>
       </c>
       <c r="P79">
-        <v>-284.4998969615003</v>
+        <v>-274.7311379615003</v>
       </c>
       <c r="Q79">
-        <v>-199.4998969615003</v>
+        <v>-189.7311379615003</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.8505328642723711</v>
+        <v>0.8494282147022333</v>
       </c>
       <c r="T79">
-        <v>3.954922332311123</v>
+        <v>3.948524517337179</v>
       </c>
       <c r="U79">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V79">
-        <v>0.0704650931379333</v>
+        <v>0.07245199131878863</v>
       </c>
       <c r="W79">
-        <v>0.3389537302484724</v>
+        <v>0.3289537302484724</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2013288375369524</v>
+        <v>0.2070056894822533</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7936,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.4598054184489587</v>
+        <v>0.4517513490478271</v>
       </c>
       <c r="C80">
-        <v>-552.0237617433395</v>
+        <v>-532.7839410181655</v>
       </c>
       <c r="D80">
-        <v>959.0802382566608</v>
+        <v>978.3200589818348</v>
       </c>
       <c r="E80">
         <v>1088.004</v>
@@ -7841,37 +7969,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M80">
-        <v>555.1426965633773</v>
+        <v>539.9186565633772</v>
       </c>
       <c r="N80">
-        <v>-444.8093632300439</v>
+        <v>-429.5853232300439</v>
       </c>
       <c r="O80">
-        <v>-155.6832771305154</v>
+        <v>-150.3548631305153</v>
       </c>
       <c r="P80">
-        <v>-289.1260860995285</v>
+        <v>-279.2304600995285</v>
       </c>
       <c r="Q80">
-        <v>-204.1260860995285</v>
+        <v>-194.2304600995285</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.8871116308302059</v>
+        <v>0.8859567699159712</v>
       </c>
       <c r="T80">
-        <v>4.134691529234355</v>
+        <v>4.128002904488869</v>
       </c>
       <c r="U80">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V80">
-        <v>0.06956169450795978</v>
+        <v>0.0715231196352144</v>
       </c>
       <c r="W80">
-        <v>0.3392831534183505</v>
+        <v>0.3292831534183505</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1987476985941709</v>
+        <v>0.2043517703863269</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8018,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.4629939058239484</v>
+        <v>0.4548398364228168</v>
       </c>
       <c r="C81">
-        <v>-578.8717231559923</v>
+        <v>-559.6888233748786</v>
       </c>
       <c r="D81">
-        <v>951.750276844008</v>
+        <v>970.9331766251217</v>
       </c>
       <c r="E81">
         <v>1107.522</v>
@@ -7923,37 +8051,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M81">
-        <v>562.2599106218821</v>
+        <v>546.8406906218821</v>
       </c>
       <c r="N81">
-        <v>-451.9265772885487</v>
+        <v>-436.5073572885487</v>
       </c>
       <c r="O81">
-        <v>-158.1743020509921</v>
+        <v>-152.7775750509921</v>
       </c>
       <c r="P81">
-        <v>-293.7522752375567</v>
+        <v>-283.7297822375567</v>
       </c>
       <c r="Q81">
-        <v>-208.7522752375567</v>
+        <v>-198.7297822375567</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.9271740894411682</v>
+        <v>0.9259642351500651</v>
       </c>
       <c r="T81">
-        <v>4.331581602055039</v>
+        <v>4.324574471369291</v>
       </c>
       <c r="U81">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V81">
-        <v>0.06868116672937802</v>
+        <v>0.07061776369046485</v>
       </c>
       <c r="W81">
-        <v>0.3396042367611431</v>
+        <v>0.3296042367611431</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1962319049410801</v>
+        <v>0.2017650391156139</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8100,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.4661823931989381</v>
+        <v>0.4579283237978063</v>
       </c>
       <c r="C82">
-        <v>-605.6084929973448</v>
+        <v>-586.4829912206885</v>
       </c>
       <c r="D82">
-        <v>944.5315070026555</v>
+        <v>963.6570087793118</v>
       </c>
       <c r="E82">
         <v>1127.04</v>
@@ -8005,37 +8133,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M82">
-        <v>569.3771246803869</v>
+        <v>553.7627246803869</v>
       </c>
       <c r="N82">
-        <v>-459.0437913470536</v>
+        <v>-443.4293913470535</v>
       </c>
       <c r="O82">
-        <v>-160.6653269714687</v>
+        <v>-155.2002869714687</v>
       </c>
       <c r="P82">
-        <v>-298.3784643755848</v>
+        <v>-288.2291043755848</v>
       </c>
       <c r="Q82">
-        <v>-213.3784643755848</v>
+        <v>-203.2291043755848</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.9712427939132267</v>
+        <v>0.9699724469075682</v>
       </c>
       <c r="T82">
-        <v>4.548160682157791</v>
+        <v>4.540803194937755</v>
       </c>
       <c r="U82">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V82">
-        <v>0.06782265214526079</v>
+        <v>0.06973504164433404</v>
       </c>
       <c r="W82">
-        <v>0.3399172930203659</v>
+        <v>0.3299172930203659</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1937790061293166</v>
+        <v>0.1992429761266687</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8182,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.4693708805739277</v>
+        <v>0.461016811172796</v>
       </c>
       <c r="C83">
-        <v>-632.236582296395</v>
+        <v>-613.1689151229718</v>
       </c>
       <c r="D83">
-        <v>937.4214177036054</v>
+        <v>956.4890848770285</v>
       </c>
       <c r="E83">
         <v>1146.558</v>
@@ -8087,37 +8215,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M83">
-        <v>576.4943387388918</v>
+        <v>560.6847587388918</v>
       </c>
       <c r="N83">
-        <v>-466.1610054055584</v>
+        <v>-450.3514254055584</v>
       </c>
       <c r="O83">
-        <v>-163.1563518919454</v>
+        <v>-157.6229988919454</v>
       </c>
       <c r="P83">
-        <v>-303.004653513613</v>
+        <v>-292.728426513613</v>
       </c>
       <c r="Q83">
-        <v>-218.004653513613</v>
+        <v>-207.728426513613</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>1.019950309382344</v>
+        <v>1.018613102007967</v>
       </c>
       <c r="T83">
-        <v>4.787537560166096</v>
+        <v>4.779792836776585</v>
       </c>
       <c r="U83">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V83">
-        <v>0.06698533545210943</v>
+        <v>0.06887411520428054</v>
       </c>
       <c r="W83">
-        <v>0.3402226194954104</v>
+        <v>0.3302226194954104</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1913866727203127</v>
+        <v>0.1967831862979444</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8264,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.4725593679489174</v>
+        <v>0.4641052985477857</v>
       </c>
       <c r="C84">
-        <v>-658.7584270385933</v>
+        <v>-639.7489926850151</v>
       </c>
       <c r="D84">
-        <v>930.4175729614071</v>
+        <v>949.4270073149853</v>
       </c>
       <c r="E84">
         <v>1166.076</v>
@@ -8169,37 +8297,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M84">
-        <v>583.6115527973966</v>
+        <v>567.6067927973966</v>
       </c>
       <c r="N84">
-        <v>-473.2782194640632</v>
+        <v>-457.2734594640632</v>
       </c>
       <c r="O84">
-        <v>-165.6473768124221</v>
+        <v>-160.0457108124221</v>
       </c>
       <c r="P84">
-        <v>-307.6308426516411</v>
+        <v>-297.2277486516411</v>
       </c>
       <c r="Q84">
-        <v>-222.6308426516411</v>
+        <v>-212.2277486516411</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>1.074069771014696</v>
+        <v>1.072658274341743</v>
       </c>
       <c r="T84">
-        <v>5.053511869064213</v>
+        <v>5.045336883264174</v>
       </c>
       <c r="U84">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V84">
-        <v>0.0661684411173276</v>
+        <v>0.068034186970082</v>
       </c>
       <c r="W84">
-        <v>0.3405204989832586</v>
+        <v>0.3305204989832586</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1890526889066504</v>
+        <v>0.1943833913430915</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8346,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.4757478553239071</v>
+        <v>0.4671937859227754</v>
       </c>
       <c r="C85">
-        <v>-685.1763909484516</v>
+        <v>-666.2255512198674</v>
       </c>
       <c r="D85">
-        <v>923.5176090515488</v>
+        <v>942.468448780133</v>
       </c>
       <c r="E85">
         <v>1185.594000000001</v>
@@ -8251,37 +8379,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M85">
-        <v>590.7287668559014</v>
+        <v>574.5288268559015</v>
       </c>
       <c r="N85">
-        <v>-480.3954335225681</v>
+        <v>-464.1954935225681</v>
       </c>
       <c r="O85">
-        <v>-168.1384017328988</v>
+        <v>-162.4684227328988</v>
       </c>
       <c r="P85">
-        <v>-312.2570317896692</v>
+        <v>-301.7270707896693</v>
       </c>
       <c r="Q85">
-        <v>-227.2570317896692</v>
+        <v>-216.7270707896693</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>1.134556228133208</v>
+        <v>1.133061702244198</v>
       </c>
       <c r="T85">
-        <v>5.350777273126814</v>
+        <v>5.342121405809126</v>
       </c>
       <c r="U85">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V85">
-        <v>0.0653712309833839</v>
+        <v>0.06721449797044245</v>
       </c>
       <c r="W85">
-        <v>0.3408112006521226</v>
+        <v>0.3308112006521226</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1867749456668112</v>
+        <v>0.1920414227726928</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8428,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.4789363426988967</v>
+        <v>0.4702822732977651</v>
       </c>
       <c r="C86">
-        <v>-711.4927681492501</v>
+        <v>-692.6008503074586</v>
       </c>
       <c r="D86">
-        <v>916.7192318507501</v>
+        <v>935.6111496925416</v>
       </c>
       <c r="E86">
         <v>1205.112</v>
@@ -8333,37 +8461,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M86">
-        <v>597.8459809144063</v>
+        <v>581.4508609144062</v>
       </c>
       <c r="N86">
-        <v>-487.5126475810729</v>
+        <v>-471.1175275810729</v>
       </c>
       <c r="O86">
-        <v>-170.6294266533755</v>
+        <v>-164.8911346533755</v>
       </c>
       <c r="P86">
-        <v>-316.8832209276974</v>
+        <v>-306.2263929276974</v>
       </c>
       <c r="Q86">
-        <v>-231.8832209276974</v>
+        <v>-221.2263929276974</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>1.202603492391533</v>
+        <v>1.20101555863446</v>
       </c>
       <c r="T86">
-        <v>5.685200852697237</v>
+        <v>5.676003993672193</v>
       </c>
       <c r="U86">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V86">
-        <v>0.06459300204310552</v>
+        <v>0.06641432537555624</v>
       </c>
       <c r="W86">
-        <v>0.3410949808526803</v>
+        <v>0.3310949808526802</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.184551434408873</v>
+        <v>0.1897552153587322</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8510,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.4821248300738864</v>
+        <v>0.4733707606727547</v>
       </c>
       <c r="C87">
-        <v>-737.7097857061271</v>
+        <v>-718.8770842408978</v>
       </c>
       <c r="D87">
-        <v>910.0202142938731</v>
+        <v>928.8529157591024</v>
       </c>
       <c r="E87">
         <v>1224.63</v>
@@ -8415,37 +8543,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M87">
-        <v>604.9631949729111</v>
+        <v>588.372894972911</v>
       </c>
       <c r="N87">
-        <v>-494.6298616395777</v>
+        <v>-478.0395616395776</v>
       </c>
       <c r="O87">
-        <v>-173.1204515738522</v>
+        <v>-167.3138465738522</v>
       </c>
       <c r="P87">
-        <v>-321.5094100657255</v>
+        <v>-310.7257150657255</v>
       </c>
       <c r="Q87">
-        <v>-236.5094100657255</v>
+        <v>-225.7257150657255</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>1.279723725217635</v>
+        <v>1.278029929210091</v>
       </c>
       <c r="T87">
-        <v>6.064214242877053</v>
+        <v>6.054404259917006</v>
       </c>
       <c r="U87">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V87">
-        <v>0.06383308437201017</v>
+        <v>0.06563298037113793</v>
       </c>
       <c r="W87">
-        <v>0.3413720838720483</v>
+        <v>0.3313720838720483</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1823802410628862</v>
+        <v>0.1875228010603941</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8592,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.4853133174488761</v>
+        <v>0.4764592480477444</v>
       </c>
       <c r="C88">
-        <v>-763.8296060584739</v>
+        <v>-745.0563843675034</v>
       </c>
       <c r="D88">
-        <v>903.4183939415263</v>
+        <v>922.1916156324969</v>
       </c>
       <c r="E88">
         <v>1244.148</v>
@@ -8497,37 +8625,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M88">
-        <v>612.0804090314159</v>
+        <v>595.2949290314159</v>
       </c>
       <c r="N88">
-        <v>-501.7470756980825</v>
+        <v>-484.9615956980825</v>
       </c>
       <c r="O88">
-        <v>-175.6114764943289</v>
+        <v>-169.7365584943289</v>
       </c>
       <c r="P88">
-        <v>-326.1355992037537</v>
+        <v>-315.2250372037537</v>
       </c>
       <c r="Q88">
-        <v>-241.1355992037537</v>
+        <v>-230.2250372037537</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>1.367861134161752</v>
+        <v>1.366046352725097</v>
       </c>
       <c r="T88">
-        <v>6.497372403082556</v>
+        <v>6.486861707053935</v>
       </c>
       <c r="U88">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V88">
-        <v>0.06309083920489376</v>
+        <v>0.06486980618077585</v>
       </c>
       <c r="W88">
-        <v>0.341642742635152</v>
+        <v>0.331642742635152</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1802595405854108</v>
+        <v>0.1853423033736453</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8674,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.4885018048238657</v>
+        <v>0.4795477354227341</v>
       </c>
       <c r="C89">
-        <v>-789.8543293472169</v>
+        <v>-771.1408213298232</v>
       </c>
       <c r="D89">
-        <v>896.9116706527834</v>
+        <v>915.6251786701771</v>
       </c>
       <c r="E89">
         <v>1263.666</v>
@@ -8579,37 +8707,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M89">
-        <v>619.1976230899207</v>
+        <v>602.2169630899208</v>
       </c>
       <c r="N89">
-        <v>-508.8642897565874</v>
+        <v>-491.8836297565874</v>
       </c>
       <c r="O89">
-        <v>-178.1025014148056</v>
+        <v>-172.1592704148056</v>
       </c>
       <c r="P89">
-        <v>-330.7617883417818</v>
+        <v>-319.7243593417818</v>
       </c>
       <c r="Q89">
-        <v>-245.7617883417818</v>
+        <v>-234.7243593417818</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>1.469558144481887</v>
+        <v>1.467603764473182</v>
       </c>
       <c r="T89">
-        <v>6.997170280242753</v>
+        <v>6.985851069135007</v>
       </c>
       <c r="U89">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V89">
-        <v>0.0623656571450674</v>
+        <v>0.06412417622467498</v>
       </c>
       <c r="W89">
-        <v>0.3419071793577246</v>
+        <v>0.3319071793577246</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1781875918430498</v>
+        <v>0.1832119320705</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8756,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.4916902921988554</v>
+        <v>0.4826362227977237</v>
       </c>
       <c r="C90">
-        <v>-815.7859956422477</v>
+        <v>-797.1324072115848</v>
       </c>
       <c r="D90">
-        <v>890.4980043577524</v>
+        <v>909.1515927884153</v>
       </c>
       <c r="E90">
         <v>1283.184</v>
@@ -8661,37 +8789,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M90">
-        <v>626.3148371484256</v>
+        <v>609.1389971484255</v>
       </c>
       <c r="N90">
-        <v>-515.9815038150922</v>
+        <v>-498.8056638150921</v>
       </c>
       <c r="O90">
-        <v>-180.5935263352823</v>
+        <v>-174.5819823352822</v>
       </c>
       <c r="P90">
-        <v>-335.3879774798099</v>
+        <v>-324.2236814798099</v>
       </c>
       <c r="Q90">
-        <v>-250.3879774798099</v>
+        <v>-239.2236814798099</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>1.588204656522044</v>
+        <v>1.586087411512614</v>
       </c>
       <c r="T90">
-        <v>7.580267803596318</v>
+        <v>7.568005324896259</v>
       </c>
       <c r="U90">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V90">
-        <v>0.06165695649569163</v>
+        <v>0.06339549240394005</v>
       </c>
       <c r="W90">
-        <v>0.3421656061547842</v>
+        <v>0.3321656061547842</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1761627328448333</v>
+        <v>0.1811299782969716</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8838,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.4948787795738451</v>
+        <v>0.4857247101727133</v>
       </c>
       <c r="C91">
-        <v>-841.6265870749637</v>
+        <v>-823.0330975932557</v>
       </c>
       <c r="D91">
-        <v>884.1754129250364</v>
+        <v>902.7689024067445</v>
       </c>
       <c r="E91">
         <v>1302.702</v>
@@ -8743,37 +8871,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M91">
-        <v>633.4320512069304</v>
+        <v>616.0610312069304</v>
       </c>
       <c r="N91">
-        <v>-523.098717873597</v>
+        <v>-505.727697873597</v>
       </c>
       <c r="O91">
-        <v>-183.084551255759</v>
+        <v>-177.0046942557589</v>
       </c>
       <c r="P91">
-        <v>-340.0141666178381</v>
+        <v>-328.7230036178381</v>
       </c>
       <c r="Q91">
-        <v>-255.0141666178381</v>
+        <v>-243.7230036178381</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>1.728423261660412</v>
+        <v>1.726113539831942</v>
       </c>
       <c r="T91">
-        <v>8.269383058468712</v>
+        <v>8.256005808977736</v>
       </c>
       <c r="U91">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V91">
-        <v>0.06096418170360521</v>
+        <v>0.06268318350052499</v>
       </c>
       <c r="W91">
-        <v>0.3424182256080896</v>
+        <v>0.3324182256080896</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.174183376296015</v>
+        <v>0.1790948100015001</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8920,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.4980672669488347</v>
+        <v>0.488813197547703</v>
       </c>
       <c r="C92">
-        <v>-867.3780298806016</v>
+        <v>-848.8447935216174</v>
       </c>
       <c r="D92">
-        <v>877.9419701193985</v>
+        <v>896.4752064783828</v>
       </c>
       <c r="E92">
         <v>1322.22</v>
@@ -8825,37 +8953,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M92">
-        <v>640.5492652654352</v>
+        <v>622.9830652654352</v>
       </c>
       <c r="N92">
-        <v>-530.2159319321019</v>
+        <v>-512.6497319321019</v>
       </c>
       <c r="O92">
-        <v>-185.5755761762356</v>
+        <v>-179.4274061762356</v>
       </c>
       <c r="P92">
-        <v>-344.6403557558662</v>
+        <v>-333.2223257558662</v>
       </c>
       <c r="Q92">
-        <v>-259.6403557558662</v>
+        <v>-248.2223257558662</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>1.896685587826453</v>
+        <v>1.894144893815137</v>
       </c>
       <c r="T92">
-        <v>9.096321364315582</v>
+        <v>9.08160638987551</v>
       </c>
       <c r="U92">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V92">
-        <v>0.06028680190689849</v>
+        <v>0.06198670368385249</v>
       </c>
       <c r="W92">
-        <v>0.342665231295766</v>
+        <v>0.332665231295766</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1722480054482814</v>
+        <v>0.17710486766815</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +9002,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.5012557543238244</v>
+        <v>0.4919016849226927</v>
       </c>
       <c r="C93">
-        <v>-893.0421963547857</v>
+        <v>-874.5693433975265</v>
       </c>
       <c r="D93">
-        <v>871.7958036452145</v>
+        <v>890.2686566024737</v>
       </c>
       <c r="E93">
         <v>1341.738</v>
@@ -8907,37 +9035,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M93">
-        <v>647.6664793239401</v>
+        <v>629.90509932394</v>
       </c>
       <c r="N93">
-        <v>-537.3331459906067</v>
+        <v>-519.5717659906067</v>
       </c>
       <c r="O93">
-        <v>-188.0666010967123</v>
+        <v>-181.8501180967123</v>
       </c>
       <c r="P93">
-        <v>-349.2665448938943</v>
+        <v>-337.7216478938943</v>
       </c>
       <c r="Q93">
-        <v>-264.2665448938943</v>
+        <v>-252.7216478938943</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>2.102339542029393</v>
+        <v>2.099516548683485</v>
       </c>
       <c r="T93">
-        <v>10.10702373812843</v>
+        <v>10.09067376652835</v>
       </c>
       <c r="U93">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V93">
-        <v>0.05962430957825125</v>
+        <v>0.06130553111589807</v>
       </c>
       <c r="W93">
-        <v>0.34290680828701</v>
+        <v>0.33290680828701</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.170355170223575</v>
+        <v>0.1751586603311374</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9084,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.5044442416988141</v>
+        <v>0.4949901722976824</v>
       </c>
       <c r="C94">
-        <v>-918.6209067284639</v>
+        <v>-900.2085447857964</v>
       </c>
       <c r="D94">
-        <v>865.7350932715364</v>
+        <v>884.1474552142038</v>
       </c>
       <c r="E94">
         <v>1361.256</v>
@@ -8989,37 +9117,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M94">
-        <v>654.7836933824449</v>
+        <v>636.8271333824449</v>
       </c>
       <c r="N94">
-        <v>-544.4503600491115</v>
+        <v>-526.4938000491115</v>
       </c>
       <c r="O94">
-        <v>-190.557626017189</v>
+        <v>-184.272830017189</v>
       </c>
       <c r="P94">
-        <v>-353.8927340319225</v>
+        <v>-342.2209700319225</v>
       </c>
       <c r="Q94">
-        <v>-268.8927340319225</v>
+        <v>-257.2209700319225</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>2.359406984783067</v>
+        <v>2.356231117268921</v>
       </c>
       <c r="T94">
-        <v>11.37040170539448</v>
+        <v>11.35200798734439</v>
       </c>
       <c r="U94">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V94">
-        <v>0.05897621925674852</v>
+        <v>0.060639166647247</v>
       </c>
       <c r="W94">
-        <v>0.3431431336045312</v>
+        <v>0.3331431336045312</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1685034835907101</v>
+        <v>0.1732547618492772</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9166,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.5076327290738037</v>
+        <v>0.4980786596726721</v>
       </c>
       <c r="C95">
-        <v>-944.1159309651778</v>
+        <v>-925.7641461509252</v>
       </c>
       <c r="D95">
-        <v>859.7580690348225</v>
+        <v>878.1098538490751</v>
       </c>
       <c r="E95">
         <v>1380.774</v>
@@ -9071,37 +9199,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M95">
-        <v>661.9009074409497</v>
+        <v>643.7491674409497</v>
       </c>
       <c r="N95">
-        <v>-551.5675741076163</v>
+        <v>-533.4158341076163</v>
       </c>
       <c r="O95">
-        <v>-193.0486509376657</v>
+        <v>-186.6955419376657</v>
       </c>
       <c r="P95">
-        <v>-358.5189231699507</v>
+        <v>-346.7202921699507</v>
       </c>
       <c r="Q95">
-        <v>-273.5189231699507</v>
+        <v>-261.7202921699507</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>2.689922268323506</v>
+        <v>2.686292705450196</v>
       </c>
       <c r="T95">
-        <v>12.99474480616512</v>
+        <v>12.97372341410788</v>
       </c>
       <c r="U95">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V95">
-        <v>0.05834206636151466</v>
+        <v>0.0599871325972766</v>
       </c>
       <c r="W95">
-        <v>0.3433743766571596</v>
+        <v>0.3333743766571596</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1666916181757563</v>
+        <v>0.1713918074207903</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9248,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.5108212164487934</v>
+        <v>0.5011671470476617</v>
       </c>
       <c r="C96">
-        <v>-969.528990484392</v>
+        <v>-951.2378485221878</v>
       </c>
       <c r="D96">
-        <v>853.8630095156083</v>
+        <v>872.1541514778124</v>
       </c>
       <c r="E96">
         <v>1400.292</v>
@@ -9153,37 +9281,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M96">
-        <v>669.0181214994547</v>
+        <v>650.6712014994546</v>
       </c>
       <c r="N96">
-        <v>-558.6847881661213</v>
+        <v>-540.3378681661212</v>
       </c>
       <c r="O96">
-        <v>-195.5396758581424</v>
+        <v>-189.1182538581424</v>
       </c>
       <c r="P96">
-        <v>-363.1451123079788</v>
+        <v>-351.2196143079788</v>
       </c>
       <c r="Q96">
-        <v>-278.1451123079788</v>
+        <v>-266.2196143079788</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>3.130609313044091</v>
+        <v>3.12637482302523</v>
       </c>
       <c r="T96">
-        <v>15.16053560719265</v>
+        <v>15.13601064979253</v>
       </c>
       <c r="U96">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V96">
-        <v>0.05772140608107301</v>
+        <v>0.05934897161219919</v>
       </c>
       <c r="W96">
-        <v>0.3436006996448384</v>
+        <v>0.3336006996448384</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1649183030887801</v>
+        <v>0.1695684903205692</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9330,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.5140097038237832</v>
+        <v>0.5042556344226514</v>
       </c>
       <c r="C97">
-        <v>-994.8617598144098</v>
+        <v>-976.6313070914262</v>
       </c>
       <c r="D97">
-        <v>848.0482401855905</v>
+        <v>866.2786929085742</v>
       </c>
       <c r="E97">
         <v>1419.81</v>
@@ -9235,37 +9363,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M97">
-        <v>676.1353355579595</v>
+        <v>657.5932355579595</v>
       </c>
       <c r="N97">
-        <v>-565.8020022246261</v>
+        <v>-547.2599022246261</v>
       </c>
       <c r="O97">
-        <v>-198.0307007786191</v>
+        <v>-191.5409657786191</v>
       </c>
       <c r="P97">
-        <v>-367.771301446007</v>
+        <v>-355.718936446007</v>
       </c>
       <c r="Q97">
-        <v>-282.771301446007</v>
+        <v>-270.718936446007</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>3.747571175652911</v>
+        <v>3.742489787630277</v>
       </c>
       <c r="T97">
-        <v>18.19264272863118</v>
+        <v>18.16321277975104</v>
       </c>
       <c r="U97">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V97">
-        <v>0.0571138123328512</v>
+        <v>0.05872424559522867</v>
       </c>
       <c r="W97">
-        <v>0.3438222579380398</v>
+        <v>0.3338222579380397</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1631823209510035</v>
+        <v>0.1677835588435105</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9412,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.5171981911987727</v>
+        <v>0.5073441217976411</v>
       </c>
       <c r="C98">
-        <v>-1020.115868178206</v>
+        <v>-1001.946132746685</v>
       </c>
       <c r="D98">
-        <v>842.3121318217939</v>
+        <v>860.481867253315</v>
       </c>
       <c r="E98">
         <v>1439.328</v>
@@ -9317,37 +9445,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M98">
-        <v>683.2525496164642</v>
+        <v>664.5152696164643</v>
       </c>
       <c r="N98">
-        <v>-572.9192162831308</v>
+        <v>-554.1819362831309</v>
       </c>
       <c r="O98">
-        <v>-200.5217256990958</v>
+        <v>-193.9636776990958</v>
       </c>
       <c r="P98">
-        <v>-372.397490584035</v>
+        <v>-360.2182585840351</v>
       </c>
       <c r="Q98">
-        <v>-287.397490584035</v>
+        <v>-275.2182585840351</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>4.673013969566129</v>
+        <v>4.666662234537838</v>
       </c>
       <c r="T98">
-        <v>22.74080341078893</v>
+        <v>22.70401597468876</v>
       </c>
       <c r="U98">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V98">
-        <v>0.05651887678771733</v>
+        <v>0.0581125347036117</v>
       </c>
       <c r="W98">
-        <v>0.3440392004334661</v>
+        <v>0.3340392004334661</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1614825051077639</v>
+        <v>0.1660358134388906</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9494,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.5203866785737624</v>
+        <v>0.5104326091726308</v>
       </c>
       <c r="C99">
-        <v>-1045.292901015338</v>
+        <v>-1027.183893544688</v>
       </c>
       <c r="D99">
-        <v>836.6530989846617</v>
+        <v>854.7621064553119</v>
       </c>
       <c r="E99">
         <v>1458.846</v>
@@ -9399,37 +9527,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M99">
-        <v>690.369763674969</v>
+        <v>671.437303674969</v>
       </c>
       <c r="N99">
-        <v>-580.0364303416357</v>
+        <v>-561.1039703416357</v>
       </c>
       <c r="O99">
-        <v>-203.0127506195725</v>
+        <v>-196.3863896195725</v>
       </c>
       <c r="P99">
-        <v>-377.0236797220632</v>
+        <v>-364.7175807220632</v>
       </c>
       <c r="Q99">
-        <v>-292.0236797220632</v>
+        <v>-279.7175807220632</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>6.215418626088171</v>
+        <v>6.20694964605045</v>
       </c>
       <c r="T99">
-        <v>30.32107121438524</v>
+        <v>30.27202129958501</v>
       </c>
       <c r="U99">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V99">
-        <v>0.05593620795485427</v>
+        <v>0.05751343640769818</v>
       </c>
       <c r="W99">
-        <v>0.3442516698877496</v>
+        <v>0.3342516698877496</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1598177370138694</v>
+        <v>0.1643241040219948</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9576,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.5235751659487522</v>
+        <v>0.5135210965476205</v>
       </c>
       <c r="C100">
-        <v>-1070.394401442912</v>
+        <v>-1052.346116124967</v>
       </c>
       <c r="D100">
-        <v>831.0695985570885</v>
+        <v>849.1178838750334</v>
       </c>
       <c r="E100">
         <v>1478.364</v>
@@ -9481,37 +9609,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M100">
-        <v>697.486977733474</v>
+        <v>678.3593377334739</v>
       </c>
       <c r="N100">
-        <v>-587.1536444001406</v>
+        <v>-568.0260044001406</v>
       </c>
       <c r="O100">
-        <v>-205.5037755400492</v>
+        <v>-198.8091015400492</v>
       </c>
       <c r="P100">
-        <v>-381.6498688600914</v>
+        <v>-369.2169028600914</v>
       </c>
       <c r="Q100">
-        <v>-296.6498688600914</v>
+        <v>-284.2169028600914</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>9.300227939132258</v>
+        <v>9.287524469075676</v>
       </c>
       <c r="T100">
-        <v>45.48160682157786</v>
+        <v>45.40803194937752</v>
       </c>
       <c r="U100">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V100">
-        <v>0.05536543032266188</v>
+        <v>0.05692656460761963</v>
       </c>
       <c r="W100">
-        <v>0.3444598032307212</v>
+        <v>0.3344598032307212</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +9647,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.158186943779034</v>
+        <v>0.1626473274503418</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9658,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.5267636533237416</v>
+        <v>0.5166095839226101</v>
       </c>
       <c r="C101">
-        <v>-1095.421871658436</v>
+        <v>-1077.434287068337</v>
       </c>
       <c r="D101">
-        <v>825.5601283415646</v>
+        <v>843.5477129316629</v>
       </c>
       <c r="E101">
         <v>1497.882</v>
@@ -9563,37 +9691,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M101">
-        <v>704.6041917919788</v>
+        <v>685.2813717919787</v>
       </c>
       <c r="N101">
-        <v>-594.2708584586454</v>
+        <v>-574.9480384586453</v>
       </c>
       <c r="O101">
-        <v>-207.9948004605259</v>
+        <v>-201.2318134605258</v>
       </c>
       <c r="P101">
-        <v>-386.2760579981195</v>
+        <v>-373.7162249981195</v>
       </c>
       <c r="Q101">
-        <v>-301.2760579981195</v>
+        <v>-288.7162249981195</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>18.55465587826452</v>
+        <v>18.52924893815135</v>
       </c>
       <c r="T101">
-        <v>90.96321364315573</v>
+        <v>90.81606389875502</v>
       </c>
       <c r="U101">
-        <v>0.3646487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V101">
-        <v>0.0548061835517259</v>
+        <v>0.05635154880350226</v>
       </c>
       <c r="W101">
-        <v>0.3446637318596933</v>
+        <v>0.3346637318596934</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +9729,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.156589095862074</v>
+        <v>0.1610044251528636</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/argentina/argentina_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_oil_gas_production_and_exploration.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2415552921411639</v>
+        <v>0.2415116154124131</v>
       </c>
       <c r="C2">
-        <v>2040.110273276448</v>
+        <v>2021.04504045537</v>
       </c>
       <c r="D2">
-        <v>2028.810273276448</v>
+        <v>2029.26304045537</v>
       </c>
       <c r="E2">
-        <v>-434.4</v>
+        <v>-414.8819999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.518</v>
       </c>
       <c r="G2">
         <v>11.3</v>
@@ -1573,28 +1573,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.301445058504835</v>
       </c>
       <c r="N2">
-        <v>110.3333333333333</v>
+        <v>107.0318882748285</v>
       </c>
       <c r="O2">
-        <v>38.61666666666667</v>
+        <v>37.46116089618997</v>
       </c>
       <c r="P2">
-        <v>71.71666666666667</v>
+        <v>69.57072737863854</v>
       </c>
       <c r="Q2">
-        <v>156.7166666666667</v>
+        <v>154.5707273786385</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2415552921411639</v>
+        <v>0.2428405541602726</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9681335781619097</v>
       </c>
       <c r="U2">
         <v>0.1691487374989669</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>33.41970906015965</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2415116154124131</v>
+        <v>0.2414679386836623</v>
       </c>
       <c r="C3">
-        <v>2021.04504045537</v>
+        <v>2001.98000976643</v>
       </c>
       <c r="D3">
-        <v>2029.26304045537</v>
+        <v>2029.71600976643</v>
       </c>
       <c r="E3">
-        <v>-414.8819999999999</v>
+        <v>-395.364</v>
       </c>
       <c r="F3">
-        <v>19.518</v>
+        <v>39.036</v>
       </c>
       <c r="G3">
         <v>11.3</v>
@@ -1655,28 +1655,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M3">
-        <v>3.301445058504835</v>
+        <v>6.602890117009671</v>
       </c>
       <c r="N3">
-        <v>107.0318882748285</v>
+        <v>103.7304432163237</v>
       </c>
       <c r="O3">
-        <v>37.46116089618997</v>
+        <v>36.30565512571329</v>
       </c>
       <c r="P3">
-        <v>69.57072737863854</v>
+        <v>67.42478809061039</v>
       </c>
       <c r="Q3">
-        <v>154.5707273786385</v>
+        <v>152.4247880906104</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2428405541602726</v>
+        <v>0.2441520460165059</v>
       </c>
       <c r="T3">
-        <v>0.9681335781619097</v>
+        <v>0.9745774257694056</v>
       </c>
       <c r="U3">
         <v>0.1691487374989669</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>33.41970906015965</v>
+        <v>16.70985453007982</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2414679386836623</v>
+        <v>0.2414535119549115</v>
       </c>
       <c r="C4">
-        <v>2001.98000976643</v>
+        <v>1982.611673128061</v>
       </c>
       <c r="D4">
-        <v>2029.71600976643</v>
+        <v>2029.865673128061</v>
       </c>
       <c r="E4">
-        <v>-395.364</v>
+        <v>-375.846</v>
       </c>
       <c r="F4">
-        <v>39.036</v>
+        <v>58.554</v>
       </c>
       <c r="G4">
         <v>11.3</v>
@@ -1737,45 +1737,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M4">
-        <v>6.602890117009671</v>
+        <v>9.992166175514505</v>
       </c>
       <c r="N4">
-        <v>103.7304432163237</v>
+        <v>100.3411671578188</v>
       </c>
       <c r="O4">
-        <v>36.30565512571329</v>
+        <v>35.11940850523658</v>
       </c>
       <c r="P4">
-        <v>67.42478809061039</v>
+        <v>65.22175865258225</v>
       </c>
       <c r="Q4">
-        <v>152.4247880906104</v>
+        <v>150.2217586525823</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2441520460165059</v>
+        <v>0.2454905789419399</v>
       </c>
       <c r="T4">
-        <v>0.9745774257694056</v>
+        <v>0.9811541362141696</v>
       </c>
       <c r="U4">
-        <v>0.1691487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V4">
         <v>0.35</v>
       </c>
       <c r="W4">
-        <v>0.1099466793743285</v>
+        <v>0.1109216793743285</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>16.70985453007982</v>
+        <v>11.04198342934906</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2414535119549115</v>
+        <v>0.2414637852261608</v>
       </c>
       <c r="C5">
-        <v>1982.611673128061</v>
+        <v>1962.987095609715</v>
       </c>
       <c r="D5">
-        <v>2029.865673128061</v>
+        <v>2029.759095609715</v>
       </c>
       <c r="E5">
-        <v>-375.846</v>
+        <v>-356.328</v>
       </c>
       <c r="F5">
-        <v>58.554</v>
+        <v>78.072</v>
       </c>
       <c r="G5">
         <v>11.3</v>
@@ -1819,45 +1819,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M5">
-        <v>9.992166175514505</v>
+        <v>13.45561063401934</v>
       </c>
       <c r="N5">
-        <v>100.3411671578188</v>
+        <v>96.87772269931401</v>
       </c>
       <c r="O5">
-        <v>35.11940850523658</v>
+        <v>33.9072029447599</v>
       </c>
       <c r="P5">
-        <v>65.22175865258225</v>
+        <v>62.9705197545541</v>
       </c>
       <c r="Q5">
-        <v>150.2217586525823</v>
+        <v>147.9705197545541</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2454905789419399</v>
+        <v>0.2468569979699871</v>
       </c>
       <c r="T5">
-        <v>0.9811541362141696</v>
+        <v>0.9878678614598663</v>
       </c>
       <c r="U5">
-        <v>0.1706487374989669</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V5">
         <v>0.35</v>
       </c>
       <c r="W5">
-        <v>0.1109216793743285</v>
+        <v>0.1120266793743285</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>11.04198342934906</v>
+        <v>8.199801282476287</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2414637852261608</v>
+        <v>0.2414669084974099</v>
       </c>
       <c r="C6">
-        <v>1962.987095609715</v>
+        <v>1943.436696221006</v>
       </c>
       <c r="D6">
-        <v>2029.759095609715</v>
+        <v>2029.726696221006</v>
       </c>
       <c r="E6">
-        <v>-356.328</v>
+        <v>-336.8099999999999</v>
       </c>
       <c r="F6">
-        <v>78.072</v>
+        <v>97.59000000000002</v>
       </c>
       <c r="G6">
         <v>11.3</v>
@@ -1901,45 +1901,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M6">
-        <v>13.45561063401934</v>
+        <v>16.89758529252418</v>
       </c>
       <c r="N6">
-        <v>96.87772269931401</v>
+        <v>93.43574804080916</v>
       </c>
       <c r="O6">
-        <v>33.9072029447599</v>
+        <v>32.70251181428321</v>
       </c>
       <c r="P6">
-        <v>62.9705197545541</v>
+        <v>60.73323622652595</v>
       </c>
       <c r="Q6">
-        <v>147.9705197545541</v>
+        <v>145.7332362265259</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2468569979699871</v>
+        <v>0.2482521837144142</v>
       </c>
       <c r="T6">
-        <v>0.9878678614598663</v>
+        <v>0.9947229282896827</v>
       </c>
       <c r="U6">
-        <v>0.1723487374989669</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.1120266793743285</v>
+        <v>0.1125466793743285</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.199801282476287</v>
+        <v>6.52953255884123</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2414669084974099</v>
+        <v>0.2414882317686592</v>
       </c>
       <c r="C7">
-        <v>1943.436696221006</v>
+        <v>1923.697525982436</v>
       </c>
       <c r="D7">
-        <v>2029.726696221006</v>
+        <v>2029.505525982436</v>
       </c>
       <c r="E7">
-        <v>-336.8099999999999</v>
+        <v>-317.292</v>
       </c>
       <c r="F7">
-        <v>97.59000000000002</v>
+        <v>117.108</v>
       </c>
       <c r="G7">
         <v>11.3</v>
@@ -1983,45 +1983,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M7">
-        <v>16.89758529252418</v>
+        <v>20.39421035102901</v>
       </c>
       <c r="N7">
-        <v>93.43574804080916</v>
+        <v>89.93912298230433</v>
       </c>
       <c r="O7">
-        <v>32.70251181428321</v>
+        <v>31.47869304380651</v>
       </c>
       <c r="P7">
-        <v>60.73323622652595</v>
+        <v>58.46042993849781</v>
       </c>
       <c r="Q7">
-        <v>145.7332362265259</v>
+        <v>143.4604299384978</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2482521837144142</v>
+        <v>0.2496770542619144</v>
       </c>
       <c r="T7">
-        <v>0.9947229282896827</v>
+        <v>1.00172384760524</v>
       </c>
       <c r="U7">
-        <v>0.1731487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V7">
         <v>0.35</v>
       </c>
       <c r="W7">
-        <v>0.1125466793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.52953255884123</v>
+        <v>5.410032133348391</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2414882317686592</v>
+        <v>0.2414770550399084</v>
       </c>
       <c r="C8">
-        <v>1923.697525982436</v>
+        <v>1904.295447763647</v>
       </c>
       <c r="D8">
-        <v>2029.505525982436</v>
+        <v>2029.621447763647</v>
       </c>
       <c r="E8">
-        <v>-317.292</v>
+        <v>-297.774</v>
       </c>
       <c r="F8">
-        <v>117.108</v>
+        <v>136.626</v>
       </c>
       <c r="G8">
         <v>11.3</v>
@@ -2065,28 +2065,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M8">
-        <v>20.39421035102901</v>
+        <v>23.79324540953385</v>
       </c>
       <c r="N8">
-        <v>89.93912298230433</v>
+        <v>86.54008792379949</v>
       </c>
       <c r="O8">
-        <v>31.47869304380651</v>
+        <v>30.28903077332982</v>
       </c>
       <c r="P8">
-        <v>58.46042993849781</v>
+        <v>56.25105715046967</v>
       </c>
       <c r="Q8">
-        <v>143.4604299384978</v>
+        <v>141.2510571504697</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2496770542619144</v>
+        <v>0.25113256718678</v>
       </c>
       <c r="T8">
-        <v>1.00172384760524</v>
+        <v>1.008875324325433</v>
       </c>
       <c r="U8">
         <v>0.1741487374989669</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.410032133348391</v>
+        <v>4.637170400012907</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2414770550399084</v>
+        <v>0.2415958783111576</v>
       </c>
       <c r="C9">
-        <v>1904.295447763647</v>
+        <v>1883.545724900525</v>
       </c>
       <c r="D9">
-        <v>2029.621447763647</v>
+        <v>2028.389724900525</v>
       </c>
       <c r="E9">
-        <v>-297.7739999999999</v>
+        <v>-278.256</v>
       </c>
       <c r="F9">
-        <v>136.626</v>
+        <v>156.144</v>
       </c>
       <c r="G9">
         <v>11.3</v>
@@ -2147,45 +2147,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M9">
-        <v>23.79324540953385</v>
+        <v>27.58264046803868</v>
       </c>
       <c r="N9">
-        <v>86.54008792379949</v>
+        <v>82.75069286529467</v>
       </c>
       <c r="O9">
-        <v>30.28903077332982</v>
+        <v>28.96274250285313</v>
       </c>
       <c r="P9">
-        <v>56.25105715046967</v>
+        <v>53.78795036244153</v>
       </c>
       <c r="Q9">
-        <v>141.2510571504697</v>
+        <v>138.7879503624415</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.25113256718678</v>
+        <v>0.2526197216969688</v>
       </c>
       <c r="T9">
-        <v>1.008875324325433</v>
+        <v>1.016182267930847</v>
       </c>
       <c r="U9">
-        <v>0.1741487374989669</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.1131966793743285</v>
+        <v>0.1148216793743285</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.637170400012906</v>
+        <v>4.000100478457885</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2415958783111576</v>
+        <v>0.2419695015824068</v>
       </c>
       <c r="C10">
-        <v>1883.545724900525</v>
+        <v>1860.164465840006</v>
       </c>
       <c r="D10">
-        <v>2028.389724900525</v>
+        <v>2024.526465840006</v>
       </c>
       <c r="E10">
-        <v>-278.256</v>
+        <v>-258.7379999999999</v>
       </c>
       <c r="F10">
-        <v>156.144</v>
+        <v>175.662</v>
       </c>
       <c r="G10">
         <v>11.3</v>
@@ -2229,45 +2229,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M10">
-        <v>27.58264046803868</v>
+        <v>32.13714112654352</v>
       </c>
       <c r="N10">
-        <v>82.75069286529467</v>
+        <v>78.19619220678982</v>
       </c>
       <c r="O10">
-        <v>28.96274250285313</v>
+        <v>27.36866727237643</v>
       </c>
       <c r="P10">
-        <v>53.78795036244153</v>
+        <v>50.82752493441338</v>
       </c>
       <c r="Q10">
-        <v>138.7879503624415</v>
+        <v>135.8275249344134</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2526197216969688</v>
+        <v>0.2541395609216673</v>
       </c>
       <c r="T10">
-        <v>1.016182267930847</v>
+        <v>1.023649803703414</v>
       </c>
       <c r="U10">
-        <v>0.1766487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.1148216793743285</v>
+        <v>0.1189166793743285</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.000100478457885</v>
+        <v>3.433203124661392</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2419695015824068</v>
+        <v>0.242015524853656</v>
       </c>
       <c r="C11">
-        <v>1860.164465840006</v>
+        <v>1840.171603666088</v>
       </c>
       <c r="D11">
-        <v>2024.526465840006</v>
+        <v>2024.051603666088</v>
       </c>
       <c r="E11">
-        <v>-258.7379999999999</v>
+        <v>-239.22</v>
       </c>
       <c r="F11">
-        <v>175.662</v>
+        <v>195.18</v>
       </c>
       <c r="G11">
         <v>11.3</v>
@@ -2311,28 +2311,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M11">
-        <v>32.13714112654352</v>
+        <v>35.70793458504836</v>
       </c>
       <c r="N11">
-        <v>78.19619220678982</v>
+        <v>74.62539874828499</v>
       </c>
       <c r="O11">
-        <v>27.36866727237643</v>
+        <v>26.11888956189975</v>
       </c>
       <c r="P11">
-        <v>50.82752493441338</v>
+        <v>48.50650918638524</v>
       </c>
       <c r="Q11">
-        <v>135.8275249344134</v>
+        <v>133.5065091863852</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2541395609216673</v>
+        <v>0.2556931743513591</v>
       </c>
       <c r="T11">
-        <v>1.023649803703414</v>
+        <v>1.031283284715371</v>
       </c>
       <c r="U11">
         <v>0.1829487374989669</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>3.433203124661392</v>
+        <v>3.089882812195253</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.242015524853656</v>
+        <v>0.2426192481249053</v>
       </c>
       <c r="C12">
-        <v>1840.171603666088</v>
+        <v>1814.445028707164</v>
       </c>
       <c r="D12">
-        <v>2024.051603666088</v>
+        <v>2017.843028707164</v>
       </c>
       <c r="E12">
-        <v>-239.2199999999999</v>
+        <v>-219.702</v>
       </c>
       <c r="F12">
-        <v>195.18</v>
+        <v>214.698</v>
       </c>
       <c r="G12">
         <v>11.3</v>
@@ -2393,45 +2393,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M12">
-        <v>35.70793458504836</v>
+        <v>40.95337244355319</v>
       </c>
       <c r="N12">
-        <v>74.62539874828499</v>
+        <v>69.37996088978015</v>
       </c>
       <c r="O12">
-        <v>26.11888956189975</v>
+        <v>24.28298631142305</v>
       </c>
       <c r="P12">
-        <v>48.50650918638524</v>
+        <v>45.0969745783571</v>
       </c>
       <c r="Q12">
-        <v>133.5065091863852</v>
+        <v>130.0969745783571</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2556931743513591</v>
+        <v>0.2572817004423923</v>
       </c>
       <c r="T12">
-        <v>1.031283284715371</v>
+        <v>1.039088304626473</v>
       </c>
       <c r="U12">
-        <v>0.1829487374989669</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.1189166793743285</v>
+        <v>0.1239866793743285</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>3.089882812195253</v>
+        <v>2.694120819607906</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2426192481249053</v>
+        <v>0.2430201713961544</v>
       </c>
       <c r="C13">
-        <v>1814.445028707164</v>
+        <v>1790.825013065409</v>
       </c>
       <c r="D13">
-        <v>2017.843028707164</v>
+        <v>2013.741013065409</v>
       </c>
       <c r="E13">
-        <v>-219.702</v>
+        <v>-200.184</v>
       </c>
       <c r="F13">
-        <v>214.698</v>
+        <v>234.216</v>
       </c>
       <c r="G13">
         <v>11.3</v>
@@ -2475,45 +2475,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M13">
-        <v>40.95337244355319</v>
+        <v>45.58984870205802</v>
       </c>
       <c r="N13">
-        <v>69.37996088978015</v>
+        <v>64.74348463127532</v>
       </c>
       <c r="O13">
-        <v>24.28298631142305</v>
+        <v>22.66021962094636</v>
       </c>
       <c r="P13">
-        <v>45.0969745783571</v>
+        <v>42.08326501032896</v>
       </c>
       <c r="Q13">
-        <v>130.0969745783571</v>
+        <v>127.083265010329</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2572817004423923</v>
+        <v>0.2589063293991307</v>
       </c>
       <c r="T13">
-        <v>1.039088304626473</v>
+        <v>1.047070711353736</v>
       </c>
       <c r="U13">
-        <v>0.1907487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.1239866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y13">
-        <v>2.694120819607906</v>
+        <v>2.420129403244821</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2430201713961544</v>
+        <v>0.2431422446674037</v>
       </c>
       <c r="C14">
-        <v>1790.825013065409</v>
+        <v>1770.061339827385</v>
       </c>
       <c r="D14">
-        <v>2013.741013065409</v>
+        <v>2012.495339827386</v>
       </c>
       <c r="E14">
-        <v>-200.184</v>
+        <v>-180.6659999999999</v>
       </c>
       <c r="F14">
-        <v>234.216</v>
+        <v>253.734</v>
       </c>
       <c r="G14">
         <v>11.3</v>
@@ -2557,28 +2557,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M14">
-        <v>45.58984870205802</v>
+        <v>49.38900276056286</v>
       </c>
       <c r="N14">
-        <v>64.74348463127532</v>
+        <v>60.94433057277048</v>
       </c>
       <c r="O14">
-        <v>22.66021962094636</v>
+        <v>21.33051570046967</v>
       </c>
       <c r="P14">
-        <v>42.08326501032896</v>
+        <v>39.61381487230081</v>
       </c>
       <c r="Q14">
-        <v>127.083265010329</v>
+        <v>124.6138148723008</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2589063293991307</v>
+        <v>0.2605683061479781</v>
       </c>
       <c r="T14">
-        <v>1.047070711353736</v>
+        <v>1.055236621683925</v>
       </c>
       <c r="U14">
         <v>0.1946487374989669</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.420129403244821</v>
+        <v>2.233965602995219</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2431422446674037</v>
+        <v>0.2432643179386529</v>
       </c>
       <c r="C15">
-        <v>1770.061339827385</v>
+        <v>1749.299206750225</v>
       </c>
       <c r="D15">
-        <v>2012.495339827386</v>
+        <v>2011.251206750225</v>
       </c>
       <c r="E15">
-        <v>-180.6659999999999</v>
+        <v>-161.1479999999999</v>
       </c>
       <c r="F15">
-        <v>253.734</v>
+        <v>273.2520000000001</v>
       </c>
       <c r="G15">
         <v>11.3</v>
@@ -2639,28 +2639,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M15">
-        <v>49.38900276056286</v>
+        <v>53.18815681906771</v>
       </c>
       <c r="N15">
-        <v>60.94433057277048</v>
+        <v>57.14517651426564</v>
       </c>
       <c r="O15">
-        <v>21.33051570046967</v>
+        <v>20.00081177999297</v>
       </c>
       <c r="P15">
-        <v>39.61381487230081</v>
+        <v>37.14436473427266</v>
       </c>
       <c r="Q15">
-        <v>124.6138148723008</v>
+        <v>122.1443647342727</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2605683061479781</v>
+        <v>0.2622689335188917</v>
       </c>
       <c r="T15">
-        <v>1.055236621683925</v>
+        <v>1.063592436905514</v>
       </c>
       <c r="U15">
         <v>0.1946487374989669</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>2.233965602995219</v>
+        <v>2.074396631352703</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2432643179386529</v>
+        <v>0.2447708912099021</v>
       </c>
       <c r="C16">
-        <v>1749.299206750225</v>
+        <v>1714.552359498085</v>
       </c>
       <c r="D16">
-        <v>2011.251206750225</v>
+        <v>1996.022359498086</v>
       </c>
       <c r="E16">
-        <v>-161.1479999999999</v>
+        <v>-141.6299999999999</v>
       </c>
       <c r="F16">
-        <v>273.2520000000001</v>
+        <v>292.7700000000001</v>
       </c>
       <c r="G16">
         <v>11.3</v>
@@ -2721,45 +2721,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M16">
-        <v>53.18815681906771</v>
+        <v>61.14464487757255</v>
       </c>
       <c r="N16">
-        <v>57.14517651426564</v>
+        <v>49.18868845576079</v>
       </c>
       <c r="O16">
-        <v>20.00081177999297</v>
+        <v>17.21604095951627</v>
       </c>
       <c r="P16">
-        <v>37.14436473427266</v>
+        <v>31.97264749624452</v>
       </c>
       <c r="Q16">
-        <v>122.1443647342727</v>
+        <v>116.9726474962445</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2622689335188917</v>
+        <v>0.2640095756514739</v>
       </c>
       <c r="T16">
-        <v>1.063592436905514</v>
+        <v>1.072144859544081</v>
       </c>
       <c r="U16">
-        <v>0.1946487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.1265216793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.074396631352703</v>
+        <v>1.804464373850716</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2447708912099021</v>
+        <v>0.2449852644811513</v>
       </c>
       <c r="C17">
-        <v>1714.552359498086</v>
+        <v>1692.886139127433</v>
       </c>
       <c r="D17">
-        <v>1996.022359498086</v>
+        <v>1993.874139127433</v>
       </c>
       <c r="E17">
-        <v>-141.6299999999999</v>
+        <v>-122.112</v>
       </c>
       <c r="F17">
-        <v>292.77</v>
+        <v>312.288</v>
       </c>
       <c r="G17">
         <v>11.3</v>
@@ -2803,28 +2803,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M17">
-        <v>61.14464487757254</v>
+        <v>65.22095453607737</v>
       </c>
       <c r="N17">
-        <v>49.1886884557608</v>
+        <v>45.11237879725597</v>
       </c>
       <c r="O17">
-        <v>17.21604095951628</v>
+        <v>15.78933257903959</v>
       </c>
       <c r="P17">
-        <v>31.97264749624452</v>
+        <v>29.32304621821638</v>
       </c>
       <c r="Q17">
-        <v>116.9726474962445</v>
+        <v>114.3230462182164</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2640095756514739</v>
+        <v>0.2657916616443556</v>
       </c>
       <c r="T17">
-        <v>1.072144859544081</v>
+        <v>1.08090091129309</v>
       </c>
       <c r="U17">
         <v>0.2088487374989669</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>1.804464373850716</v>
+        <v>1.691685350485047</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2449852644811513</v>
+        <v>0.2451996377524005</v>
       </c>
       <c r="C18">
-        <v>1692.886139127433</v>
+        <v>1671.224537832657</v>
       </c>
       <c r="D18">
-        <v>1993.874139127433</v>
+        <v>1991.730537832658</v>
       </c>
       <c r="E18">
-        <v>-122.112</v>
+        <v>-102.5939999999999</v>
       </c>
       <c r="F18">
-        <v>312.288</v>
+        <v>331.806</v>
       </c>
       <c r="G18">
         <v>11.3</v>
@@ -2885,28 +2885,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M18">
-        <v>65.22095453607737</v>
+        <v>69.29726419458221</v>
       </c>
       <c r="N18">
-        <v>45.11237879725597</v>
+        <v>41.03606913875113</v>
       </c>
       <c r="O18">
-        <v>15.78933257903959</v>
+        <v>14.36262419856289</v>
       </c>
       <c r="P18">
-        <v>29.32304621821638</v>
+        <v>26.67344494018824</v>
       </c>
       <c r="Q18">
-        <v>114.3230462182164</v>
+        <v>111.6734449401882</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2657916616443556</v>
+        <v>0.2676166894683911</v>
       </c>
       <c r="T18">
-        <v>1.08090091129309</v>
+        <v>1.089867952240871</v>
       </c>
       <c r="U18">
         <v>0.2088487374989669</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>1.691685350485047</v>
+        <v>1.592174447515338</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2451996377524005</v>
+        <v>0.2454140110236497</v>
       </c>
       <c r="C19">
-        <v>1671.224537832657</v>
+        <v>1649.56754073194</v>
       </c>
       <c r="D19">
-        <v>1991.730537832658</v>
+        <v>1989.59154073194</v>
       </c>
       <c r="E19">
-        <v>-102.5939999999999</v>
+        <v>-83.07599999999991</v>
       </c>
       <c r="F19">
-        <v>331.806</v>
+        <v>351.3240000000001</v>
       </c>
       <c r="G19">
         <v>11.3</v>
@@ -2967,28 +2967,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M19">
-        <v>69.29726419458221</v>
+        <v>73.37357385308705</v>
       </c>
       <c r="N19">
-        <v>41.03606913875113</v>
+        <v>36.95975948024629</v>
       </c>
       <c r="O19">
-        <v>14.36262419856289</v>
+        <v>12.9359158180862</v>
       </c>
       <c r="P19">
-        <v>26.67344494018824</v>
+        <v>24.02384366216009</v>
       </c>
       <c r="Q19">
-        <v>111.6734449401882</v>
+        <v>109.0238436621601</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2676166894683911</v>
+        <v>0.2694862301661836</v>
       </c>
       <c r="T19">
-        <v>1.089867952240871</v>
+        <v>1.099053701504451</v>
       </c>
       <c r="U19">
         <v>0.2088487374989669</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.592174447515338</v>
+        <v>1.503720311542263</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2454140110236497</v>
+        <v>0.249160484294899</v>
       </c>
       <c r="C20">
-        <v>1649.56754073194</v>
+        <v>1593.395657093235</v>
       </c>
       <c r="D20">
-        <v>1989.59154073194</v>
+        <v>1952.937657093235</v>
       </c>
       <c r="E20">
-        <v>-83.07599999999996</v>
+        <v>-63.55799999999994</v>
       </c>
       <c r="F20">
-        <v>351.324</v>
+        <v>370.842</v>
       </c>
       <c r="G20">
         <v>11.3</v>
@@ -3049,45 +3049,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M20">
-        <v>73.37357385308704</v>
+        <v>88.05596471159188</v>
       </c>
       <c r="N20">
-        <v>36.9597594802463</v>
+        <v>22.27736862174146</v>
       </c>
       <c r="O20">
-        <v>12.93591581808621</v>
+        <v>7.79707901760951</v>
       </c>
       <c r="P20">
-        <v>24.0238436621601</v>
+        <v>14.48028960413195</v>
       </c>
       <c r="Q20">
-        <v>109.0238436621601</v>
+        <v>99.48028960413195</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2694862301661836</v>
+        <v>0.2714019323626871</v>
       </c>
       <c r="T20">
-        <v>1.099053701504451</v>
+        <v>1.108466259391824</v>
       </c>
       <c r="U20">
-        <v>0.2088487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.1357516793743285</v>
+        <v>0.1543416793743285</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.503720311542264</v>
+        <v>1.25299102331916</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.249160484294899</v>
+        <v>0.2532267575661482</v>
       </c>
       <c r="C21">
-        <v>1593.395657093235</v>
+        <v>1535.593405395757</v>
       </c>
       <c r="D21">
-        <v>1952.937657093235</v>
+        <v>1914.653405395757</v>
       </c>
       <c r="E21">
-        <v>-63.55799999999994</v>
+        <v>-44.03999999999991</v>
       </c>
       <c r="F21">
-        <v>370.842</v>
+        <v>390.3600000000001</v>
       </c>
       <c r="G21">
         <v>11.3</v>
@@ -3131,45 +3131,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M21">
-        <v>88.05596471159188</v>
+        <v>103.6986411700967</v>
       </c>
       <c r="N21">
-        <v>22.27736862174146</v>
+        <v>6.634692163236636</v>
       </c>
       <c r="O21">
-        <v>7.79707901760951</v>
+        <v>2.322142257132823</v>
       </c>
       <c r="P21">
-        <v>14.48028960413195</v>
+        <v>4.312549906103813</v>
       </c>
       <c r="Q21">
-        <v>99.48028960413195</v>
+        <v>89.31254990610381</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2714019323626871</v>
+        <v>0.2733655271141031</v>
       </c>
       <c r="T21">
-        <v>1.108466259391824</v>
+        <v>1.11811413122638</v>
       </c>
       <c r="U21">
-        <v>0.2374487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V21">
         <v>0.35</v>
       </c>
       <c r="W21">
-        <v>0.1543416793743285</v>
+        <v>0.1726716793743285</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.25299102331916</v>
+        <v>1.063980512072032</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2532267575661482</v>
+        <v>0.2538103308373973</v>
       </c>
       <c r="C22">
-        <v>1535.593405395757</v>
+        <v>1510.703842615211</v>
       </c>
       <c r="D22">
-        <v>1914.653405395757</v>
+        <v>1909.281842615211</v>
       </c>
       <c r="E22">
-        <v>-44.03999999999991</v>
+        <v>-24.52199999999988</v>
       </c>
       <c r="F22">
-        <v>390.3600000000001</v>
+        <v>409.8780000000001</v>
       </c>
       <c r="G22">
         <v>11.3</v>
@@ -3213,28 +3213,28 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M22">
-        <v>103.6986411700967</v>
+        <v>108.8835732286015</v>
       </c>
       <c r="N22">
-        <v>6.634692163236636</v>
+        <v>1.449760104731794</v>
       </c>
       <c r="O22">
-        <v>2.322142257132823</v>
+        <v>0.507416036656128</v>
       </c>
       <c r="P22">
-        <v>4.312549906103813</v>
+        <v>0.9423440680756663</v>
       </c>
       <c r="Q22">
-        <v>89.31254990610381</v>
+        <v>85.94234406807567</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2733655271141031</v>
+        <v>0.2753788331250486</v>
       </c>
       <c r="T22">
-        <v>1.11811413122638</v>
+        <v>1.128006252980799</v>
       </c>
       <c r="U22">
         <v>0.2656487374989668</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>1.063980512072032</v>
+        <v>1.013314773401935</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2538103308373973</v>
+        <v>0.2555572716899343</v>
       </c>
       <c r="C23">
-        <v>1510.703842615211</v>
+        <v>1475.284594362888</v>
       </c>
       <c r="D23">
-        <v>1909.281842615211</v>
+        <v>1893.380594362888</v>
       </c>
       <c r="E23">
-        <v>-24.52199999999993</v>
+        <v>-5.003999999999962</v>
       </c>
       <c r="F23">
-        <v>409.878</v>
+        <v>429.396</v>
       </c>
       <c r="G23">
         <v>11.3</v>
@@ -3295,37 +3295,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M23">
-        <v>108.8835732286015</v>
+        <v>114.0685052871064</v>
       </c>
       <c r="N23">
-        <v>1.449760104731808</v>
+        <v>-3.735171953773019</v>
       </c>
       <c r="O23">
-        <v>0.507416036656133</v>
+        <v>-1.307310183820557</v>
       </c>
       <c r="P23">
-        <v>0.9423440680756755</v>
+        <v>-2.427861769952463</v>
       </c>
       <c r="Q23">
-        <v>85.94234406807567</v>
+        <v>82.57213823004754</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2753788331250486</v>
+        <v>0.2780765449013363</v>
       </c>
       <c r="T23">
-        <v>1.128006252980799</v>
+        <v>1.141261114986021</v>
       </c>
       <c r="U23">
         <v>0.2656487374989668</v>
       </c>
       <c r="V23">
-        <v>0.35</v>
+        <v>0.338539253841101</v>
       </c>
       <c r="W23">
-        <v>0.1726716793743285</v>
+        <v>0.1757162121222361</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.013314773401935</v>
+        <v>0.9672550109745742</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2555572716899343</v>
+        <v>0.2577557590649239</v>
       </c>
       <c r="C24">
-        <v>1475.284594362888</v>
+        <v>1436.127716178493</v>
       </c>
       <c r="D24">
-        <v>1893.380594362888</v>
+        <v>1873.741716178493</v>
       </c>
       <c r="E24">
-        <v>-5.003999999999962</v>
+        <v>14.51400000000007</v>
       </c>
       <c r="F24">
-        <v>429.396</v>
+        <v>448.914</v>
       </c>
       <c r="G24">
         <v>11.3</v>
@@ -3377,37 +3377,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M24">
-        <v>114.0685052871064</v>
+        <v>119.2534373456112</v>
       </c>
       <c r="N24">
-        <v>-3.735171953773019</v>
+        <v>-8.920104012277861</v>
       </c>
       <c r="O24">
-        <v>-1.307310183820557</v>
+        <v>-3.122036404297251</v>
       </c>
       <c r="P24">
-        <v>-2.427861769952463</v>
+        <v>-5.798067607980609</v>
       </c>
       <c r="Q24">
-        <v>82.57213823004754</v>
+        <v>79.20193239201939</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2780765449013363</v>
+        <v>0.2810931234065485</v>
       </c>
       <c r="T24">
-        <v>1.141261114986021</v>
+        <v>1.156082687907918</v>
       </c>
       <c r="U24">
         <v>0.2656487374989668</v>
       </c>
       <c r="V24">
-        <v>0.338539253841101</v>
+        <v>0.3238201558480096</v>
       </c>
       <c r="W24">
-        <v>0.1757162121222361</v>
+        <v>0.1796263219212244</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.9672550109745742</v>
+        <v>0.9252004452800274</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2577557590649239</v>
+        <v>0.2599542464399136</v>
       </c>
       <c r="C25">
-        <v>1436.127716178493</v>
+        <v>1397.374059750985</v>
       </c>
       <c r="D25">
-        <v>1873.741716178493</v>
+        <v>1854.506059750985</v>
       </c>
       <c r="E25">
-        <v>14.51400000000007</v>
+        <v>34.0320000000001</v>
       </c>
       <c r="F25">
-        <v>448.914</v>
+        <v>468.4320000000001</v>
       </c>
       <c r="G25">
         <v>11.3</v>
@@ -3459,37 +3459,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M25">
-        <v>119.2534373456112</v>
+        <v>124.438369404116</v>
       </c>
       <c r="N25">
-        <v>-8.920104012277861</v>
+        <v>-14.1050360707827</v>
       </c>
       <c r="O25">
-        <v>-3.122036404297251</v>
+        <v>-4.936762624773945</v>
       </c>
       <c r="P25">
-        <v>-5.798067607980609</v>
+        <v>-9.168273446008758</v>
       </c>
       <c r="Q25">
-        <v>79.20193239201939</v>
+        <v>75.83172655399125</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2810931234065485</v>
+        <v>0.2841890855566346</v>
       </c>
       <c r="T25">
-        <v>1.156082687907918</v>
+        <v>1.171294302222496</v>
       </c>
       <c r="U25">
         <v>0.2656487374989668</v>
       </c>
       <c r="V25">
-        <v>0.3238201558480096</v>
+        <v>0.3103276493543425</v>
       </c>
       <c r="W25">
-        <v>0.1796263219212244</v>
+        <v>0.1832105892369637</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.9252004452800274</v>
+        <v>0.8866504267266929</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2599542464399135</v>
+        <v>0.2621527338149032</v>
       </c>
       <c r="C26">
-        <v>1397.374059750986</v>
+        <v>1359.011332960094</v>
       </c>
       <c r="D26">
-        <v>1854.506059750986</v>
+        <v>1835.661332960094</v>
       </c>
       <c r="E26">
-        <v>34.03200000000004</v>
+        <v>53.55000000000007</v>
       </c>
       <c r="F26">
-        <v>468.432</v>
+        <v>487.95</v>
       </c>
       <c r="G26">
         <v>11.3</v>
@@ -3541,37 +3541,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M26">
-        <v>124.438369404116</v>
+        <v>129.6233014626209</v>
       </c>
       <c r="N26">
-        <v>-14.10503607078269</v>
+        <v>-19.28996812928753</v>
       </c>
       <c r="O26">
-        <v>-4.936762624773941</v>
+        <v>-6.751488845250635</v>
       </c>
       <c r="P26">
-        <v>-9.168273446008747</v>
+        <v>-12.5384792840369</v>
       </c>
       <c r="Q26">
-        <v>75.83172655399125</v>
+        <v>72.4615207159631</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2841890855566346</v>
+        <v>0.2873676066973898</v>
       </c>
       <c r="T26">
-        <v>1.171294302222495</v>
+        <v>1.186911559585462</v>
       </c>
       <c r="U26">
         <v>0.2656487374989668</v>
       </c>
       <c r="V26">
-        <v>0.3103276493543425</v>
+        <v>0.2979145433801688</v>
       </c>
       <c r="W26">
-        <v>0.1832105892369637</v>
+        <v>0.1865081151674438</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.886650426726693</v>
+        <v>0.8511844096576253</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2621527338149032</v>
+        <v>0.2643512211898929</v>
       </c>
       <c r="C27">
-        <v>1359.011332960094</v>
+        <v>1321.027738289438</v>
       </c>
       <c r="D27">
-        <v>1835.661332960094</v>
+        <v>1817.195738289438</v>
       </c>
       <c r="E27">
-        <v>53.55000000000007</v>
+        <v>73.0680000000001</v>
       </c>
       <c r="F27">
-        <v>487.95</v>
+        <v>507.4680000000001</v>
       </c>
       <c r="G27">
         <v>11.3</v>
@@ -3623,37 +3623,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M27">
-        <v>129.6233014626209</v>
+        <v>134.8082335211257</v>
       </c>
       <c r="N27">
-        <v>-19.28996812928753</v>
+        <v>-24.47490018779237</v>
       </c>
       <c r="O27">
-        <v>-6.751488845250635</v>
+        <v>-8.566215065727329</v>
       </c>
       <c r="P27">
-        <v>-12.5384792840369</v>
+        <v>-15.90868512206504</v>
       </c>
       <c r="Q27">
-        <v>72.4615207159631</v>
+        <v>69.09131487793496</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2873676066973898</v>
+        <v>0.290632033814922</v>
       </c>
       <c r="T27">
-        <v>1.186911559585462</v>
+        <v>1.202950904985266</v>
       </c>
       <c r="U27">
         <v>0.2656487374989668</v>
       </c>
       <c r="V27">
-        <v>0.2979145433801688</v>
+        <v>0.2864562917117008</v>
       </c>
       <c r="W27">
-        <v>0.1865081151674438</v>
+        <v>0.1895519852571177</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8511844096576253</v>
+        <v>0.8184465477477165</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2643512211898929</v>
+        <v>0.2835927175244632</v>
       </c>
       <c r="C28">
-        <v>1321.027738289438</v>
+        <v>1154.467534888503</v>
       </c>
       <c r="D28">
-        <v>1817.195738289438</v>
+        <v>1670.153534888504</v>
       </c>
       <c r="E28">
-        <v>73.0680000000001</v>
+        <v>92.58600000000013</v>
       </c>
       <c r="F28">
-        <v>507.4680000000001</v>
+        <v>526.9860000000001</v>
       </c>
       <c r="G28">
         <v>11.3</v>
@@ -3705,45 +3705,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M28">
-        <v>134.8082335211257</v>
+        <v>168.4504095796306</v>
       </c>
       <c r="N28">
-        <v>-24.47490018779237</v>
+        <v>-58.11707624629724</v>
       </c>
       <c r="O28">
-        <v>-8.566215065727329</v>
+        <v>-20.34097668620403</v>
       </c>
       <c r="P28">
-        <v>-15.90868512206504</v>
+        <v>-37.77609956009321</v>
       </c>
       <c r="Q28">
-        <v>69.09131487793496</v>
+        <v>47.22390043990679</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.290632033814922</v>
+        <v>0.2973598821679765</v>
       </c>
       <c r="T28">
-        <v>1.202950904985266</v>
+        <v>1.236007327949217</v>
       </c>
       <c r="U28">
-        <v>0.2656487374989668</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V28">
-        <v>0.2864562917117008</v>
+        <v>0.229246499091542</v>
       </c>
       <c r="W28">
-        <v>0.1895519852571177</v>
+        <v>0.2463703834882974</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.8184465477477165</v>
+        <v>0.6549899974044059</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2835927175244632</v>
+        <v>0.2863312048994528</v>
       </c>
       <c r="C29">
-        <v>1154.467534888503</v>
+        <v>1115.934561877005</v>
       </c>
       <c r="D29">
-        <v>1670.153534888504</v>
+        <v>1651.138561877005</v>
       </c>
       <c r="E29">
-        <v>92.58600000000013</v>
+        <v>112.1040000000002</v>
       </c>
       <c r="F29">
-        <v>526.9860000000001</v>
+        <v>546.5040000000001</v>
       </c>
       <c r="G29">
         <v>11.3</v>
@@ -3787,37 +3787,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M29">
-        <v>168.4504095796306</v>
+        <v>174.6893136381354</v>
       </c>
       <c r="N29">
-        <v>-58.11707624629724</v>
+        <v>-64.3559803048021</v>
       </c>
       <c r="O29">
-        <v>-20.34097668620403</v>
+        <v>-22.52459310668073</v>
       </c>
       <c r="P29">
-        <v>-37.77609956009321</v>
+        <v>-41.83138719812137</v>
       </c>
       <c r="Q29">
-        <v>47.22390043990679</v>
+        <v>43.16861280187863</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2973598821679765</v>
+        <v>0.3008537694203095</v>
       </c>
       <c r="T29">
-        <v>1.236007327949217</v>
+        <v>1.253174096392956</v>
       </c>
       <c r="U29">
         <v>0.3196487374989669</v>
       </c>
       <c r="V29">
-        <v>0.229246499091542</v>
+        <v>0.2210591241239869</v>
       </c>
       <c r="W29">
-        <v>0.2463703834882974</v>
+        <v>0.248987467560107</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.6549899974044059</v>
+        <v>0.6315974974971056</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2863312048994528</v>
+        <v>0.2890696922744425</v>
       </c>
       <c r="C30">
-        <v>1115.934561877005</v>
+        <v>1077.829692038086</v>
       </c>
       <c r="D30">
-        <v>1651.138561877005</v>
+        <v>1632.551692038086</v>
       </c>
       <c r="E30">
-        <v>112.1040000000002</v>
+        <v>131.6220000000002</v>
       </c>
       <c r="F30">
-        <v>546.5040000000001</v>
+        <v>566.0220000000002</v>
       </c>
       <c r="G30">
         <v>11.3</v>
@@ -3869,37 +3869,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M30">
-        <v>174.6893136381354</v>
+        <v>180.9282176966403</v>
       </c>
       <c r="N30">
-        <v>-64.3559803048021</v>
+        <v>-70.59488436330693</v>
       </c>
       <c r="O30">
-        <v>-22.52459310668073</v>
+        <v>-24.70820952715743</v>
       </c>
       <c r="P30">
-        <v>-41.83138719812137</v>
+        <v>-45.88667483614951</v>
       </c>
       <c r="Q30">
-        <v>43.16861280187863</v>
+        <v>39.11332516385049</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.3008537694203095</v>
+        <v>0.3044460760318632</v>
       </c>
       <c r="T30">
-        <v>1.253174096392956</v>
+        <v>1.270824435778772</v>
       </c>
       <c r="U30">
         <v>0.3196487374989669</v>
       </c>
       <c r="V30">
-        <v>0.2210591241239869</v>
+        <v>0.2134363957059184</v>
       </c>
       <c r="W30">
-        <v>0.248987467560107</v>
+        <v>0.2514240630752401</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.6315974974971056</v>
+        <v>0.6098182734454813</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2890696922744425</v>
+        <v>0.2918081796494322</v>
       </c>
       <c r="C31">
-        <v>1077.829692038086</v>
+        <v>1040.138628833296</v>
       </c>
       <c r="D31">
-        <v>1632.551692038086</v>
+        <v>1614.378628833297</v>
       </c>
       <c r="E31">
-        <v>131.6220000000001</v>
+        <v>151.1400000000001</v>
       </c>
       <c r="F31">
-        <v>566.022</v>
+        <v>585.5400000000001</v>
       </c>
       <c r="G31">
         <v>11.3</v>
@@ -3951,37 +3951,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M31">
-        <v>180.9282176966402</v>
+        <v>187.1671217551451</v>
       </c>
       <c r="N31">
-        <v>-70.5948843633069</v>
+        <v>-76.83378842181176</v>
       </c>
       <c r="O31">
-        <v>-24.70820952715741</v>
+        <v>-26.89182594763411</v>
       </c>
       <c r="P31">
-        <v>-45.88667483614949</v>
+        <v>-49.94196247417764</v>
       </c>
       <c r="Q31">
-        <v>39.11332516385051</v>
+        <v>35.05803752582236</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.3044460760318632</v>
+        <v>0.3081410199751755</v>
       </c>
       <c r="T31">
-        <v>1.270824435778772</v>
+        <v>1.288979070575612</v>
       </c>
       <c r="U31">
         <v>0.3196487374989669</v>
       </c>
       <c r="V31">
-        <v>0.2134363957059185</v>
+        <v>0.2063218491823878</v>
       </c>
       <c r="W31">
-        <v>0.2514240630752401</v>
+        <v>0.2536982188893643</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.6098182734454813</v>
+        <v>0.5894909976639653</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2918081796494322</v>
+        <v>0.2945466670244218</v>
       </c>
       <c r="C32">
-        <v>1040.138628833296</v>
+        <v>1002.847705294671</v>
       </c>
       <c r="D32">
-        <v>1614.378628833297</v>
+        <v>1596.605705294671</v>
       </c>
       <c r="E32">
-        <v>151.1400000000001</v>
+        <v>170.6580000000001</v>
       </c>
       <c r="F32">
-        <v>585.5400000000001</v>
+        <v>605.0580000000001</v>
       </c>
       <c r="G32">
         <v>11.3</v>
@@ -4033,37 +4033,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M32">
-        <v>187.1671217551451</v>
+        <v>193.4060258136499</v>
       </c>
       <c r="N32">
-        <v>-76.83378842181176</v>
+        <v>-83.07269248031659</v>
       </c>
       <c r="O32">
-        <v>-26.89182594763411</v>
+        <v>-29.0754423681108</v>
       </c>
       <c r="P32">
-        <v>-49.94196247417764</v>
+        <v>-53.99725011220579</v>
       </c>
       <c r="Q32">
-        <v>35.05803752582236</v>
+        <v>31.00274988779421</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3081410199751755</v>
+        <v>0.3119430637429317</v>
       </c>
       <c r="T32">
-        <v>1.288979070575612</v>
+        <v>1.307659926670911</v>
       </c>
       <c r="U32">
         <v>0.3196487374989669</v>
       </c>
       <c r="V32">
-        <v>0.2063218491823878</v>
+        <v>0.1996663056603753</v>
       </c>
       <c r="W32">
-        <v>0.2536982188893643</v>
+        <v>0.2558256549735451</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5894909976639653</v>
+        <v>0.5704751590296437</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2945466670244218</v>
+        <v>0.2972851543994115</v>
       </c>
       <c r="C33">
-        <v>1002.847705294671</v>
+        <v>965.9438497469439</v>
       </c>
       <c r="D33">
-        <v>1596.605705294671</v>
+        <v>1579.219849746944</v>
       </c>
       <c r="E33">
-        <v>170.6580000000001</v>
+        <v>190.176</v>
       </c>
       <c r="F33">
-        <v>605.0580000000001</v>
+        <v>624.576</v>
       </c>
       <c r="G33">
         <v>11.3</v>
@@ -4115,37 +4115,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M33">
-        <v>193.4060258136499</v>
+        <v>199.6449298721547</v>
       </c>
       <c r="N33">
-        <v>-83.07269248031659</v>
+        <v>-89.31159653882139</v>
       </c>
       <c r="O33">
-        <v>-29.0754423681108</v>
+        <v>-31.25905878858748</v>
       </c>
       <c r="P33">
-        <v>-53.99725011220579</v>
+        <v>-58.05253775023391</v>
       </c>
       <c r="Q33">
-        <v>31.00274988779421</v>
+        <v>26.94746224976609</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3119430637429317</v>
+        <v>0.3158569323273865</v>
       </c>
       <c r="T33">
-        <v>1.307659926670911</v>
+        <v>1.326890219710189</v>
       </c>
       <c r="U33">
         <v>0.3196487374989669</v>
       </c>
       <c r="V33">
-        <v>0.1996663056603753</v>
+        <v>0.1934267336084886</v>
       </c>
       <c r="W33">
-        <v>0.2558256549735451</v>
+        <v>0.2578201263024645</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5704751590296437</v>
+        <v>0.5526478103099676</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2972851543994115</v>
+        <v>0.3000236417744012</v>
       </c>
       <c r="C34">
-        <v>965.9438497469439</v>
+        <v>929.4145537452023</v>
       </c>
       <c r="D34">
-        <v>1579.219849746944</v>
+        <v>1562.208553745202</v>
       </c>
       <c r="E34">
-        <v>190.176</v>
+        <v>209.6940000000001</v>
       </c>
       <c r="F34">
-        <v>624.576</v>
+        <v>644.0940000000001</v>
       </c>
       <c r="G34">
         <v>11.3</v>
@@ -4197,37 +4197,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M34">
-        <v>199.6449298721547</v>
+        <v>205.8838339306596</v>
       </c>
       <c r="N34">
-        <v>-89.31159653882139</v>
+        <v>-95.55050059732625</v>
       </c>
       <c r="O34">
-        <v>-31.25905878858748</v>
+        <v>-33.44267520906418</v>
       </c>
       <c r="P34">
-        <v>-58.05253775023391</v>
+        <v>-62.10782538826206</v>
       </c>
       <c r="Q34">
-        <v>26.94746224976609</v>
+        <v>22.89217461173794</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3158569323273865</v>
+        <v>0.3198876328098849</v>
       </c>
       <c r="T34">
-        <v>1.326890219710189</v>
+        <v>1.346694551347654</v>
       </c>
       <c r="U34">
         <v>0.3196487374989669</v>
       </c>
       <c r="V34">
-        <v>0.1934267336084886</v>
+        <v>0.1875653174385344</v>
       </c>
       <c r="W34">
-        <v>0.2578201263024645</v>
+        <v>0.2596937205811464</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5526478103099676</v>
+        <v>0.5359009069672411</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.3000236417744012</v>
+        <v>0.3027621291493908</v>
       </c>
       <c r="C35">
-        <v>929.4145537452023</v>
+        <v>893.2478420626921</v>
       </c>
       <c r="D35">
-        <v>1562.208553745202</v>
+        <v>1545.559842062692</v>
       </c>
       <c r="E35">
-        <v>209.6940000000001</v>
+        <v>229.2120000000001</v>
       </c>
       <c r="F35">
-        <v>644.0940000000001</v>
+        <v>663.6120000000001</v>
       </c>
       <c r="G35">
         <v>11.3</v>
@@ -4279,37 +4279,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M35">
-        <v>205.8838339306596</v>
+        <v>212.1227379891644</v>
       </c>
       <c r="N35">
-        <v>-95.55050059732625</v>
+        <v>-101.7894046558311</v>
       </c>
       <c r="O35">
-        <v>-33.44267520906418</v>
+        <v>-35.62629162954089</v>
       </c>
       <c r="P35">
-        <v>-62.10782538826206</v>
+        <v>-66.16311302629022</v>
       </c>
       <c r="Q35">
-        <v>22.89217461173794</v>
+        <v>18.83688697370978</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3198876328098849</v>
+        <v>0.3240404757312468</v>
       </c>
       <c r="T35">
-        <v>1.346694551347654</v>
+        <v>1.367099014246861</v>
       </c>
       <c r="U35">
         <v>0.3196487374989669</v>
       </c>
       <c r="V35">
-        <v>0.1875653174385344</v>
+        <v>0.1820486904550481</v>
       </c>
       <c r="W35">
-        <v>0.2596937205811464</v>
+        <v>0.2614571034316706</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5359009069672411</v>
+        <v>0.5201391155858517</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.3027621291493908</v>
+        <v>0.3055006165243805</v>
       </c>
       <c r="C36">
-        <v>893.2478420626921</v>
+        <v>857.4322445774646</v>
       </c>
       <c r="D36">
-        <v>1545.559842062692</v>
+        <v>1529.262244577465</v>
       </c>
       <c r="E36">
-        <v>229.2120000000001</v>
+        <v>248.7300000000001</v>
       </c>
       <c r="F36">
-        <v>663.6120000000001</v>
+        <v>683.1300000000001</v>
       </c>
       <c r="G36">
         <v>11.3</v>
@@ -4361,37 +4361,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M36">
-        <v>212.1227379891644</v>
+        <v>218.3616420476693</v>
       </c>
       <c r="N36">
-        <v>-101.7894046558311</v>
+        <v>-108.0283087143359</v>
       </c>
       <c r="O36">
-        <v>-35.62629162954089</v>
+        <v>-37.80990805001758</v>
       </c>
       <c r="P36">
-        <v>-66.16311302629022</v>
+        <v>-70.21840066431835</v>
       </c>
       <c r="Q36">
-        <v>18.83688697370978</v>
+        <v>14.78159933568165</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3240404757312468</v>
+        <v>0.3283210984348044</v>
       </c>
       <c r="T36">
-        <v>1.367099014246861</v>
+        <v>1.388131306773736</v>
       </c>
       <c r="U36">
         <v>0.3196487374989669</v>
       </c>
       <c r="V36">
-        <v>0.1820486904550481</v>
+        <v>0.1768472992991896</v>
       </c>
       <c r="W36">
-        <v>0.2614571034316706</v>
+        <v>0.263119721547879</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5201391155858517</v>
+        <v>0.5052779979976845</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.3055006165243805</v>
+        <v>0.322034879298261</v>
       </c>
       <c r="C37">
-        <v>857.4322445774646</v>
+        <v>746.3790124364261</v>
       </c>
       <c r="D37">
-        <v>1529.262244577465</v>
+        <v>1437.727012436426</v>
       </c>
       <c r="E37">
-        <v>248.7300000000001</v>
+        <v>268.2480000000002</v>
       </c>
       <c r="F37">
-        <v>683.1300000000001</v>
+        <v>702.6480000000001</v>
       </c>
       <c r="G37">
         <v>11.3</v>
@@ -4443,45 +4443,45 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M37">
-        <v>218.3616420476693</v>
+        <v>249.1932261061741</v>
       </c>
       <c r="N37">
-        <v>-108.0283087143359</v>
+        <v>-138.8598927728408</v>
       </c>
       <c r="O37">
-        <v>-37.80990805001758</v>
+        <v>-48.60096247049427</v>
       </c>
       <c r="P37">
-        <v>-70.21840066431835</v>
+        <v>-90.2589303023465</v>
       </c>
       <c r="Q37">
-        <v>14.78159933568165</v>
+        <v>-5.258930302346499</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3283210984348044</v>
+        <v>0.3346038896586152</v>
       </c>
       <c r="T37">
-        <v>1.388131306773736</v>
+        <v>1.419000998418049</v>
       </c>
       <c r="U37">
-        <v>0.3196487374989669</v>
+        <v>0.3546487374989669</v>
       </c>
       <c r="V37">
-        <v>0.1768472992991896</v>
+        <v>0.1549667592096312</v>
       </c>
       <c r="W37">
-        <v>0.263119721547879</v>
+        <v>0.2996899719909648</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.5052779979976845</v>
+        <v>0.4427621691703749</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.322034879298261</v>
+        <v>0.3251233666732506</v>
       </c>
       <c r="C38">
-        <v>746.3790124364267</v>
+        <v>710.9640190001923</v>
       </c>
       <c r="D38">
-        <v>1437.727012436427</v>
+        <v>1421.830019000192</v>
       </c>
       <c r="E38">
-        <v>268.248</v>
+        <v>287.7660000000001</v>
       </c>
       <c r="F38">
-        <v>702.648</v>
+        <v>722.1660000000001</v>
       </c>
       <c r="G38">
         <v>11.3</v>
@@ -4525,37 +4525,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M38">
-        <v>249.1932261061741</v>
+        <v>256.1152601646789</v>
       </c>
       <c r="N38">
-        <v>-138.8598927728407</v>
+        <v>-145.7819268313456</v>
       </c>
       <c r="O38">
-        <v>-48.60096247049425</v>
+        <v>-51.02367439097096</v>
       </c>
       <c r="P38">
-        <v>-90.25893030234649</v>
+        <v>-94.75825244037463</v>
       </c>
       <c r="Q38">
-        <v>-5.258930302346485</v>
+        <v>-9.758252440374633</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3346038896586151</v>
+        <v>0.339188078383355</v>
       </c>
       <c r="T38">
-        <v>1.419000998418048</v>
+        <v>1.441524823789764</v>
       </c>
       <c r="U38">
         <v>0.3546487374989669</v>
       </c>
       <c r="V38">
-        <v>0.1549667592096312</v>
+        <v>0.1507784684201817</v>
       </c>
       <c r="W38">
-        <v>0.2996899719909648</v>
+        <v>0.3011753440317216</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4427621691703749</v>
+        <v>0.430795624057662</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.3251233666732506</v>
+        <v>0.3282118540482403</v>
       </c>
       <c r="C39">
-        <v>710.9640190001923</v>
+        <v>675.8967281325598</v>
       </c>
       <c r="D39">
-        <v>1421.830019000192</v>
+        <v>1406.28072813256</v>
       </c>
       <c r="E39">
-        <v>287.7660000000001</v>
+        <v>307.2840000000001</v>
       </c>
       <c r="F39">
-        <v>722.1660000000001</v>
+        <v>741.6840000000001</v>
       </c>
       <c r="G39">
         <v>11.3</v>
@@ -4607,37 +4607,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M39">
-        <v>256.1152601646789</v>
+        <v>263.0372942231838</v>
       </c>
       <c r="N39">
-        <v>-145.7819268313456</v>
+        <v>-152.7039608898504</v>
       </c>
       <c r="O39">
-        <v>-51.02367439097096</v>
+        <v>-53.44638631144765</v>
       </c>
       <c r="P39">
-        <v>-94.75825244037463</v>
+        <v>-99.2575745784028</v>
       </c>
       <c r="Q39">
-        <v>-9.758252440374633</v>
+        <v>-14.2575745784028</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.339188078383355</v>
+        <v>0.3439201441637317</v>
       </c>
       <c r="T39">
-        <v>1.441524823789764</v>
+        <v>1.46477522417347</v>
       </c>
       <c r="U39">
         <v>0.3546487374989669</v>
       </c>
       <c r="V39">
-        <v>0.1507784684201817</v>
+        <v>0.1468106139880717</v>
       </c>
       <c r="W39">
-        <v>0.3011753440317216</v>
+        <v>0.3025825385966491</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.430795624057662</v>
+        <v>0.4194588971087763</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.3282118540482403</v>
+        <v>0.33130034142323</v>
       </c>
       <c r="C40">
-        <v>675.8967281325598</v>
+        <v>641.1658556964804</v>
       </c>
       <c r="D40">
-        <v>1406.28072813256</v>
+        <v>1391.067855696481</v>
       </c>
       <c r="E40">
-        <v>307.2840000000001</v>
+        <v>326.8020000000001</v>
       </c>
       <c r="F40">
-        <v>741.6840000000001</v>
+        <v>761.2020000000001</v>
       </c>
       <c r="G40">
         <v>11.3</v>
@@ -4689,37 +4689,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M40">
-        <v>263.0372942231838</v>
+        <v>269.9593282816886</v>
       </c>
       <c r="N40">
-        <v>-152.7039608898504</v>
+        <v>-159.6259949483553</v>
       </c>
       <c r="O40">
-        <v>-53.44638631144765</v>
+        <v>-55.86909823192434</v>
       </c>
       <c r="P40">
-        <v>-99.2575745784028</v>
+        <v>-103.7568967164309</v>
       </c>
       <c r="Q40">
-        <v>-14.2575745784028</v>
+        <v>-18.75689671643093</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3439201441637317</v>
+        <v>0.3488073596418257</v>
       </c>
       <c r="T40">
-        <v>1.46477522417347</v>
+        <v>1.488787932766477</v>
       </c>
       <c r="U40">
         <v>0.3546487374989669</v>
       </c>
       <c r="V40">
-        <v>0.1468106139880717</v>
+        <v>0.1430462392704288</v>
       </c>
       <c r="W40">
-        <v>0.3025825385966491</v>
+        <v>0.3039175693377342</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4194588971087763</v>
+        <v>0.4087035407726538</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.33130034142323</v>
+        <v>0.3343888287982196</v>
       </c>
       <c r="C41">
-        <v>641.1658556964804</v>
+        <v>606.7606006077657</v>
       </c>
       <c r="D41">
-        <v>1391.067855696481</v>
+        <v>1376.180600607766</v>
       </c>
       <c r="E41">
-        <v>326.8020000000001</v>
+        <v>346.3200000000002</v>
       </c>
       <c r="F41">
-        <v>761.2020000000001</v>
+        <v>780.7200000000001</v>
       </c>
       <c r="G41">
         <v>11.3</v>
@@ -4771,37 +4771,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M41">
-        <v>269.9593282816886</v>
+        <v>276.8813623401934</v>
       </c>
       <c r="N41">
-        <v>-159.6259949483553</v>
+        <v>-166.5480290068601</v>
       </c>
       <c r="O41">
-        <v>-55.86909823192434</v>
+        <v>-58.29181015240103</v>
       </c>
       <c r="P41">
-        <v>-103.7568967164309</v>
+        <v>-108.2562188544591</v>
       </c>
       <c r="Q41">
-        <v>-18.75689671643093</v>
+        <v>-23.25621885445906</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3488073596418257</v>
+        <v>0.3538574823025227</v>
       </c>
       <c r="T41">
-        <v>1.488787932766477</v>
+        <v>1.513601064979252</v>
       </c>
       <c r="U41">
         <v>0.3546487374989669</v>
       </c>
       <c r="V41">
-        <v>0.1430462392704288</v>
+        <v>0.1394700832886681</v>
       </c>
       <c r="W41">
-        <v>0.3039175693377342</v>
+        <v>0.305185848541765</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4087035407726538</v>
+        <v>0.3984859522533374</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.3343888287982196</v>
+        <v>0.3374773161732093</v>
       </c>
       <c r="C42">
-        <v>606.7606006077657</v>
+        <v>572.6706192605474</v>
       </c>
       <c r="D42">
-        <v>1376.180600607766</v>
+        <v>1361.608619260548</v>
       </c>
       <c r="E42">
-        <v>346.3200000000002</v>
+        <v>365.8380000000002</v>
       </c>
       <c r="F42">
-        <v>780.7200000000001</v>
+        <v>800.2380000000002</v>
       </c>
       <c r="G42">
         <v>11.3</v>
@@ -4853,37 +4853,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M42">
-        <v>276.8813623401934</v>
+        <v>283.8033963986983</v>
       </c>
       <c r="N42">
-        <v>-166.5480290068601</v>
+        <v>-173.4700630653649</v>
       </c>
       <c r="O42">
-        <v>-58.29181015240103</v>
+        <v>-60.71452207287773</v>
       </c>
       <c r="P42">
-        <v>-108.2562188544591</v>
+        <v>-112.7555409924872</v>
       </c>
       <c r="Q42">
-        <v>-23.25621885445906</v>
+        <v>-27.75554099248721</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3538574823025227</v>
+        <v>0.3590787955618875</v>
       </c>
       <c r="T42">
-        <v>1.513601064979252</v>
+        <v>1.539255320317883</v>
       </c>
       <c r="U42">
         <v>0.3546487374989669</v>
       </c>
       <c r="V42">
-        <v>0.1394700832886681</v>
+        <v>0.136068373940164</v>
       </c>
       <c r="W42">
-        <v>0.305185848541765</v>
+        <v>0.3063922604675504</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3984859522533374</v>
+        <v>0.3887667826861828</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.3374773161732093</v>
+        <v>0.340565803548199</v>
       </c>
       <c r="C43">
-        <v>572.6706192605474</v>
+        <v>538.8860015605204</v>
       </c>
       <c r="D43">
-        <v>1361.608619260548</v>
+        <v>1347.342001560521</v>
       </c>
       <c r="E43">
-        <v>365.8380000000002</v>
+        <v>385.3560000000002</v>
       </c>
       <c r="F43">
-        <v>800.2380000000002</v>
+        <v>819.7560000000002</v>
       </c>
       <c r="G43">
         <v>11.3</v>
@@ -4935,37 +4935,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M43">
-        <v>283.8033963986983</v>
+        <v>290.7254304572032</v>
       </c>
       <c r="N43">
-        <v>-173.4700630653649</v>
+        <v>-180.3920971238698</v>
       </c>
       <c r="O43">
-        <v>-60.71452207287773</v>
+        <v>-63.13723399335444</v>
       </c>
       <c r="P43">
-        <v>-112.7555409924872</v>
+        <v>-117.2548631305154</v>
       </c>
       <c r="Q43">
-        <v>-27.75554099248721</v>
+        <v>-32.25486313051539</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3590787955618875</v>
+        <v>0.3644801541060581</v>
       </c>
       <c r="T43">
-        <v>1.539255320317883</v>
+        <v>1.56579420515095</v>
       </c>
       <c r="U43">
         <v>0.3546487374989669</v>
       </c>
       <c r="V43">
-        <v>0.136068373940164</v>
+        <v>0.1328286507511124</v>
       </c>
       <c r="W43">
-        <v>0.3063922604675504</v>
+        <v>0.3075412242063936</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3887667826861828</v>
+        <v>0.3795104307174642</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.3405658035481989</v>
+        <v>0.3436542909231887</v>
       </c>
       <c r="C44">
-        <v>538.8860015605208</v>
+        <v>505.3972484492749</v>
       </c>
       <c r="D44">
-        <v>1347.342001560521</v>
+        <v>1333.371248449275</v>
       </c>
       <c r="E44">
-        <v>385.3560000000001</v>
+        <v>404.8740000000001</v>
       </c>
       <c r="F44">
-        <v>819.7560000000001</v>
+        <v>839.2740000000001</v>
       </c>
       <c r="G44">
         <v>11.3</v>
@@ -5017,37 +5017,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M44">
-        <v>290.7254304572031</v>
+        <v>297.647464515708</v>
       </c>
       <c r="N44">
-        <v>-180.3920971238698</v>
+        <v>-187.3141311823746</v>
       </c>
       <c r="O44">
-        <v>-63.13723399335441</v>
+        <v>-65.55994591383111</v>
       </c>
       <c r="P44">
-        <v>-117.2548631305154</v>
+        <v>-121.7541852685435</v>
       </c>
       <c r="Q44">
-        <v>-32.25486313051536</v>
+        <v>-36.75418526854349</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3644801541060579</v>
+        <v>0.3700710340026555</v>
       </c>
       <c r="T44">
-        <v>1.56579420515095</v>
+        <v>1.593264278925528</v>
       </c>
       <c r="U44">
         <v>0.3546487374989669</v>
       </c>
       <c r="V44">
-        <v>0.1328286507511125</v>
+        <v>0.1297396123615517</v>
       </c>
       <c r="W44">
-        <v>0.3075412242063936</v>
+        <v>0.3086367477713372</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3795104307174643</v>
+        <v>0.3706846067472906</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.3436542909231887</v>
+        <v>0.3467427782981783</v>
       </c>
       <c r="C45">
-        <v>505.3972484492749</v>
+        <v>472.1952508125897</v>
       </c>
       <c r="D45">
-        <v>1333.371248449275</v>
+        <v>1319.68725081259</v>
       </c>
       <c r="E45">
-        <v>404.8740000000001</v>
+        <v>424.3920000000001</v>
       </c>
       <c r="F45">
-        <v>839.2740000000001</v>
+        <v>858.792</v>
       </c>
       <c r="G45">
         <v>11.3</v>
@@ -5099,37 +5099,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M45">
-        <v>297.647464515708</v>
+        <v>304.5694985742127</v>
       </c>
       <c r="N45">
-        <v>-187.3141311823746</v>
+        <v>-194.2361652408794</v>
       </c>
       <c r="O45">
-        <v>-65.55994591383111</v>
+        <v>-67.98265783430779</v>
       </c>
       <c r="P45">
-        <v>-121.7541852685435</v>
+        <v>-126.2535074065716</v>
       </c>
       <c r="Q45">
-        <v>-36.75418526854349</v>
+        <v>-41.2535074065716</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3700710340026555</v>
+        <v>0.3758615881812744</v>
       </c>
       <c r="T45">
-        <v>1.593264278925528</v>
+        <v>1.621715426763484</v>
       </c>
       <c r="U45">
         <v>0.3546487374989669</v>
       </c>
       <c r="V45">
-        <v>0.1297396123615517</v>
+        <v>0.1267909848078801</v>
       </c>
       <c r="W45">
-        <v>0.3086367477713372</v>
+        <v>0.3096824748106015</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3706846067472906</v>
+        <v>0.3622599565939432</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.3467427782981783</v>
+        <v>0.349831265673168</v>
       </c>
       <c r="C46">
-        <v>472.1952508125897</v>
+        <v>439.2712696742848</v>
       </c>
       <c r="D46">
-        <v>1319.68725081259</v>
+        <v>1306.281269674285</v>
       </c>
       <c r="E46">
-        <v>424.3920000000001</v>
+        <v>443.9100000000001</v>
       </c>
       <c r="F46">
-        <v>858.792</v>
+        <v>878.3100000000001</v>
       </c>
       <c r="G46">
         <v>11.3</v>
@@ -5181,37 +5181,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M46">
-        <v>304.5694985742127</v>
+        <v>311.4915326327176</v>
       </c>
       <c r="N46">
-        <v>-194.2361652408794</v>
+        <v>-201.1581992993843</v>
       </c>
       <c r="O46">
-        <v>-67.98265783430779</v>
+        <v>-70.40536975478449</v>
       </c>
       <c r="P46">
-        <v>-126.2535074065716</v>
+        <v>-130.7528295445998</v>
       </c>
       <c r="Q46">
-        <v>-41.2535074065716</v>
+        <v>-45.75282954459979</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3758615881812744</v>
+        <v>0.3818627079663884</v>
       </c>
       <c r="T46">
-        <v>1.621715426763484</v>
+        <v>1.651201161795547</v>
       </c>
       <c r="U46">
         <v>0.3546487374989669</v>
       </c>
       <c r="V46">
-        <v>0.1267909848078801</v>
+        <v>0.123973407367705</v>
       </c>
       <c r="W46">
-        <v>0.3096824748106015</v>
+        <v>0.3106817250925651</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3622599565939432</v>
+        <v>0.3542097353363</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.349831265673168</v>
+        <v>0.3529197530481577</v>
       </c>
       <c r="C47">
-        <v>439.2712696742848</v>
+        <v>406.6169175851306</v>
       </c>
       <c r="D47">
-        <v>1306.281269674285</v>
+        <v>1293.144917585131</v>
       </c>
       <c r="E47">
-        <v>443.9100000000001</v>
+        <v>463.4280000000001</v>
       </c>
       <c r="F47">
-        <v>878.3100000000001</v>
+        <v>897.8280000000001</v>
       </c>
       <c r="G47">
         <v>11.3</v>
@@ -5263,37 +5263,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M47">
-        <v>311.4915326327176</v>
+        <v>318.4135666912225</v>
       </c>
       <c r="N47">
-        <v>-201.1581992993843</v>
+        <v>-208.0802333578891</v>
       </c>
       <c r="O47">
-        <v>-70.40536975478449</v>
+        <v>-72.82808167526119</v>
       </c>
       <c r="P47">
-        <v>-130.7528295445998</v>
+        <v>-135.2521516826279</v>
       </c>
       <c r="Q47">
-        <v>-45.75282954459979</v>
+        <v>-50.25215168262793</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3818627079663884</v>
+        <v>0.3880860914472475</v>
       </c>
       <c r="T47">
-        <v>1.651201161795547</v>
+        <v>1.681778961088058</v>
       </c>
       <c r="U47">
         <v>0.3546487374989669</v>
       </c>
       <c r="V47">
-        <v>0.123973407367705</v>
+        <v>0.121278333294494</v>
       </c>
       <c r="W47">
-        <v>0.3106817250925651</v>
+        <v>0.3116375297100956</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3542097353363</v>
+        <v>0.3465095236985543</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.3529197530481577</v>
+        <v>0.3560082404231473</v>
       </c>
       <c r="C48">
-        <v>406.6169175851306</v>
+        <v>374.2241411235328</v>
       </c>
       <c r="D48">
-        <v>1293.144917585131</v>
+        <v>1280.270141123533</v>
       </c>
       <c r="E48">
-        <v>463.4280000000001</v>
+        <v>482.9460000000001</v>
       </c>
       <c r="F48">
-        <v>897.8280000000001</v>
+        <v>917.3460000000001</v>
       </c>
       <c r="G48">
         <v>11.3</v>
@@ -5345,37 +5345,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M48">
-        <v>318.4135666912225</v>
+        <v>325.3356007497273</v>
       </c>
       <c r="N48">
-        <v>-208.0802333578891</v>
+        <v>-215.0022674163939</v>
       </c>
       <c r="O48">
-        <v>-72.82808167526119</v>
+        <v>-75.25079359573787</v>
       </c>
       <c r="P48">
-        <v>-135.2521516826279</v>
+        <v>-139.7514738206561</v>
       </c>
       <c r="Q48">
-        <v>-50.25215168262793</v>
+        <v>-54.75147382065609</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3880860914472475</v>
+        <v>0.3945443195877616</v>
       </c>
       <c r="T48">
-        <v>1.681778961088058</v>
+        <v>1.713510639599153</v>
       </c>
       <c r="U48">
         <v>0.3546487374989669</v>
       </c>
       <c r="V48">
-        <v>0.121278333294494</v>
+        <v>0.1186979432243984</v>
       </c>
       <c r="W48">
-        <v>0.3116375297100956</v>
+        <v>0.3125526617907099</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3465095236985543</v>
+        <v>0.3391369806411383</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.3560082404231473</v>
+        <v>0.359096727798137</v>
       </c>
       <c r="C49">
-        <v>374.2241411235328</v>
+        <v>342.0852044312606</v>
       </c>
       <c r="D49">
-        <v>1280.270141123533</v>
+        <v>1267.649204431261</v>
       </c>
       <c r="E49">
-        <v>482.9460000000001</v>
+        <v>502.4640000000002</v>
       </c>
       <c r="F49">
-        <v>917.3460000000001</v>
+        <v>936.8640000000001</v>
       </c>
       <c r="G49">
         <v>11.3</v>
@@ -5427,37 +5427,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M49">
-        <v>325.3356007497273</v>
+        <v>332.2576348082321</v>
       </c>
       <c r="N49">
-        <v>-215.0022674163939</v>
+        <v>-221.9243014748988</v>
       </c>
       <c r="O49">
-        <v>-75.25079359573787</v>
+        <v>-77.67350551621458</v>
       </c>
       <c r="P49">
-        <v>-139.7514738206561</v>
+        <v>-144.2507959586842</v>
       </c>
       <c r="Q49">
-        <v>-54.75147382065609</v>
+        <v>-59.25079595868419</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3945443195877616</v>
+        <v>0.4012509411182955</v>
       </c>
       <c r="T49">
-        <v>1.713510639599153</v>
+        <v>1.746462767283752</v>
       </c>
       <c r="U49">
         <v>0.3546487374989669</v>
       </c>
       <c r="V49">
-        <v>0.1186979432243984</v>
+        <v>0.1162250694072234</v>
       </c>
       <c r="W49">
-        <v>0.3125526617907099</v>
+        <v>0.3134296633679653</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3391369806411383</v>
+        <v>0.3320716268777812</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3590967277981369</v>
+        <v>0.3621852151731266</v>
       </c>
       <c r="C50">
-        <v>342.0852044312608</v>
+        <v>310.1926737135113</v>
       </c>
       <c r="D50">
-        <v>1267.649204431261</v>
+        <v>1255.274673713511</v>
       </c>
       <c r="E50">
-        <v>502.4640000000001</v>
+        <v>521.9820000000001</v>
       </c>
       <c r="F50">
-        <v>936.864</v>
+        <v>956.3820000000001</v>
       </c>
       <c r="G50">
         <v>11.3</v>
@@ -5509,37 +5509,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M50">
-        <v>332.2576348082321</v>
+        <v>339.179668866737</v>
       </c>
       <c r="N50">
-        <v>-221.9243014748988</v>
+        <v>-228.8463355334036</v>
       </c>
       <c r="O50">
-        <v>-77.67350551621458</v>
+        <v>-80.09621743669126</v>
       </c>
       <c r="P50">
-        <v>-144.2507959586842</v>
+        <v>-148.7501180967124</v>
       </c>
       <c r="Q50">
-        <v>-59.25079595868419</v>
+        <v>-63.75011809671236</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.4012509411182955</v>
+        <v>0.4082205674147326</v>
       </c>
       <c r="T50">
-        <v>1.746462767283752</v>
+        <v>1.780707135269708</v>
       </c>
       <c r="U50">
         <v>0.3546487374989669</v>
       </c>
       <c r="V50">
-        <v>0.1162250694072234</v>
+        <v>0.1138531292152393</v>
       </c>
       <c r="W50">
-        <v>0.3134296633679653</v>
+        <v>0.3142708689624755</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3320716268777812</v>
+        <v>0.3252946549006837</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3621852151731266</v>
+        <v>0.3652737025481163</v>
       </c>
       <c r="C51">
-        <v>310.1926737135113</v>
+        <v>278.5394026380318</v>
       </c>
       <c r="D51">
-        <v>1255.274673713511</v>
+        <v>1243.139402638032</v>
       </c>
       <c r="E51">
-        <v>521.9820000000001</v>
+        <v>541.5000000000001</v>
       </c>
       <c r="F51">
-        <v>956.3820000000001</v>
+        <v>975.9000000000001</v>
       </c>
       <c r="G51">
         <v>11.3</v>
@@ -5591,37 +5591,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M51">
-        <v>339.179668866737</v>
+        <v>346.1017029252418</v>
       </c>
       <c r="N51">
-        <v>-228.8463355334036</v>
+        <v>-235.7683695919085</v>
       </c>
       <c r="O51">
-        <v>-80.09621743669126</v>
+        <v>-82.51892935716795</v>
       </c>
       <c r="P51">
-        <v>-148.7501180967124</v>
+        <v>-153.2494402347405</v>
       </c>
       <c r="Q51">
-        <v>-63.75011809671236</v>
+        <v>-68.24944023474052</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.4082205674147326</v>
+        <v>0.4154689787630272</v>
       </c>
       <c r="T51">
-        <v>1.780707135269708</v>
+        <v>1.816321277975102</v>
       </c>
       <c r="U51">
         <v>0.3546487374989669</v>
       </c>
       <c r="V51">
-        <v>0.1138531292152393</v>
+        <v>0.1115760666309345</v>
       </c>
       <c r="W51">
-        <v>0.3142708689624755</v>
+        <v>0.3150784263332054</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3252946549006837</v>
+        <v>0.3187887618026699</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3652737025481163</v>
+        <v>0.368362189923106</v>
       </c>
       <c r="C52">
-        <v>278.5394026380318</v>
+        <v>247.1185185730551</v>
       </c>
       <c r="D52">
-        <v>1243.139402638032</v>
+        <v>1231.236518573055</v>
       </c>
       <c r="E52">
-        <v>541.5000000000001</v>
+        <v>561.0180000000001</v>
       </c>
       <c r="F52">
-        <v>975.9000000000001</v>
+        <v>995.4180000000001</v>
       </c>
       <c r="G52">
         <v>11.3</v>
@@ -5673,37 +5673,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M52">
-        <v>346.1017029252418</v>
+        <v>353.0237369837466</v>
       </c>
       <c r="N52">
-        <v>-235.7683695919085</v>
+        <v>-242.6904036504133</v>
       </c>
       <c r="O52">
-        <v>-82.51892935716795</v>
+        <v>-84.94164127764465</v>
       </c>
       <c r="P52">
-        <v>-153.2494402347405</v>
+        <v>-157.7487623727686</v>
       </c>
       <c r="Q52">
-        <v>-68.24944023474052</v>
+        <v>-72.74876237276862</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.4154689787630272</v>
+        <v>0.4230132436357421</v>
       </c>
       <c r="T52">
-        <v>1.816321277975102</v>
+        <v>1.853389059158267</v>
       </c>
       <c r="U52">
         <v>0.3546487374989669</v>
       </c>
       <c r="V52">
-        <v>0.1115760666309345</v>
+        <v>0.1093883006185632</v>
       </c>
       <c r="W52">
-        <v>0.3150784263332054</v>
+        <v>0.315854314787436</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3187887618026699</v>
+        <v>0.3125380017673235</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.368362189923106</v>
+        <v>0.3714506772980957</v>
       </c>
       <c r="C53">
-        <v>247.1185185730551</v>
+        <v>215.9234096083521</v>
       </c>
       <c r="D53">
-        <v>1231.236518573055</v>
+        <v>1219.559409608352</v>
       </c>
       <c r="E53">
-        <v>561.0180000000001</v>
+        <v>580.5360000000002</v>
       </c>
       <c r="F53">
-        <v>995.4180000000001</v>
+        <v>1014.936</v>
       </c>
       <c r="G53">
         <v>11.3</v>
@@ -5755,37 +5755,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M53">
-        <v>353.0237369837466</v>
+        <v>359.9457710422515</v>
       </c>
       <c r="N53">
-        <v>-242.6904036504133</v>
+        <v>-249.6124377089181</v>
       </c>
       <c r="O53">
-        <v>-84.94164127764465</v>
+        <v>-87.36435319812134</v>
       </c>
       <c r="P53">
-        <v>-157.7487623727686</v>
+        <v>-162.2480845107968</v>
       </c>
       <c r="Q53">
-        <v>-72.74876237276862</v>
+        <v>-77.24808451079679</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.4230132436357421</v>
+        <v>0.4308718528781534</v>
       </c>
       <c r="T53">
-        <v>1.853389059158267</v>
+        <v>1.892001331224065</v>
       </c>
       <c r="U53">
         <v>0.3546487374989669</v>
       </c>
       <c r="V53">
-        <v>0.1093883006185632</v>
+        <v>0.1072846794528216</v>
       </c>
       <c r="W53">
-        <v>0.315854314787436</v>
+        <v>0.3166003613780423</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3125380017673235</v>
+        <v>0.3065276555794904</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3714506772980957</v>
+        <v>0.3745391646730853</v>
       </c>
       <c r="C54">
-        <v>215.9234096083521</v>
+        <v>184.9477123079075</v>
       </c>
       <c r="D54">
-        <v>1219.559409608352</v>
+        <v>1208.101712307908</v>
       </c>
       <c r="E54">
-        <v>580.5360000000002</v>
+        <v>600.0540000000002</v>
       </c>
       <c r="F54">
-        <v>1014.936</v>
+        <v>1034.454</v>
       </c>
       <c r="G54">
         <v>11.3</v>
@@ -5837,37 +5837,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M54">
-        <v>359.9457710422515</v>
+        <v>366.8678051007563</v>
       </c>
       <c r="N54">
-        <v>-249.6124377089181</v>
+        <v>-256.5344717674229</v>
       </c>
       <c r="O54">
-        <v>-87.36435319812134</v>
+        <v>-89.78706511859802</v>
       </c>
       <c r="P54">
-        <v>-162.2480845107968</v>
+        <v>-166.7474066488249</v>
       </c>
       <c r="Q54">
-        <v>-77.24808451079679</v>
+        <v>-81.74740664882489</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4308718528781534</v>
+        <v>0.4390648710244971</v>
       </c>
       <c r="T54">
-        <v>1.892001331224065</v>
+        <v>1.932256678696917</v>
       </c>
       <c r="U54">
         <v>0.3546487374989669</v>
       </c>
       <c r="V54">
-        <v>0.1072846794528216</v>
+        <v>0.1052604402178627</v>
       </c>
       <c r="W54">
-        <v>0.3166003613780423</v>
+        <v>0.3173182552671164</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3065276555794904</v>
+        <v>0.3007441149081793</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3745391646730853</v>
+        <v>0.377627652048075</v>
       </c>
       <c r="C55">
-        <v>184.9477123079075</v>
+        <v>154.1853001465431</v>
       </c>
       <c r="D55">
-        <v>1208.101712307908</v>
+        <v>1196.857300146543</v>
       </c>
       <c r="E55">
-        <v>600.0540000000002</v>
+        <v>619.5720000000002</v>
       </c>
       <c r="F55">
-        <v>1034.454</v>
+        <v>1053.972</v>
       </c>
       <c r="G55">
         <v>11.3</v>
@@ -5919,37 +5919,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M55">
-        <v>366.8678051007563</v>
+        <v>373.7898391592612</v>
       </c>
       <c r="N55">
-        <v>-256.5344717674229</v>
+        <v>-263.4565058259278</v>
       </c>
       <c r="O55">
-        <v>-89.78706511859802</v>
+        <v>-92.20977703907474</v>
       </c>
       <c r="P55">
-        <v>-166.7474066488249</v>
+        <v>-171.2467287868531</v>
       </c>
       <c r="Q55">
-        <v>-81.74740664882489</v>
+        <v>-86.24672878685308</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4390648710244971</v>
+        <v>0.4476141073511167</v>
       </c>
       <c r="T55">
-        <v>1.932256678696917</v>
+        <v>1.974262258668589</v>
       </c>
       <c r="U55">
         <v>0.3546487374989669</v>
       </c>
       <c r="V55">
-        <v>0.1052604402178627</v>
+        <v>0.1033111728064208</v>
       </c>
       <c r="W55">
-        <v>0.3173182552671164</v>
+        <v>0.3180095604936322</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3007441149081793</v>
+        <v>0.2951747794469166</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.377627652048075</v>
+        <v>0.3807161394230647</v>
       </c>
       <c r="C56">
-        <v>154.1853001465431</v>
+        <v>123.630272586347</v>
       </c>
       <c r="D56">
-        <v>1196.857300146543</v>
+        <v>1185.820272586347</v>
       </c>
       <c r="E56">
-        <v>619.5720000000002</v>
+        <v>639.0900000000003</v>
       </c>
       <c r="F56">
-        <v>1053.972</v>
+        <v>1073.49</v>
       </c>
       <c r="G56">
         <v>11.3</v>
@@ -6001,37 +6001,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M56">
-        <v>373.7898391592612</v>
+        <v>380.711873217766</v>
       </c>
       <c r="N56">
-        <v>-263.4565058259278</v>
+        <v>-270.3785398844327</v>
       </c>
       <c r="O56">
-        <v>-92.20977703907474</v>
+        <v>-94.63248895955144</v>
       </c>
       <c r="P56">
-        <v>-171.2467287868531</v>
+        <v>-175.7460509248813</v>
       </c>
       <c r="Q56">
-        <v>-86.24672878685308</v>
+        <v>-90.74605092488127</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4476141073511167</v>
+        <v>0.456543309736697</v>
       </c>
       <c r="T56">
-        <v>1.974262258668589</v>
+        <v>2.018134753305669</v>
       </c>
       <c r="U56">
         <v>0.3546487374989669</v>
       </c>
       <c r="V56">
-        <v>0.1033111728064208</v>
+        <v>0.1014327878463041</v>
       </c>
       <c r="W56">
-        <v>0.3180095604936322</v>
+        <v>0.3186757273482746</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2951747794469166</v>
+        <v>0.2898079652751544</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3807161394230647</v>
+        <v>0.3838046267980543</v>
       </c>
       <c r="C57">
-        <v>123.630272586347</v>
+        <v>93.27694475197995</v>
       </c>
       <c r="D57">
-        <v>1185.820272586347</v>
+        <v>1174.98494475198</v>
       </c>
       <c r="E57">
-        <v>639.0900000000003</v>
+        <v>658.6080000000003</v>
       </c>
       <c r="F57">
-        <v>1073.49</v>
+        <v>1093.008</v>
       </c>
       <c r="G57">
         <v>11.3</v>
@@ -6083,37 +6083,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M57">
-        <v>380.711873217766</v>
+        <v>387.6339072762709</v>
       </c>
       <c r="N57">
-        <v>-270.3785398844327</v>
+        <v>-277.3005739429375</v>
       </c>
       <c r="O57">
-        <v>-94.63248895955144</v>
+        <v>-97.05520088002811</v>
       </c>
       <c r="P57">
-        <v>-175.7460509248813</v>
+        <v>-180.2453730629094</v>
       </c>
       <c r="Q57">
-        <v>-90.74605092488127</v>
+        <v>-95.24537306290938</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.456543309736697</v>
+        <v>0.4658783849579856</v>
       </c>
       <c r="T57">
-        <v>2.018134753305669</v>
+        <v>2.064001452244435</v>
       </c>
       <c r="U57">
         <v>0.3546487374989669</v>
       </c>
       <c r="V57">
-        <v>0.1014327878463041</v>
+        <v>0.09962148806333433</v>
       </c>
       <c r="W57">
-        <v>0.3186757273482746</v>
+        <v>0.3193181025295369</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2898079652751544</v>
+        <v>0.2846328230380982</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3838046267980543</v>
+        <v>0.386893114173044</v>
       </c>
       <c r="C58">
-        <v>93.27694475197995</v>
+        <v>63.11983766690309</v>
       </c>
       <c r="D58">
-        <v>1174.98494475198</v>
+        <v>1164.345837666903</v>
       </c>
       <c r="E58">
-        <v>658.6080000000003</v>
+        <v>678.1260000000003</v>
       </c>
       <c r="F58">
-        <v>1093.008</v>
+        <v>1112.526</v>
       </c>
       <c r="G58">
         <v>11.3</v>
@@ -6165,37 +6165,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M58">
-        <v>387.6339072762709</v>
+        <v>394.5559413347757</v>
       </c>
       <c r="N58">
-        <v>-277.3005739429375</v>
+        <v>-284.2226080014424</v>
       </c>
       <c r="O58">
-        <v>-97.05520088002811</v>
+        <v>-99.47791280050482</v>
       </c>
       <c r="P58">
-        <v>-180.2453730629094</v>
+        <v>-184.7446952009375</v>
       </c>
       <c r="Q58">
-        <v>-95.24537306290938</v>
+        <v>-99.74469520093754</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4658783849579856</v>
+        <v>0.4756476497244504</v>
       </c>
       <c r="T58">
-        <v>2.064001452244435</v>
+        <v>2.112001486017561</v>
       </c>
       <c r="U58">
         <v>0.3546487374989669</v>
       </c>
       <c r="V58">
-        <v>0.09962148806333433</v>
+        <v>0.09787374265871443</v>
       </c>
       <c r="W58">
-        <v>0.3193181025295369</v>
+        <v>0.319937938230755</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2846328230380982</v>
+        <v>0.2796392647391841</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.386893114173044</v>
+        <v>0.3899816015480337</v>
       </c>
       <c r="C59">
-        <v>63.11983766690309</v>
+        <v>33.15366901529023</v>
       </c>
       <c r="D59">
-        <v>1164.345837666903</v>
+        <v>1153.897669015291</v>
       </c>
       <c r="E59">
-        <v>678.1260000000003</v>
+        <v>697.6440000000003</v>
       </c>
       <c r="F59">
-        <v>1112.526</v>
+        <v>1132.044</v>
       </c>
       <c r="G59">
         <v>11.3</v>
@@ -6247,37 +6247,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M59">
-        <v>394.5559413347757</v>
+        <v>401.4779753932805</v>
       </c>
       <c r="N59">
-        <v>-284.2226080014424</v>
+        <v>-291.1446420599472</v>
       </c>
       <c r="O59">
-        <v>-99.47791280050482</v>
+        <v>-101.9006247209815</v>
       </c>
       <c r="P59">
-        <v>-184.7446952009375</v>
+        <v>-189.2440173389656</v>
       </c>
       <c r="Q59">
-        <v>-99.74469520093754</v>
+        <v>-104.2440173389656</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4756476497244504</v>
+        <v>0.4858821175750326</v>
       </c>
       <c r="T59">
-        <v>2.112001486017561</v>
+        <v>2.162287235684646</v>
       </c>
       <c r="U59">
         <v>0.3546487374989669</v>
       </c>
       <c r="V59">
-        <v>0.09787374265871443</v>
+        <v>0.09618626433701247</v>
       </c>
       <c r="W59">
-        <v>0.319937938230755</v>
+        <v>0.3205364002871035</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2796392647391841</v>
+        <v>0.27481789810575</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3899816015480336</v>
+        <v>0.3930700889230233</v>
       </c>
       <c r="C60">
-        <v>33.15366901529069</v>
+        <v>3.37334439690494</v>
       </c>
       <c r="D60">
-        <v>1153.897669015291</v>
+        <v>1143.635344396905</v>
       </c>
       <c r="E60">
-        <v>697.6440000000001</v>
+        <v>717.1620000000001</v>
       </c>
       <c r="F60">
-        <v>1132.044</v>
+        <v>1151.562</v>
       </c>
       <c r="G60">
         <v>11.3</v>
@@ -6329,37 +6329,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M60">
-        <v>401.4779753932805</v>
+        <v>408.4000094517853</v>
       </c>
       <c r="N60">
-        <v>-291.1446420599472</v>
+        <v>-298.0666761184519</v>
       </c>
       <c r="O60">
-        <v>-101.9006247209815</v>
+        <v>-104.3233366414582</v>
       </c>
       <c r="P60">
-        <v>-189.2440173389656</v>
+        <v>-193.7433394769938</v>
       </c>
       <c r="Q60">
-        <v>-104.2440173389656</v>
+        <v>-108.7433394769938</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4858821175750324</v>
+        <v>0.4966158277597893</v>
       </c>
       <c r="T60">
-        <v>2.162287235684645</v>
+        <v>2.215025948750124</v>
       </c>
       <c r="U60">
         <v>0.3546487374989669</v>
       </c>
       <c r="V60">
-        <v>0.09618626433701248</v>
+        <v>0.09455598867028346</v>
       </c>
       <c r="W60">
-        <v>0.3205364002871035</v>
+        <v>0.3211145754940842</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2748178981057499</v>
+        <v>0.2701599676293814</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3930700889230233</v>
+        <v>0.396158576298013</v>
       </c>
       <c r="C61">
-        <v>3.37334439690494</v>
+        <v>-26.22605095548784</v>
       </c>
       <c r="D61">
-        <v>1143.635344396905</v>
+        <v>1133.553949044512</v>
       </c>
       <c r="E61">
-        <v>717.1620000000001</v>
+        <v>736.6800000000002</v>
       </c>
       <c r="F61">
-        <v>1151.562</v>
+        <v>1171.08</v>
       </c>
       <c r="G61">
         <v>11.3</v>
@@ -6411,37 +6411,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M61">
-        <v>408.4000094517853</v>
+        <v>415.3220435102901</v>
       </c>
       <c r="N61">
-        <v>-298.0666761184519</v>
+        <v>-304.9887101769568</v>
       </c>
       <c r="O61">
-        <v>-104.3233366414582</v>
+        <v>-106.7460485619349</v>
       </c>
       <c r="P61">
-        <v>-193.7433394769938</v>
+        <v>-198.2426616150219</v>
       </c>
       <c r="Q61">
-        <v>-108.7433394769938</v>
+        <v>-113.2426616150219</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4966158277597893</v>
+        <v>0.5078862234537841</v>
       </c>
       <c r="T61">
-        <v>2.215025948750124</v>
+        <v>2.270401597468878</v>
       </c>
       <c r="U61">
         <v>0.3546487374989669</v>
       </c>
       <c r="V61">
-        <v>0.09455598867028346</v>
+        <v>0.09298005552577872</v>
       </c>
       <c r="W61">
-        <v>0.3211145754940842</v>
+        <v>0.3216734781941656</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2701599676293814</v>
+        <v>0.2656573015022249</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.396158576298013</v>
+        <v>0.3992470636730027</v>
       </c>
       <c r="C62">
-        <v>-26.22605095548784</v>
+        <v>-55.64926002445554</v>
       </c>
       <c r="D62">
-        <v>1133.553949044512</v>
+        <v>1123.648739975545</v>
       </c>
       <c r="E62">
-        <v>736.6800000000002</v>
+        <v>756.1980000000002</v>
       </c>
       <c r="F62">
-        <v>1171.08</v>
+        <v>1190.598</v>
       </c>
       <c r="G62">
         <v>11.3</v>
@@ -6493,37 +6493,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M62">
-        <v>415.3220435102901</v>
+        <v>422.244077568795</v>
       </c>
       <c r="N62">
-        <v>-304.9887101769568</v>
+        <v>-311.9107442354617</v>
       </c>
       <c r="O62">
-        <v>-106.7460485619349</v>
+        <v>-109.1687604824116</v>
       </c>
       <c r="P62">
-        <v>-198.2426616150219</v>
+        <v>-202.7419837530501</v>
       </c>
       <c r="Q62">
-        <v>-113.2426616150219</v>
+        <v>-117.7419837530501</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.5078862234537841</v>
+        <v>0.5197345881577273</v>
       </c>
       <c r="T62">
-        <v>2.270401597468878</v>
+        <v>2.328617023045003</v>
       </c>
       <c r="U62">
         <v>0.3546487374989669</v>
       </c>
       <c r="V62">
-        <v>0.09298005552577872</v>
+        <v>0.09145579232043807</v>
       </c>
       <c r="W62">
-        <v>0.3216734781941656</v>
+        <v>0.3222140562155558</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2656573015022249</v>
+        <v>0.2613022637726802</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3992470636730027</v>
+        <v>0.4023355510479923</v>
       </c>
       <c r="C63">
-        <v>-55.64926002445554</v>
+        <v>-84.90086144831548</v>
       </c>
       <c r="D63">
-        <v>1123.648739975545</v>
+        <v>1113.915138551685</v>
       </c>
       <c r="E63">
-        <v>756.1980000000002</v>
+        <v>775.7160000000002</v>
       </c>
       <c r="F63">
-        <v>1190.598</v>
+        <v>1210.116</v>
       </c>
       <c r="G63">
         <v>11.3</v>
@@ -6575,37 +6575,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M63">
-        <v>422.244077568795</v>
+        <v>429.1661116272999</v>
       </c>
       <c r="N63">
-        <v>-311.9107442354617</v>
+        <v>-318.8327782939665</v>
       </c>
       <c r="O63">
-        <v>-109.1687604824116</v>
+        <v>-111.5914724028883</v>
       </c>
       <c r="P63">
-        <v>-202.7419837530501</v>
+        <v>-207.2413058910782</v>
       </c>
       <c r="Q63">
-        <v>-117.7419837530501</v>
+        <v>-122.2413058910782</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.5197345881577273</v>
+        <v>0.5322065510039833</v>
       </c>
       <c r="T63">
-        <v>2.328617023045003</v>
+        <v>2.389896418388292</v>
       </c>
       <c r="U63">
         <v>0.3546487374989669</v>
       </c>
       <c r="V63">
-        <v>0.09145579232043807</v>
+        <v>0.08998069889591488</v>
       </c>
       <c r="W63">
-        <v>0.3222140562155558</v>
+        <v>0.322737196236256</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2613022637726802</v>
+        <v>0.2570877111311854</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.4023355510479923</v>
+        <v>0.405424038422982</v>
       </c>
       <c r="C64">
-        <v>-84.90086144831548</v>
+        <v>-113.9852765781636</v>
       </c>
       <c r="D64">
-        <v>1113.915138551685</v>
+        <v>1104.348723421836</v>
       </c>
       <c r="E64">
-        <v>775.7160000000002</v>
+        <v>795.234</v>
       </c>
       <c r="F64">
-        <v>1210.116</v>
+        <v>1229.634</v>
       </c>
       <c r="G64">
         <v>11.3</v>
@@ -6657,37 +6657,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M64">
-        <v>429.1661116272999</v>
+        <v>436.0881456858046</v>
       </c>
       <c r="N64">
-        <v>-318.8327782939665</v>
+        <v>-325.7548123524713</v>
       </c>
       <c r="O64">
-        <v>-111.5914724028883</v>
+        <v>-114.0141843233649</v>
       </c>
       <c r="P64">
-        <v>-207.2413058910782</v>
+        <v>-211.7406280291063</v>
       </c>
       <c r="Q64">
-        <v>-122.2413058910782</v>
+        <v>-126.7406280291063</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.5322065510039833</v>
+        <v>0.5453526740040909</v>
       </c>
       <c r="T64">
-        <v>2.389896418388292</v>
+        <v>2.454488213479868</v>
       </c>
       <c r="U64">
         <v>0.3546487374989669</v>
       </c>
       <c r="V64">
-        <v>0.08998069889591488</v>
+        <v>0.08855243383407499</v>
       </c>
       <c r="W64">
-        <v>0.322737196236256</v>
+        <v>0.3232437286372514</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2570877111311854</v>
+        <v>0.2530069538116428</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.405424038422982</v>
+        <v>0.4085125257979716</v>
       </c>
       <c r="C65">
-        <v>-113.9852765781636</v>
+        <v>-142.9067761743534</v>
       </c>
       <c r="D65">
-        <v>1104.348723421836</v>
+        <v>1094.945223825647</v>
       </c>
       <c r="E65">
-        <v>795.234</v>
+        <v>814.7520000000001</v>
       </c>
       <c r="F65">
-        <v>1229.634</v>
+        <v>1249.152</v>
       </c>
       <c r="G65">
         <v>11.3</v>
@@ -6739,37 +6739,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M65">
-        <v>436.0881456858046</v>
+        <v>443.0101797443095</v>
       </c>
       <c r="N65">
-        <v>-325.7548123524713</v>
+        <v>-332.6768464109762</v>
       </c>
       <c r="O65">
-        <v>-114.0141843233649</v>
+        <v>-116.4368962438416</v>
       </c>
       <c r="P65">
-        <v>-211.7406280291063</v>
+        <v>-216.2399501671345</v>
       </c>
       <c r="Q65">
-        <v>-126.7406280291063</v>
+        <v>-131.2399501671345</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5453526740040909</v>
+        <v>0.5592291371708711</v>
       </c>
       <c r="T65">
-        <v>2.454488213479868</v>
+        <v>2.522668441632086</v>
       </c>
       <c r="U65">
         <v>0.3546487374989669</v>
       </c>
       <c r="V65">
-        <v>0.08855243383407499</v>
+        <v>0.08716880205541756</v>
       </c>
       <c r="W65">
-        <v>0.3232437286372514</v>
+        <v>0.3237344319007157</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2530069538116428</v>
+        <v>0.2490537201583358</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.4085125257979716</v>
+        <v>0.4116010131729613</v>
       </c>
       <c r="C66">
-        <v>-142.9067761743534</v>
+        <v>-171.6694867637466</v>
       </c>
       <c r="D66">
-        <v>1094.945223825647</v>
+        <v>1085.700513236254</v>
       </c>
       <c r="E66">
-        <v>814.7520000000001</v>
+        <v>834.2700000000001</v>
       </c>
       <c r="F66">
-        <v>1249.152</v>
+        <v>1268.67</v>
       </c>
       <c r="G66">
         <v>11.3</v>
@@ -6821,37 +6821,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M66">
-        <v>443.0101797443095</v>
+        <v>449.9322138028143</v>
       </c>
       <c r="N66">
-        <v>-332.6768464109762</v>
+        <v>-339.5988804694809</v>
       </c>
       <c r="O66">
-        <v>-116.4368962438416</v>
+        <v>-118.8596081643183</v>
       </c>
       <c r="P66">
-        <v>-216.2399501671345</v>
+        <v>-220.7392723051626</v>
       </c>
       <c r="Q66">
-        <v>-131.2399501671345</v>
+        <v>-135.7392723051626</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5592291371708711</v>
+        <v>0.5738985410900389</v>
       </c>
       <c r="T66">
-        <v>2.522668441632086</v>
+        <v>2.594744682821574</v>
       </c>
       <c r="U66">
         <v>0.3546487374989669</v>
       </c>
       <c r="V66">
-        <v>0.08716880205541756</v>
+        <v>0.08582774356225729</v>
       </c>
       <c r="W66">
-        <v>0.3237344319007157</v>
+        <v>0.3242100366022272</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2490537201583358</v>
+        <v>0.2452221244635924</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.4116010131729613</v>
+        <v>0.414689500547951</v>
       </c>
       <c r="C67">
-        <v>-171.6694867637466</v>
+        <v>-200.2773966776074</v>
       </c>
       <c r="D67">
-        <v>1085.700513236254</v>
+        <v>1076.610603322393</v>
       </c>
       <c r="E67">
-        <v>834.2700000000001</v>
+        <v>853.7880000000001</v>
       </c>
       <c r="F67">
-        <v>1268.67</v>
+        <v>1288.188</v>
       </c>
       <c r="G67">
         <v>11.3</v>
@@ -6903,37 +6903,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M67">
-        <v>449.9322138028143</v>
+        <v>456.8542478613192</v>
       </c>
       <c r="N67">
-        <v>-339.5988804694809</v>
+        <v>-346.5209145279858</v>
       </c>
       <c r="O67">
-        <v>-118.8596081643183</v>
+        <v>-121.282320084795</v>
       </c>
       <c r="P67">
-        <v>-220.7392723051626</v>
+        <v>-225.2385944431908</v>
       </c>
       <c r="Q67">
-        <v>-135.7392723051626</v>
+        <v>-140.2385944431908</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5738985410900389</v>
+        <v>0.5894308511220989</v>
       </c>
       <c r="T67">
-        <v>2.594744682821574</v>
+        <v>2.671060702904562</v>
       </c>
       <c r="U67">
         <v>0.3546487374989669</v>
       </c>
       <c r="V67">
-        <v>0.08582774356225729</v>
+        <v>0.0845273232052534</v>
       </c>
       <c r="W67">
-        <v>0.3242100366022272</v>
+        <v>0.3246712290400566</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2452221244635924</v>
+        <v>0.2415066377292954</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.414689500547951</v>
+        <v>0.4177779879229407</v>
       </c>
       <c r="C68">
-        <v>-200.2773966776074</v>
+        <v>-228.73436178871</v>
       </c>
       <c r="D68">
-        <v>1076.610603322393</v>
+        <v>1067.67163821129</v>
       </c>
       <c r="E68">
-        <v>853.7880000000001</v>
+        <v>873.3060000000002</v>
       </c>
       <c r="F68">
-        <v>1288.188</v>
+        <v>1307.706</v>
       </c>
       <c r="G68">
         <v>11.3</v>
@@ -6985,37 +6985,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M68">
-        <v>456.8542478613192</v>
+        <v>463.776281919824</v>
       </c>
       <c r="N68">
-        <v>-346.5209145279858</v>
+        <v>-353.4429485864906</v>
       </c>
       <c r="O68">
-        <v>-121.282320084795</v>
+        <v>-123.7050320052717</v>
       </c>
       <c r="P68">
-        <v>-225.2385944431908</v>
+        <v>-229.7379165812189</v>
       </c>
       <c r="Q68">
-        <v>-140.2385944431908</v>
+        <v>-144.7379165812189</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5894308511220989</v>
+        <v>0.6059045132773141</v>
       </c>
       <c r="T68">
-        <v>2.671060702904562</v>
+        <v>2.752001936325912</v>
       </c>
       <c r="U68">
         <v>0.3546487374989669</v>
       </c>
       <c r="V68">
-        <v>0.0845273232052534</v>
+        <v>0.08326572136636901</v>
       </c>
       <c r="W68">
-        <v>0.3246712290400566</v>
+        <v>0.3251186545394433</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2415066377292954</v>
+        <v>0.2379020610467687</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.4177779879229407</v>
+        <v>0.4208664752979304</v>
       </c>
       <c r="C69">
-        <v>-228.73436178871</v>
+        <v>-257.044110964988</v>
       </c>
       <c r="D69">
-        <v>1067.67163821129</v>
+        <v>1058.879889035012</v>
       </c>
       <c r="E69">
-        <v>873.3060000000002</v>
+        <v>892.8240000000002</v>
       </c>
       <c r="F69">
-        <v>1307.706</v>
+        <v>1327.224</v>
       </c>
       <c r="G69">
         <v>11.3</v>
@@ -7067,37 +7067,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M69">
-        <v>463.776281919824</v>
+        <v>470.6983159783288</v>
       </c>
       <c r="N69">
-        <v>-353.4429485864906</v>
+        <v>-360.3649826449955</v>
       </c>
       <c r="O69">
-        <v>-123.7050320052717</v>
+        <v>-126.1277439257484</v>
       </c>
       <c r="P69">
-        <v>-229.7379165812189</v>
+        <v>-234.2372387192471</v>
       </c>
       <c r="Q69">
-        <v>-144.7379165812189</v>
+        <v>-149.2372387192471</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.6059045132773141</v>
+        <v>0.6234077793172302</v>
       </c>
       <c r="T69">
-        <v>2.752001936325912</v>
+        <v>2.838001996836097</v>
       </c>
       <c r="U69">
         <v>0.3546487374989669</v>
       </c>
       <c r="V69">
-        <v>0.08326572136636901</v>
+        <v>0.08204122546392241</v>
       </c>
       <c r="W69">
-        <v>0.3251186545394433</v>
+        <v>0.3255529204653187</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2379020610467687</v>
+        <v>0.2344035013254926</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.4208664752979304</v>
+        <v>0.42395496267292</v>
       </c>
       <c r="C70">
-        <v>-257.044110964988</v>
+        <v>-285.2102512559397</v>
       </c>
       <c r="D70">
-        <v>1058.879889035012</v>
+        <v>1050.23174874406</v>
       </c>
       <c r="E70">
-        <v>892.8240000000002</v>
+        <v>912.3420000000002</v>
       </c>
       <c r="F70">
-        <v>1327.224</v>
+        <v>1346.742</v>
       </c>
       <c r="G70">
         <v>11.3</v>
@@ -7149,37 +7149,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M70">
-        <v>470.6983159783288</v>
+        <v>477.6203500368337</v>
       </c>
       <c r="N70">
-        <v>-360.3649826449955</v>
+        <v>-367.2870167035004</v>
       </c>
       <c r="O70">
-        <v>-126.1277439257484</v>
+        <v>-128.5504558462251</v>
       </c>
       <c r="P70">
-        <v>-234.2372387192471</v>
+        <v>-238.7365608572753</v>
       </c>
       <c r="Q70">
-        <v>-149.2372387192471</v>
+        <v>-153.7365608572753</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.6234077793172302</v>
+        <v>0.6420402883274634</v>
       </c>
       <c r="T70">
-        <v>2.838001996836097</v>
+        <v>2.929550448346939</v>
       </c>
       <c r="U70">
         <v>0.3546487374989669</v>
       </c>
       <c r="V70">
-        <v>0.08204122546392241</v>
+        <v>0.08085222219632932</v>
       </c>
       <c r="W70">
-        <v>0.3255529204653187</v>
+        <v>0.3259745989730528</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2344035013254926</v>
+        <v>0.2310063491323695</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.42395496267292</v>
+        <v>0.4270434500479097</v>
       </c>
       <c r="C71">
-        <v>-285.2102512559397</v>
+        <v>-313.2362728269381</v>
       </c>
       <c r="D71">
-        <v>1050.23174874406</v>
+        <v>1041.723727173062</v>
       </c>
       <c r="E71">
-        <v>912.3420000000002</v>
+        <v>931.8600000000002</v>
       </c>
       <c r="F71">
-        <v>1346.742</v>
+        <v>1366.26</v>
       </c>
       <c r="G71">
         <v>11.3</v>
@@ -7231,37 +7231,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M71">
-        <v>477.6203500368337</v>
+        <v>484.5423840953385</v>
       </c>
       <c r="N71">
-        <v>-367.2870167035004</v>
+        <v>-374.2090507620052</v>
       </c>
       <c r="O71">
-        <v>-128.5504558462251</v>
+        <v>-130.9731677667018</v>
       </c>
       <c r="P71">
-        <v>-238.7365608572753</v>
+        <v>-243.2358829953034</v>
       </c>
       <c r="Q71">
-        <v>-153.7365608572753</v>
+        <v>-158.2358829953034</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6420402883274634</v>
+        <v>0.6619149646050455</v>
       </c>
       <c r="T71">
-        <v>2.929550448346939</v>
+        <v>3.027202129958504</v>
       </c>
       <c r="U71">
         <v>0.3546487374989669</v>
       </c>
       <c r="V71">
-        <v>0.08085222219632932</v>
+        <v>0.07969719045066748</v>
       </c>
       <c r="W71">
-        <v>0.3259745989730528</v>
+        <v>0.3263842295234229</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2310063491323695</v>
+        <v>0.2277062584304785</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.4270434500479097</v>
+        <v>0.4301319374228993</v>
       </c>
       <c r="C72">
-        <v>-313.2362728269381</v>
+        <v>-341.1255536556271</v>
       </c>
       <c r="D72">
-        <v>1041.723727173062</v>
+        <v>1033.352446344373</v>
       </c>
       <c r="E72">
-        <v>931.8600000000002</v>
+        <v>951.3780000000003</v>
       </c>
       <c r="F72">
-        <v>1366.26</v>
+        <v>1385.778</v>
       </c>
       <c r="G72">
         <v>11.3</v>
@@ -7313,37 +7313,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M72">
-        <v>484.5423840953385</v>
+        <v>491.4644181538434</v>
       </c>
       <c r="N72">
-        <v>-374.2090507620052</v>
+        <v>-381.1310848205101</v>
       </c>
       <c r="O72">
-        <v>-130.9731677667018</v>
+        <v>-133.3958796871785</v>
       </c>
       <c r="P72">
-        <v>-243.2358829953034</v>
+        <v>-247.7352051333316</v>
       </c>
       <c r="Q72">
-        <v>-158.2358829953034</v>
+        <v>-162.7352051333316</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6619149646050455</v>
+        <v>0.683160308212116</v>
       </c>
       <c r="T72">
-        <v>3.027202129958504</v>
+        <v>3.131588410301901</v>
       </c>
       <c r="U72">
         <v>0.3546487374989669</v>
       </c>
       <c r="V72">
-        <v>0.07969719045066748</v>
+        <v>0.07857469481051722</v>
       </c>
       <c r="W72">
-        <v>0.3263842295234229</v>
+        <v>0.3267823211850503</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2277062584304785</v>
+        <v>0.2244991280300492</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.4301319374228993</v>
+        <v>0.433220424797889</v>
       </c>
       <c r="C73">
-        <v>-341.1255536556266</v>
+        <v>-368.8813640036853</v>
       </c>
       <c r="D73">
-        <v>1033.352446344373</v>
+        <v>1025.114635996315</v>
       </c>
       <c r="E73">
-        <v>951.378</v>
+        <v>970.8960000000001</v>
       </c>
       <c r="F73">
-        <v>1385.778</v>
+        <v>1405.296</v>
       </c>
       <c r="G73">
         <v>11.3</v>
@@ -7395,37 +7395,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M73">
-        <v>491.4644181538433</v>
+        <v>498.3864522123482</v>
       </c>
       <c r="N73">
-        <v>-381.13108482051</v>
+        <v>-388.0531188790148</v>
       </c>
       <c r="O73">
-        <v>-133.3958796871785</v>
+        <v>-135.8185916076552</v>
       </c>
       <c r="P73">
-        <v>-247.7352051333315</v>
+        <v>-252.2345272713597</v>
       </c>
       <c r="Q73">
-        <v>-162.7352051333315</v>
+        <v>-167.2345272713597</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6831603082121158</v>
+        <v>0.7059231763625485</v>
       </c>
       <c r="T73">
-        <v>3.131588410301899</v>
+        <v>3.243430853526967</v>
       </c>
       <c r="U73">
         <v>0.3546487374989669</v>
       </c>
       <c r="V73">
-        <v>0.07857469481051724</v>
+        <v>0.07748337960481561</v>
       </c>
       <c r="W73">
-        <v>0.3267823211850503</v>
+        <v>0.3271693547449658</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2244991280300493</v>
+        <v>0.2213810845851875</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.433220424797889</v>
+        <v>0.4363089121728787</v>
       </c>
       <c r="C74">
-        <v>-368.8813640036853</v>
+        <v>-396.5068706763886</v>
       </c>
       <c r="D74">
-        <v>1025.114635996315</v>
+        <v>1017.007129323611</v>
       </c>
       <c r="E74">
-        <v>970.8960000000001</v>
+        <v>990.4140000000001</v>
       </c>
       <c r="F74">
-        <v>1405.296</v>
+        <v>1424.814</v>
       </c>
       <c r="G74">
         <v>11.3</v>
@@ -7477,37 +7477,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M74">
-        <v>498.3864522123482</v>
+        <v>505.308486270853</v>
       </c>
       <c r="N74">
-        <v>-388.0531188790148</v>
+        <v>-394.9751529375196</v>
       </c>
       <c r="O74">
-        <v>-135.8185916076552</v>
+        <v>-138.2413035281319</v>
       </c>
       <c r="P74">
-        <v>-252.2345272713597</v>
+        <v>-256.7338494093877</v>
       </c>
       <c r="Q74">
-        <v>-167.2345272713597</v>
+        <v>-171.7338494093877</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.7059231763625485</v>
+        <v>0.7303721828944949</v>
       </c>
       <c r="T74">
-        <v>3.243430853526967</v>
+        <v>3.363557922176115</v>
       </c>
       <c r="U74">
         <v>0.3546487374989669</v>
       </c>
       <c r="V74">
-        <v>0.07748337960481561</v>
+        <v>0.07642196344584554</v>
       </c>
       <c r="W74">
-        <v>0.3271693547449658</v>
+        <v>0.3275457846457056</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2213810845851875</v>
+        <v>0.2183484669881302</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.4363089121728787</v>
+        <v>0.4393973995478684</v>
       </c>
       <c r="C75">
-        <v>-396.5068706763886</v>
+        <v>-424.0051410816266</v>
       </c>
       <c r="D75">
-        <v>1017.007129323611</v>
+        <v>1009.026858918374</v>
       </c>
       <c r="E75">
-        <v>990.4140000000001</v>
+        <v>1009.932</v>
       </c>
       <c r="F75">
-        <v>1424.814</v>
+        <v>1444.332</v>
       </c>
       <c r="G75">
         <v>11.3</v>
@@ -7559,37 +7559,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M75">
-        <v>505.308486270853</v>
+        <v>512.2305203293579</v>
       </c>
       <c r="N75">
-        <v>-394.9751529375196</v>
+        <v>-401.8971869960245</v>
       </c>
       <c r="O75">
-        <v>-138.2413035281319</v>
+        <v>-140.6640154486086</v>
       </c>
       <c r="P75">
-        <v>-256.7338494093877</v>
+        <v>-261.233171547416</v>
       </c>
       <c r="Q75">
-        <v>-171.7338494093877</v>
+        <v>-176.233171547416</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.7303721828944949</v>
+        <v>0.7567018822365909</v>
       </c>
       <c r="T75">
-        <v>3.363557922176115</v>
+        <v>3.492925534567504</v>
       </c>
       <c r="U75">
         <v>0.3546487374989669</v>
       </c>
       <c r="V75">
-        <v>0.07642196344584554</v>
+        <v>0.07538923421009086</v>
       </c>
       <c r="W75">
-        <v>0.3275457846457056</v>
+        <v>0.3279120407653442</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2183484669881302</v>
+        <v>0.2153978120288311</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.4393973995478684</v>
+        <v>0.442485886922858</v>
       </c>
       <c r="C76">
-        <v>-424.0051410816266</v>
+        <v>-451.379147099307</v>
       </c>
       <c r="D76">
-        <v>1009.026858918374</v>
+        <v>1001.170852900693</v>
       </c>
       <c r="E76">
-        <v>1009.932</v>
+        <v>1029.45</v>
       </c>
       <c r="F76">
-        <v>1444.332</v>
+        <v>1463.85</v>
       </c>
       <c r="G76">
         <v>11.3</v>
@@ -7641,37 +7641,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M76">
-        <v>512.2305203293579</v>
+        <v>519.1525543878627</v>
       </c>
       <c r="N76">
-        <v>-401.8971869960245</v>
+        <v>-408.8192210545293</v>
       </c>
       <c r="O76">
-        <v>-140.6640154486086</v>
+        <v>-143.0867273690853</v>
       </c>
       <c r="P76">
-        <v>-261.233171547416</v>
+        <v>-265.7324936854441</v>
       </c>
       <c r="Q76">
-        <v>-176.233171547416</v>
+        <v>-180.7324936854441</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7567018822365909</v>
+        <v>0.7851379575260544</v>
       </c>
       <c r="T76">
-        <v>3.492925534567504</v>
+        <v>3.632642555950204</v>
       </c>
       <c r="U76">
         <v>0.3546487374989669</v>
       </c>
       <c r="V76">
-        <v>0.07538923421009086</v>
+        <v>0.07438404442062299</v>
       </c>
       <c r="W76">
-        <v>0.3279120407653442</v>
+        <v>0.3282685300551259</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2153978120288311</v>
+        <v>0.2125258412017801</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.442485886922858</v>
+        <v>0.4455743742978477</v>
       </c>
       <c r="C77">
-        <v>-451.379147099307</v>
+        <v>-478.6317687713997</v>
       </c>
       <c r="D77">
-        <v>1001.170852900693</v>
+        <v>993.4362312286005</v>
       </c>
       <c r="E77">
-        <v>1029.45</v>
+        <v>1048.968</v>
       </c>
       <c r="F77">
-        <v>1463.85</v>
+        <v>1483.368</v>
       </c>
       <c r="G77">
         <v>11.3</v>
@@ -7723,37 +7723,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M77">
-        <v>519.1525543878627</v>
+        <v>526.0745884463676</v>
       </c>
       <c r="N77">
-        <v>-408.8192210545293</v>
+        <v>-415.7412551130342</v>
       </c>
       <c r="O77">
-        <v>-143.0867273690853</v>
+        <v>-145.509439289562</v>
       </c>
       <c r="P77">
-        <v>-265.7324936854441</v>
+        <v>-270.2318158234722</v>
       </c>
       <c r="Q77">
-        <v>-180.7324936854441</v>
+        <v>-185.2318158234722</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.7851379575260544</v>
+        <v>0.8159437057563068</v>
       </c>
       <c r="T77">
-        <v>3.632642555950204</v>
+        <v>3.784002662448129</v>
       </c>
       <c r="U77">
         <v>0.3546487374989669</v>
       </c>
       <c r="V77">
-        <v>0.07438404442062299</v>
+        <v>0.07340530699403583</v>
       </c>
       <c r="W77">
-        <v>0.3282685300551259</v>
+        <v>0.328615638047808</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2125258412017801</v>
+        <v>0.2097294485543881</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.4455743742978477</v>
+        <v>0.4486628616728374</v>
       </c>
       <c r="C78">
-        <v>-478.6317687713997</v>
+        <v>-505.7657978222448</v>
       </c>
       <c r="D78">
-        <v>993.4362312286005</v>
+        <v>985.8202021777554</v>
       </c>
       <c r="E78">
-        <v>1048.968</v>
+        <v>1068.486</v>
       </c>
       <c r="F78">
-        <v>1483.368</v>
+        <v>1502.886</v>
       </c>
       <c r="G78">
         <v>11.3</v>
@@ -7805,37 +7805,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M78">
-        <v>526.0745884463676</v>
+        <v>532.9966225048723</v>
       </c>
       <c r="N78">
-        <v>-415.7412551130342</v>
+        <v>-422.663289171539</v>
       </c>
       <c r="O78">
-        <v>-145.509439289562</v>
+        <v>-147.9321512100386</v>
       </c>
       <c r="P78">
-        <v>-270.2318158234722</v>
+        <v>-274.7311379615003</v>
       </c>
       <c r="Q78">
-        <v>-185.2318158234722</v>
+        <v>-189.7311379615003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.8159437057563068</v>
+        <v>0.8494282147022333</v>
       </c>
       <c r="T78">
-        <v>3.784002662448129</v>
+        <v>3.948524517337179</v>
       </c>
       <c r="U78">
         <v>0.3546487374989669</v>
       </c>
       <c r="V78">
-        <v>0.07340530699403583</v>
+        <v>0.07245199131878863</v>
       </c>
       <c r="W78">
-        <v>0.328615638047808</v>
+        <v>0.3289537302484724</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2097294485543881</v>
+        <v>0.2070056894822533</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.4486628616728374</v>
+        <v>0.4517513490478271</v>
       </c>
       <c r="C79">
-        <v>-505.7657978222448</v>
+        <v>-532.7839410181655</v>
       </c>
       <c r="D79">
-        <v>985.8202021777554</v>
+        <v>978.3200589818348</v>
       </c>
       <c r="E79">
-        <v>1068.486</v>
+        <v>1088.004</v>
       </c>
       <c r="F79">
-        <v>1502.886</v>
+        <v>1522.404</v>
       </c>
       <c r="G79">
         <v>11.3</v>
@@ -7887,37 +7887,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M79">
-        <v>532.9966225048723</v>
+        <v>539.9186565633772</v>
       </c>
       <c r="N79">
-        <v>-422.663289171539</v>
+        <v>-429.5853232300439</v>
       </c>
       <c r="O79">
-        <v>-147.9321512100386</v>
+        <v>-150.3548631305153</v>
       </c>
       <c r="P79">
-        <v>-274.7311379615003</v>
+        <v>-279.2304600995285</v>
       </c>
       <c r="Q79">
-        <v>-189.7311379615003</v>
+        <v>-194.2304600995285</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.8494282147022333</v>
+        <v>0.8859567699159712</v>
       </c>
       <c r="T79">
-        <v>3.948524517337179</v>
+        <v>4.128002904488869</v>
       </c>
       <c r="U79">
         <v>0.3546487374989669</v>
       </c>
       <c r="V79">
-        <v>0.07245199131878863</v>
+        <v>0.0715231196352144</v>
       </c>
       <c r="W79">
-        <v>0.3289537302484724</v>
+        <v>0.3292831534183505</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2070056894822533</v>
+        <v>0.2043517703863269</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.4517513490478271</v>
+        <v>0.4548398364228168</v>
       </c>
       <c r="C80">
-        <v>-532.7839410181655</v>
+        <v>-559.6888233748786</v>
       </c>
       <c r="D80">
-        <v>978.3200589818348</v>
+        <v>970.9331766251217</v>
       </c>
       <c r="E80">
-        <v>1088.004</v>
+        <v>1107.522</v>
       </c>
       <c r="F80">
-        <v>1522.404</v>
+        <v>1541.922</v>
       </c>
       <c r="G80">
         <v>11.3</v>
@@ -7969,37 +7969,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M80">
-        <v>539.9186565633772</v>
+        <v>546.8406906218821</v>
       </c>
       <c r="N80">
-        <v>-429.5853232300439</v>
+        <v>-436.5073572885487</v>
       </c>
       <c r="O80">
-        <v>-150.3548631305153</v>
+        <v>-152.7775750509921</v>
       </c>
       <c r="P80">
-        <v>-279.2304600995285</v>
+        <v>-283.7297822375567</v>
       </c>
       <c r="Q80">
-        <v>-194.2304600995285</v>
+        <v>-198.7297822375567</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.8859567699159712</v>
+        <v>0.9259642351500651</v>
       </c>
       <c r="T80">
-        <v>4.128002904488869</v>
+        <v>4.324574471369291</v>
       </c>
       <c r="U80">
         <v>0.3546487374989669</v>
       </c>
       <c r="V80">
-        <v>0.0715231196352144</v>
+        <v>0.07061776369046485</v>
       </c>
       <c r="W80">
-        <v>0.3292831534183505</v>
+        <v>0.3296042367611431</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2043517703863269</v>
+        <v>0.2017650391156139</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.4548398364228168</v>
+        <v>0.4579283237978063</v>
       </c>
       <c r="C81">
-        <v>-559.6888233748786</v>
+        <v>-586.4829912206885</v>
       </c>
       <c r="D81">
-        <v>970.9331766251217</v>
+        <v>963.6570087793118</v>
       </c>
       <c r="E81">
-        <v>1107.522</v>
+        <v>1127.04</v>
       </c>
       <c r="F81">
-        <v>1541.922</v>
+        <v>1561.44</v>
       </c>
       <c r="G81">
         <v>11.3</v>
@@ -8051,37 +8051,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M81">
-        <v>546.8406906218821</v>
+        <v>553.7627246803869</v>
       </c>
       <c r="N81">
-        <v>-436.5073572885487</v>
+        <v>-443.4293913470535</v>
       </c>
       <c r="O81">
-        <v>-152.7775750509921</v>
+        <v>-155.2002869714687</v>
       </c>
       <c r="P81">
-        <v>-283.7297822375567</v>
+        <v>-288.2291043755848</v>
       </c>
       <c r="Q81">
-        <v>-198.7297822375567</v>
+        <v>-203.2291043755848</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.9259642351500651</v>
+        <v>0.9699724469075682</v>
       </c>
       <c r="T81">
-        <v>4.324574471369291</v>
+        <v>4.540803194937755</v>
       </c>
       <c r="U81">
         <v>0.3546487374989669</v>
       </c>
       <c r="V81">
-        <v>0.07061776369046485</v>
+        <v>0.06973504164433404</v>
       </c>
       <c r="W81">
-        <v>0.3296042367611431</v>
+        <v>0.3299172930203659</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2017650391156139</v>
+        <v>0.1992429761266687</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.4579283237978063</v>
+        <v>0.461016811172796</v>
       </c>
       <c r="C82">
-        <v>-586.4829912206885</v>
+        <v>-613.1689151229718</v>
       </c>
       <c r="D82">
-        <v>963.6570087793118</v>
+        <v>956.4890848770285</v>
       </c>
       <c r="E82">
-        <v>1127.04</v>
+        <v>1146.558</v>
       </c>
       <c r="F82">
-        <v>1561.44</v>
+        <v>1580.958</v>
       </c>
       <c r="G82">
         <v>11.3</v>
@@ -8133,37 +8133,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M82">
-        <v>553.7627246803869</v>
+        <v>560.6847587388918</v>
       </c>
       <c r="N82">
-        <v>-443.4293913470535</v>
+        <v>-450.3514254055584</v>
       </c>
       <c r="O82">
-        <v>-155.2002869714687</v>
+        <v>-157.6229988919454</v>
       </c>
       <c r="P82">
-        <v>-288.2291043755848</v>
+        <v>-292.728426513613</v>
       </c>
       <c r="Q82">
-        <v>-203.2291043755848</v>
+        <v>-207.728426513613</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.9699724469075682</v>
+        <v>1.018613102007967</v>
       </c>
       <c r="T82">
-        <v>4.540803194937755</v>
+        <v>4.779792836776585</v>
       </c>
       <c r="U82">
         <v>0.3546487374989669</v>
       </c>
       <c r="V82">
-        <v>0.06973504164433404</v>
+        <v>0.06887411520428054</v>
       </c>
       <c r="W82">
-        <v>0.3299172930203659</v>
+        <v>0.3302226194954104</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1992429761266687</v>
+        <v>0.1967831862979444</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.461016811172796</v>
+        <v>0.4641052985477857</v>
       </c>
       <c r="C83">
-        <v>-613.1689151229718</v>
+        <v>-639.7489926850151</v>
       </c>
       <c r="D83">
-        <v>956.4890848770285</v>
+        <v>949.4270073149853</v>
       </c>
       <c r="E83">
-        <v>1146.558</v>
+        <v>1166.076</v>
       </c>
       <c r="F83">
-        <v>1580.958</v>
+        <v>1600.476</v>
       </c>
       <c r="G83">
         <v>11.3</v>
@@ -8215,37 +8215,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M83">
-        <v>560.6847587388918</v>
+        <v>567.6067927973966</v>
       </c>
       <c r="N83">
-        <v>-450.3514254055584</v>
+        <v>-457.2734594640632</v>
       </c>
       <c r="O83">
-        <v>-157.6229988919454</v>
+        <v>-160.0457108124221</v>
       </c>
       <c r="P83">
-        <v>-292.728426513613</v>
+        <v>-297.2277486516411</v>
       </c>
       <c r="Q83">
-        <v>-207.728426513613</v>
+        <v>-212.2277486516411</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>1.018613102007967</v>
+        <v>1.072658274341743</v>
       </c>
       <c r="T83">
-        <v>4.779792836776585</v>
+        <v>5.045336883264174</v>
       </c>
       <c r="U83">
         <v>0.3546487374989669</v>
       </c>
       <c r="V83">
-        <v>0.06887411520428054</v>
+        <v>0.068034186970082</v>
       </c>
       <c r="W83">
-        <v>0.3302226194954104</v>
+        <v>0.3305204989832586</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1967831862979444</v>
+        <v>0.1943833913430915</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.4641052985477857</v>
+        <v>0.4671937859227754</v>
       </c>
       <c r="C84">
-        <v>-639.7489926850151</v>
+        <v>-666.2255512198674</v>
       </c>
       <c r="D84">
-        <v>949.4270073149853</v>
+        <v>942.468448780133</v>
       </c>
       <c r="E84">
-        <v>1166.076</v>
+        <v>1185.594000000001</v>
       </c>
       <c r="F84">
-        <v>1600.476</v>
+        <v>1619.994</v>
       </c>
       <c r="G84">
         <v>11.3</v>
@@ -8297,37 +8297,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M84">
-        <v>567.6067927973966</v>
+        <v>574.5288268559015</v>
       </c>
       <c r="N84">
-        <v>-457.2734594640632</v>
+        <v>-464.1954935225681</v>
       </c>
       <c r="O84">
-        <v>-160.0457108124221</v>
+        <v>-162.4684227328988</v>
       </c>
       <c r="P84">
-        <v>-297.2277486516411</v>
+        <v>-301.7270707896693</v>
       </c>
       <c r="Q84">
-        <v>-212.2277486516411</v>
+        <v>-216.7270707896693</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.072658274341743</v>
+        <v>1.133061702244198</v>
       </c>
       <c r="T84">
-        <v>5.045336883264174</v>
+        <v>5.342121405809126</v>
       </c>
       <c r="U84">
         <v>0.3546487374989669</v>
       </c>
       <c r="V84">
-        <v>0.068034186970082</v>
+        <v>0.06721449797044245</v>
       </c>
       <c r="W84">
-        <v>0.3305204989832586</v>
+        <v>0.3308112006521226</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1943833913430915</v>
+        <v>0.1920414227726928</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.4671937859227754</v>
+        <v>0.4702822732977651</v>
       </c>
       <c r="C85">
-        <v>-666.2255512198674</v>
+        <v>-692.6008503074588</v>
       </c>
       <c r="D85">
-        <v>942.468448780133</v>
+        <v>935.6111496925416</v>
       </c>
       <c r="E85">
-        <v>1185.594000000001</v>
+        <v>1205.112000000001</v>
       </c>
       <c r="F85">
-        <v>1619.994</v>
+        <v>1639.512</v>
       </c>
       <c r="G85">
         <v>11.3</v>
@@ -8379,37 +8379,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M85">
-        <v>574.5288268559015</v>
+        <v>581.4508609144063</v>
       </c>
       <c r="N85">
-        <v>-464.1954935225681</v>
+        <v>-471.117527581073</v>
       </c>
       <c r="O85">
-        <v>-162.4684227328988</v>
+        <v>-164.8911346533755</v>
       </c>
       <c r="P85">
-        <v>-301.7270707896693</v>
+        <v>-306.2263929276975</v>
       </c>
       <c r="Q85">
-        <v>-216.7270707896693</v>
+        <v>-221.2263929276975</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.133061702244198</v>
+        <v>1.201015558634461</v>
       </c>
       <c r="T85">
-        <v>5.342121405809126</v>
+        <v>5.676003993672197</v>
       </c>
       <c r="U85">
         <v>0.3546487374989669</v>
       </c>
       <c r="V85">
-        <v>0.06721449797044245</v>
+        <v>0.06641432537555622</v>
       </c>
       <c r="W85">
-        <v>0.3308112006521226</v>
+        <v>0.3310949808526802</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1920414227726928</v>
+        <v>0.1897552153587321</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.4702822732977651</v>
+        <v>0.4733707606727547</v>
       </c>
       <c r="C86">
-        <v>-692.6008503074586</v>
+        <v>-718.8770842408978</v>
       </c>
       <c r="D86">
-        <v>935.6111496925416</v>
+        <v>928.8529157591024</v>
       </c>
       <c r="E86">
-        <v>1205.112</v>
+        <v>1224.63</v>
       </c>
       <c r="F86">
-        <v>1639.512</v>
+        <v>1659.03</v>
       </c>
       <c r="G86">
         <v>11.3</v>
@@ -8461,37 +8461,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M86">
-        <v>581.4508609144062</v>
+        <v>588.372894972911</v>
       </c>
       <c r="N86">
-        <v>-471.1175275810729</v>
+        <v>-478.0395616395776</v>
       </c>
       <c r="O86">
-        <v>-164.8911346533755</v>
+        <v>-167.3138465738522</v>
       </c>
       <c r="P86">
-        <v>-306.2263929276974</v>
+        <v>-310.7257150657255</v>
       </c>
       <c r="Q86">
-        <v>-221.2263929276974</v>
+        <v>-225.7257150657255</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.20101555863446</v>
+        <v>1.278029929210091</v>
       </c>
       <c r="T86">
-        <v>5.676003993672193</v>
+        <v>6.054404259917006</v>
       </c>
       <c r="U86">
         <v>0.3546487374989669</v>
       </c>
       <c r="V86">
-        <v>0.06641432537555624</v>
+        <v>0.06563298037113793</v>
       </c>
       <c r="W86">
-        <v>0.3310949808526802</v>
+        <v>0.3313720838720483</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1897552153587322</v>
+        <v>0.1875228010603941</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.4733707606727547</v>
+        <v>0.4764592480477444</v>
       </c>
       <c r="C87">
-        <v>-718.8770842408978</v>
+        <v>-745.0563843675034</v>
       </c>
       <c r="D87">
-        <v>928.8529157591024</v>
+        <v>922.1916156324969</v>
       </c>
       <c r="E87">
-        <v>1224.63</v>
+        <v>1244.148</v>
       </c>
       <c r="F87">
-        <v>1659.03</v>
+        <v>1678.548</v>
       </c>
       <c r="G87">
         <v>11.3</v>
@@ -8543,37 +8543,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M87">
-        <v>588.372894972911</v>
+        <v>595.2949290314159</v>
       </c>
       <c r="N87">
-        <v>-478.0395616395776</v>
+        <v>-484.9615956980825</v>
       </c>
       <c r="O87">
-        <v>-167.3138465738522</v>
+        <v>-169.7365584943289</v>
       </c>
       <c r="P87">
-        <v>-310.7257150657255</v>
+        <v>-315.2250372037537</v>
       </c>
       <c r="Q87">
-        <v>-225.7257150657255</v>
+        <v>-230.2250372037537</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.278029929210091</v>
+        <v>1.366046352725097</v>
       </c>
       <c r="T87">
-        <v>6.054404259917006</v>
+        <v>6.486861707053935</v>
       </c>
       <c r="U87">
         <v>0.3546487374989669</v>
       </c>
       <c r="V87">
-        <v>0.06563298037113793</v>
+        <v>0.06486980618077585</v>
       </c>
       <c r="W87">
-        <v>0.3313720838720483</v>
+        <v>0.331642742635152</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1875228010603941</v>
+        <v>0.1853423033736453</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.4764592480477444</v>
+        <v>0.4795477354227341</v>
       </c>
       <c r="C88">
-        <v>-745.0563843675034</v>
+        <v>-771.1408213298232</v>
       </c>
       <c r="D88">
-        <v>922.1916156324969</v>
+        <v>915.6251786701771</v>
       </c>
       <c r="E88">
-        <v>1244.148</v>
+        <v>1263.666</v>
       </c>
       <c r="F88">
-        <v>1678.548</v>
+        <v>1698.066</v>
       </c>
       <c r="G88">
         <v>11.3</v>
@@ -8625,37 +8625,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M88">
-        <v>595.2949290314159</v>
+        <v>602.2169630899208</v>
       </c>
       <c r="N88">
-        <v>-484.9615956980825</v>
+        <v>-491.8836297565874</v>
       </c>
       <c r="O88">
-        <v>-169.7365584943289</v>
+        <v>-172.1592704148056</v>
       </c>
       <c r="P88">
-        <v>-315.2250372037537</v>
+        <v>-319.7243593417818</v>
       </c>
       <c r="Q88">
-        <v>-230.2250372037537</v>
+        <v>-234.7243593417818</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.366046352725097</v>
+        <v>1.467603764473182</v>
       </c>
       <c r="T88">
-        <v>6.486861707053935</v>
+        <v>6.985851069135007</v>
       </c>
       <c r="U88">
         <v>0.3546487374989669</v>
       </c>
       <c r="V88">
-        <v>0.06486980618077585</v>
+        <v>0.06412417622467498</v>
       </c>
       <c r="W88">
-        <v>0.331642742635152</v>
+        <v>0.3319071793577246</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1853423033736453</v>
+        <v>0.1832119320705</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.4795477354227341</v>
+        <v>0.4826362227977237</v>
       </c>
       <c r="C89">
-        <v>-771.1408213298232</v>
+        <v>-797.1324072115848</v>
       </c>
       <c r="D89">
-        <v>915.6251786701771</v>
+        <v>909.1515927884153</v>
       </c>
       <c r="E89">
-        <v>1263.666</v>
+        <v>1283.184</v>
       </c>
       <c r="F89">
-        <v>1698.066</v>
+        <v>1717.584</v>
       </c>
       <c r="G89">
         <v>11.3</v>
@@ -8707,37 +8707,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M89">
-        <v>602.2169630899208</v>
+        <v>609.1389971484255</v>
       </c>
       <c r="N89">
-        <v>-491.8836297565874</v>
+        <v>-498.8056638150921</v>
       </c>
       <c r="O89">
-        <v>-172.1592704148056</v>
+        <v>-174.5819823352822</v>
       </c>
       <c r="P89">
-        <v>-319.7243593417818</v>
+        <v>-324.2236814798099</v>
       </c>
       <c r="Q89">
-        <v>-234.7243593417818</v>
+        <v>-239.2236814798099</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.467603764473182</v>
+        <v>1.586087411512614</v>
       </c>
       <c r="T89">
-        <v>6.985851069135007</v>
+        <v>7.568005324896259</v>
       </c>
       <c r="U89">
         <v>0.3546487374989669</v>
       </c>
       <c r="V89">
-        <v>0.06412417622467498</v>
+        <v>0.06339549240394005</v>
       </c>
       <c r="W89">
-        <v>0.3319071793577246</v>
+        <v>0.3321656061547842</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1832119320705</v>
+        <v>0.1811299782969716</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.4826362227977237</v>
+        <v>0.4857247101727133</v>
       </c>
       <c r="C90">
-        <v>-797.1324072115848</v>
+        <v>-823.0330975932557</v>
       </c>
       <c r="D90">
-        <v>909.1515927884153</v>
+        <v>902.7689024067445</v>
       </c>
       <c r="E90">
-        <v>1283.184</v>
+        <v>1302.702</v>
       </c>
       <c r="F90">
-        <v>1717.584</v>
+        <v>1737.102</v>
       </c>
       <c r="G90">
         <v>11.3</v>
@@ -8789,37 +8789,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M90">
-        <v>609.1389971484255</v>
+        <v>616.0610312069304</v>
       </c>
       <c r="N90">
-        <v>-498.8056638150921</v>
+        <v>-505.727697873597</v>
       </c>
       <c r="O90">
-        <v>-174.5819823352822</v>
+        <v>-177.0046942557589</v>
       </c>
       <c r="P90">
-        <v>-324.2236814798099</v>
+        <v>-328.7230036178381</v>
       </c>
       <c r="Q90">
-        <v>-239.2236814798099</v>
+        <v>-243.7230036178381</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.586087411512614</v>
+        <v>1.726113539831942</v>
       </c>
       <c r="T90">
-        <v>7.568005324896259</v>
+        <v>8.256005808977736</v>
       </c>
       <c r="U90">
         <v>0.3546487374989669</v>
       </c>
       <c r="V90">
-        <v>0.06339549240394005</v>
+        <v>0.06268318350052499</v>
       </c>
       <c r="W90">
-        <v>0.3321656061547842</v>
+        <v>0.3324182256080896</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1811299782969716</v>
+        <v>0.1790948100015001</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.4857247101727133</v>
+        <v>0.488813197547703</v>
       </c>
       <c r="C91">
-        <v>-823.0330975932557</v>
+        <v>-848.8447935216174</v>
       </c>
       <c r="D91">
-        <v>902.7689024067445</v>
+        <v>896.4752064783828</v>
       </c>
       <c r="E91">
-        <v>1302.702</v>
+        <v>1322.22</v>
       </c>
       <c r="F91">
-        <v>1737.102</v>
+        <v>1756.62</v>
       </c>
       <c r="G91">
         <v>11.3</v>
@@ -8871,37 +8871,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M91">
-        <v>616.0610312069304</v>
+        <v>622.9830652654352</v>
       </c>
       <c r="N91">
-        <v>-505.727697873597</v>
+        <v>-512.6497319321019</v>
       </c>
       <c r="O91">
-        <v>-177.0046942557589</v>
+        <v>-179.4274061762356</v>
       </c>
       <c r="P91">
-        <v>-328.7230036178381</v>
+        <v>-333.2223257558662</v>
       </c>
       <c r="Q91">
-        <v>-243.7230036178381</v>
+        <v>-248.2223257558662</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.726113539831942</v>
+        <v>1.894144893815137</v>
       </c>
       <c r="T91">
-        <v>8.256005808977736</v>
+        <v>9.08160638987551</v>
       </c>
       <c r="U91">
         <v>0.3546487374989669</v>
       </c>
       <c r="V91">
-        <v>0.06268318350052499</v>
+        <v>0.06198670368385249</v>
       </c>
       <c r="W91">
-        <v>0.3324182256080896</v>
+        <v>0.332665231295766</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1790948100015001</v>
+        <v>0.17710486766815</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.488813197547703</v>
+        <v>0.4919016849226927</v>
       </c>
       <c r="C92">
-        <v>-848.8447935216174</v>
+        <v>-874.5693433975265</v>
       </c>
       <c r="D92">
-        <v>896.4752064783828</v>
+        <v>890.2686566024737</v>
       </c>
       <c r="E92">
-        <v>1322.22</v>
+        <v>1341.738</v>
       </c>
       <c r="F92">
-        <v>1756.62</v>
+        <v>1776.138</v>
       </c>
       <c r="G92">
         <v>11.3</v>
@@ -8953,37 +8953,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M92">
-        <v>622.9830652654352</v>
+        <v>629.90509932394</v>
       </c>
       <c r="N92">
-        <v>-512.6497319321019</v>
+        <v>-519.5717659906067</v>
       </c>
       <c r="O92">
-        <v>-179.4274061762356</v>
+        <v>-181.8501180967123</v>
       </c>
       <c r="P92">
-        <v>-333.2223257558662</v>
+        <v>-337.7216478938943</v>
       </c>
       <c r="Q92">
-        <v>-248.2223257558662</v>
+        <v>-252.7216478938943</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.894144893815137</v>
+        <v>2.099516548683485</v>
       </c>
       <c r="T92">
-        <v>9.08160638987551</v>
+        <v>10.09067376652835</v>
       </c>
       <c r="U92">
         <v>0.3546487374989669</v>
       </c>
       <c r="V92">
-        <v>0.06198670368385249</v>
+        <v>0.06130553111589807</v>
       </c>
       <c r="W92">
-        <v>0.332665231295766</v>
+        <v>0.33290680828701</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.17710486766815</v>
+        <v>0.1751586603311374</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.4919016849226927</v>
+        <v>0.4949901722976824</v>
       </c>
       <c r="C93">
-        <v>-874.5693433975265</v>
+        <v>-900.2085447857964</v>
       </c>
       <c r="D93">
-        <v>890.2686566024737</v>
+        <v>884.1474552142038</v>
       </c>
       <c r="E93">
-        <v>1341.738</v>
+        <v>1361.256</v>
       </c>
       <c r="F93">
-        <v>1776.138</v>
+        <v>1795.656</v>
       </c>
       <c r="G93">
         <v>11.3</v>
@@ -9035,37 +9035,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M93">
-        <v>629.90509932394</v>
+        <v>636.8271333824449</v>
       </c>
       <c r="N93">
-        <v>-519.5717659906067</v>
+        <v>-526.4938000491115</v>
       </c>
       <c r="O93">
-        <v>-181.8501180967123</v>
+        <v>-184.272830017189</v>
       </c>
       <c r="P93">
-        <v>-337.7216478938943</v>
+        <v>-342.2209700319225</v>
       </c>
       <c r="Q93">
-        <v>-252.7216478938943</v>
+        <v>-257.2209700319225</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.099516548683485</v>
+        <v>2.356231117268921</v>
       </c>
       <c r="T93">
-        <v>10.09067376652835</v>
+        <v>11.35200798734439</v>
       </c>
       <c r="U93">
         <v>0.3546487374989669</v>
       </c>
       <c r="V93">
-        <v>0.06130553111589807</v>
+        <v>0.060639166647247</v>
       </c>
       <c r="W93">
-        <v>0.33290680828701</v>
+        <v>0.3331431336045312</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1751586603311374</v>
+        <v>0.1732547618492772</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.4949901722976824</v>
+        <v>0.4980786596726721</v>
       </c>
       <c r="C94">
-        <v>-900.2085447857964</v>
+        <v>-925.7641461509252</v>
       </c>
       <c r="D94">
-        <v>884.1474552142038</v>
+        <v>878.1098538490751</v>
       </c>
       <c r="E94">
-        <v>1361.256</v>
+        <v>1380.774</v>
       </c>
       <c r="F94">
-        <v>1795.656</v>
+        <v>1815.174</v>
       </c>
       <c r="G94">
         <v>11.3</v>
@@ -9117,37 +9117,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M94">
-        <v>636.8271333824449</v>
+        <v>643.7491674409497</v>
       </c>
       <c r="N94">
-        <v>-526.4938000491115</v>
+        <v>-533.4158341076163</v>
       </c>
       <c r="O94">
-        <v>-184.272830017189</v>
+        <v>-186.6955419376657</v>
       </c>
       <c r="P94">
-        <v>-342.2209700319225</v>
+        <v>-346.7202921699507</v>
       </c>
       <c r="Q94">
-        <v>-257.2209700319225</v>
+        <v>-261.7202921699507</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.356231117268921</v>
+        <v>2.686292705450196</v>
       </c>
       <c r="T94">
-        <v>11.35200798734439</v>
+        <v>12.97372341410788</v>
       </c>
       <c r="U94">
         <v>0.3546487374989669</v>
       </c>
       <c r="V94">
-        <v>0.060639166647247</v>
+        <v>0.0599871325972766</v>
       </c>
       <c r="W94">
-        <v>0.3331431336045312</v>
+        <v>0.3333743766571596</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1732547618492772</v>
+        <v>0.1713918074207903</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.4980786596726721</v>
+        <v>0.5011671470476617</v>
       </c>
       <c r="C95">
-        <v>-925.7641461509252</v>
+        <v>-951.2378485221878</v>
       </c>
       <c r="D95">
-        <v>878.1098538490751</v>
+        <v>872.1541514778124</v>
       </c>
       <c r="E95">
-        <v>1380.774</v>
+        <v>1400.292</v>
       </c>
       <c r="F95">
-        <v>1815.174</v>
+        <v>1834.692</v>
       </c>
       <c r="G95">
         <v>11.3</v>
@@ -9199,37 +9199,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M95">
-        <v>643.7491674409497</v>
+        <v>650.6712014994546</v>
       </c>
       <c r="N95">
-        <v>-533.4158341076163</v>
+        <v>-540.3378681661212</v>
       </c>
       <c r="O95">
-        <v>-186.6955419376657</v>
+        <v>-189.1182538581424</v>
       </c>
       <c r="P95">
-        <v>-346.7202921699507</v>
+        <v>-351.2196143079788</v>
       </c>
       <c r="Q95">
-        <v>-261.7202921699507</v>
+        <v>-266.2196143079788</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.686292705450196</v>
+        <v>3.12637482302523</v>
       </c>
       <c r="T95">
-        <v>12.97372341410788</v>
+        <v>15.13601064979253</v>
       </c>
       <c r="U95">
         <v>0.3546487374989669</v>
       </c>
       <c r="V95">
-        <v>0.0599871325972766</v>
+        <v>0.05934897161219919</v>
       </c>
       <c r="W95">
-        <v>0.3333743766571596</v>
+        <v>0.3336006996448384</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1713918074207903</v>
+        <v>0.1695684903205692</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.5011671470476617</v>
+        <v>0.5042556344226514</v>
       </c>
       <c r="C96">
-        <v>-951.2378485221878</v>
+        <v>-976.6313070914262</v>
       </c>
       <c r="D96">
-        <v>872.1541514778124</v>
+        <v>866.2786929085742</v>
       </c>
       <c r="E96">
-        <v>1400.292</v>
+        <v>1419.81</v>
       </c>
       <c r="F96">
-        <v>1834.692</v>
+        <v>1854.21</v>
       </c>
       <c r="G96">
         <v>11.3</v>
@@ -9281,37 +9281,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M96">
-        <v>650.6712014994546</v>
+        <v>657.5932355579595</v>
       </c>
       <c r="N96">
-        <v>-540.3378681661212</v>
+        <v>-547.2599022246261</v>
       </c>
       <c r="O96">
-        <v>-189.1182538581424</v>
+        <v>-191.5409657786191</v>
       </c>
       <c r="P96">
-        <v>-351.2196143079788</v>
+        <v>-355.718936446007</v>
       </c>
       <c r="Q96">
-        <v>-266.2196143079788</v>
+        <v>-270.718936446007</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.12637482302523</v>
+        <v>3.742489787630277</v>
       </c>
       <c r="T96">
-        <v>15.13601064979253</v>
+        <v>18.16321277975104</v>
       </c>
       <c r="U96">
         <v>0.3546487374989669</v>
       </c>
       <c r="V96">
-        <v>0.05934897161219919</v>
+        <v>0.05872424559522867</v>
       </c>
       <c r="W96">
-        <v>0.3336006996448384</v>
+        <v>0.3338222579380397</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1695684903205692</v>
+        <v>0.1677835588435105</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.5042556344226514</v>
+        <v>0.5073441217976411</v>
       </c>
       <c r="C97">
-        <v>-976.6313070914262</v>
+        <v>-1001.946132746685</v>
       </c>
       <c r="D97">
-        <v>866.2786929085742</v>
+        <v>860.481867253315</v>
       </c>
       <c r="E97">
-        <v>1419.81</v>
+        <v>1439.328</v>
       </c>
       <c r="F97">
-        <v>1854.21</v>
+        <v>1873.728</v>
       </c>
       <c r="G97">
         <v>11.3</v>
@@ -9363,37 +9363,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M97">
-        <v>657.5932355579595</v>
+        <v>664.5152696164643</v>
       </c>
       <c r="N97">
-        <v>-547.2599022246261</v>
+        <v>-554.1819362831309</v>
       </c>
       <c r="O97">
-        <v>-191.5409657786191</v>
+        <v>-193.9636776990958</v>
       </c>
       <c r="P97">
-        <v>-355.718936446007</v>
+        <v>-360.2182585840351</v>
       </c>
       <c r="Q97">
-        <v>-270.718936446007</v>
+        <v>-275.2182585840351</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.742489787630277</v>
+        <v>4.666662234537849</v>
       </c>
       <c r="T97">
-        <v>18.16321277975104</v>
+        <v>22.70401597468882</v>
       </c>
       <c r="U97">
         <v>0.3546487374989669</v>
       </c>
       <c r="V97">
-        <v>0.05872424559522867</v>
+        <v>0.0581125347036117</v>
       </c>
       <c r="W97">
-        <v>0.3338222579380397</v>
+        <v>0.3340392004334661</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1677835588435105</v>
+        <v>0.1660358134388906</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.5073441217976411</v>
+        <v>0.5104326091726308</v>
       </c>
       <c r="C98">
-        <v>-1001.946132746685</v>
+        <v>-1027.183893544688</v>
       </c>
       <c r="D98">
-        <v>860.481867253315</v>
+        <v>854.7621064553119</v>
       </c>
       <c r="E98">
-        <v>1439.328</v>
+        <v>1458.846</v>
       </c>
       <c r="F98">
-        <v>1873.728</v>
+        <v>1893.246</v>
       </c>
       <c r="G98">
         <v>11.3</v>
@@ -9445,37 +9445,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M98">
-        <v>664.5152696164643</v>
+        <v>671.437303674969</v>
       </c>
       <c r="N98">
-        <v>-554.1819362831309</v>
+        <v>-561.1039703416357</v>
       </c>
       <c r="O98">
-        <v>-193.9636776990958</v>
+        <v>-196.3863896195725</v>
       </c>
       <c r="P98">
-        <v>-360.2182585840351</v>
+        <v>-364.7175807220632</v>
       </c>
       <c r="Q98">
-        <v>-275.2182585840351</v>
+        <v>-279.7175807220632</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.666662234537838</v>
+        <v>6.20694964605045</v>
       </c>
       <c r="T98">
-        <v>22.70401597468876</v>
+        <v>30.27202129958501</v>
       </c>
       <c r="U98">
         <v>0.3546487374989669</v>
       </c>
       <c r="V98">
-        <v>0.0581125347036117</v>
+        <v>0.05751343640769818</v>
       </c>
       <c r="W98">
-        <v>0.3340392004334661</v>
+        <v>0.3342516698877496</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1660358134388906</v>
+        <v>0.1643241040219948</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.5104326091726308</v>
+        <v>0.5135210965476205</v>
       </c>
       <c r="C99">
-        <v>-1027.183893544688</v>
+        <v>-1052.346116124967</v>
       </c>
       <c r="D99">
-        <v>854.7621064553119</v>
+        <v>849.1178838750334</v>
       </c>
       <c r="E99">
-        <v>1458.846</v>
+        <v>1478.364</v>
       </c>
       <c r="F99">
-        <v>1893.246</v>
+        <v>1912.764</v>
       </c>
       <c r="G99">
         <v>11.3</v>
@@ -9527,37 +9527,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M99">
-        <v>671.437303674969</v>
+        <v>678.3593377334739</v>
       </c>
       <c r="N99">
-        <v>-561.1039703416357</v>
+        <v>-568.0260044001406</v>
       </c>
       <c r="O99">
-        <v>-196.3863896195725</v>
+        <v>-198.8091015400492</v>
       </c>
       <c r="P99">
-        <v>-364.7175807220632</v>
+        <v>-369.2169028600914</v>
       </c>
       <c r="Q99">
-        <v>-279.7175807220632</v>
+        <v>-284.2169028600914</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>6.20694964605045</v>
+        <v>9.287524469075676</v>
       </c>
       <c r="T99">
-        <v>30.27202129958501</v>
+        <v>45.40803194937752</v>
       </c>
       <c r="U99">
         <v>0.3546487374989669</v>
       </c>
       <c r="V99">
-        <v>0.05751343640769818</v>
+        <v>0.05692656460761963</v>
       </c>
       <c r="W99">
-        <v>0.3342516698877496</v>
+        <v>0.3344598032307212</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1643241040219948</v>
+        <v>0.1626473274503418</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.5135210965476205</v>
+        <v>0.5166095839226101</v>
       </c>
       <c r="C100">
-        <v>-1052.346116124967</v>
+        <v>-1077.434287068337</v>
       </c>
       <c r="D100">
-        <v>849.1178838750334</v>
+        <v>843.5477129316629</v>
       </c>
       <c r="E100">
-        <v>1478.364</v>
+        <v>1497.882</v>
       </c>
       <c r="F100">
-        <v>1912.764</v>
+        <v>1932.282</v>
       </c>
       <c r="G100">
         <v>11.3</v>
@@ -9609,37 +9609,37 @@
         <v>110.3333333333333</v>
       </c>
       <c r="M100">
-        <v>678.3593377334739</v>
+        <v>685.2813717919787</v>
       </c>
       <c r="N100">
-        <v>-568.0260044001406</v>
+        <v>-574.9480384586453</v>
       </c>
       <c r="O100">
-        <v>-198.8091015400492</v>
+        <v>-201.2318134605258</v>
       </c>
       <c r="P100">
-        <v>-369.2169028600914</v>
+        <v>-373.7162249981195</v>
       </c>
       <c r="Q100">
-        <v>-284.2169028600914</v>
+        <v>-288.7162249981195</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>9.287524469075676</v>
+        <v>18.52924893815135</v>
       </c>
       <c r="T100">
-        <v>45.40803194937752</v>
+        <v>90.81606389875502</v>
       </c>
       <c r="U100">
         <v>0.3546487374989669</v>
       </c>
       <c r="V100">
-        <v>0.05692656460761963</v>
+        <v>0.05635154880350226</v>
       </c>
       <c r="W100">
-        <v>0.3344598032307212</v>
+        <v>0.3346637318596934</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1626473274503418</v>
+        <v>0.1610044251528636</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.5166095839226101</v>
-      </c>
-      <c r="C101">
-        <v>-1077.434287068337</v>
-      </c>
-      <c r="D101">
-        <v>843.5477129316629</v>
-      </c>
-      <c r="E101">
-        <v>1497.882</v>
-      </c>
-      <c r="F101">
-        <v>1932.282</v>
-      </c>
-      <c r="G101">
-        <v>11.3</v>
-      </c>
-      <c r="H101">
-        <v>1517.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>195.3333333333333</v>
-      </c>
-      <c r="K101">
-        <v>85</v>
-      </c>
-      <c r="L101">
-        <v>110.3333333333333</v>
-      </c>
-      <c r="M101">
-        <v>685.2813717919787</v>
-      </c>
-      <c r="N101">
-        <v>-574.9480384586453</v>
-      </c>
-      <c r="O101">
-        <v>-201.2318134605258</v>
-      </c>
-      <c r="P101">
-        <v>-373.7162249981195</v>
-      </c>
-      <c r="Q101">
-        <v>-288.7162249981195</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>18.52924893815135</v>
-      </c>
-      <c r="T101">
-        <v>90.81606389875502</v>
-      </c>
-      <c r="U101">
-        <v>0.3546487374989669</v>
-      </c>
-      <c r="V101">
-        <v>0.05635154880350226</v>
-      </c>
-      <c r="W101">
-        <v>0.3346637318596934</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1610044251528636</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
